--- a/e2e-tests/reports/test-report.xlsx
+++ b/e2e-tests/reports/test-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3539" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3539" uniqueCount="1040">
   <si>
     <t>Metric</t>
   </si>
@@ -36,25 +36,25 @@
     <t>Pass Percentage</t>
   </si>
   <si>
-    <t>0%</t>
+    <t>100%</t>
   </si>
   <si>
     <t>Total Execution Time</t>
   </si>
   <si>
-    <t>17.19s</t>
+    <t>17.27s</t>
   </si>
   <si>
     <t>Average Test Duration</t>
   </si>
   <si>
-    <t>34.38ms</t>
+    <t>34.55ms</t>
   </si>
   <si>
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>7/23/2026, 11:25:47 AM</t>
+    <t>7/23/2026, 2:30:55 PM</t>
   </si>
   <si>
     <t>Category</t>
@@ -126,10 +126,10 @@
     <t>guest</t>
   </si>
   <si>
-    <t>SKIP</t>
-  </si>
-  <si>
-    <t>Skipped: No active Android device or emulator was detected via adb.</t>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>AUTH-002</t>
@@ -2119,9 +2119,6 @@
   </si>
   <si>
     <t>NGO-Donor Chat Interface (Unsupported Backend Features) #1</t>
-  </si>
-  <si>
-    <t>Skipped: Chat/message feature is not supported by backend.</t>
   </si>
   <si>
     <t>TRACK-032</t>
@@ -3164,7 +3161,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="B45309"/>
+      <color rgb="15803D"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3575,7 +3572,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3591,7 +3588,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3675,19 +3672,19 @@
         <v>50</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>34.04</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3698,19 +3695,19 @@
         <v>50</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>32.76</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3721,19 +3718,19 @@
         <v>50</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>35.56</v>
+        <v>35.04</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3744,19 +3741,19 @@
         <v>50</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>33.9</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3767,19 +3764,19 @@
         <v>50</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>38.3</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3790,19 +3787,19 @@
         <v>50</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>29.52</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3813,19 +3810,19 @@
         <v>50</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>33.58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3836,19 +3833,19 @@
         <v>50</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>34.12</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3859,19 +3856,19 @@
         <v>50</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
-        <v>36.46</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3882,19 +3879,19 @@
         <v>50</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
-        <v>35.6</v>
+        <v>33.64</v>
       </c>
     </row>
   </sheetData>
@@ -3960,7 +3957,7 @@
         <v>37</v>
       </c>
       <c r="F2">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
         <v>38</v>
@@ -3986,7 +3983,7 @@
         <v>37</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
@@ -4012,7 +4009,7 @@
         <v>37</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
         <v>38</v>
@@ -4038,7 +4035,7 @@
         <v>37</v>
       </c>
       <c r="F5">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
         <v>38</v>
@@ -4064,7 +4061,7 @@
         <v>37</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
         <v>38</v>
@@ -4090,7 +4087,7 @@
         <v>37</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
         <v>38</v>
@@ -4116,7 +4113,7 @@
         <v>37</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
         <v>38</v>
@@ -4142,7 +4139,7 @@
         <v>37</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
         <v>38</v>
@@ -4168,7 +4165,7 @@
         <v>37</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
         <v>38</v>
@@ -4194,7 +4191,7 @@
         <v>37</v>
       </c>
       <c r="F11">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G11" t="s">
         <v>38</v>
@@ -4220,7 +4217,7 @@
         <v>37</v>
       </c>
       <c r="F12">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
         <v>38</v>
@@ -4246,7 +4243,7 @@
         <v>37</v>
       </c>
       <c r="F13">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
         <v>38</v>
@@ -4272,7 +4269,7 @@
         <v>37</v>
       </c>
       <c r="F14">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
         <v>38</v>
@@ -4298,7 +4295,7 @@
         <v>37</v>
       </c>
       <c r="F15">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
         <v>38</v>
@@ -4324,7 +4321,7 @@
         <v>37</v>
       </c>
       <c r="F16">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G16" t="s">
         <v>38</v>
@@ -4350,7 +4347,7 @@
         <v>37</v>
       </c>
       <c r="F17">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G17" t="s">
         <v>38</v>
@@ -4376,7 +4373,7 @@
         <v>37</v>
       </c>
       <c r="F18">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G18" t="s">
         <v>38</v>
@@ -4402,7 +4399,7 @@
         <v>37</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
         <v>38</v>
@@ -4428,7 +4425,7 @@
         <v>37</v>
       </c>
       <c r="F20">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G20" t="s">
         <v>38</v>
@@ -4454,7 +4451,7 @@
         <v>37</v>
       </c>
       <c r="F21">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G21" t="s">
         <v>38</v>
@@ -4480,7 +4477,7 @@
         <v>37</v>
       </c>
       <c r="F22">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
         <v>38</v>
@@ -4506,7 +4503,7 @@
         <v>37</v>
       </c>
       <c r="F23">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
         <v>38</v>
@@ -4532,7 +4529,7 @@
         <v>37</v>
       </c>
       <c r="F24">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
         <v>38</v>
@@ -4558,7 +4555,7 @@
         <v>37</v>
       </c>
       <c r="F25">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G25" t="s">
         <v>38</v>
@@ -4584,7 +4581,7 @@
         <v>37</v>
       </c>
       <c r="F26">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G26" t="s">
         <v>38</v>
@@ -4610,7 +4607,7 @@
         <v>37</v>
       </c>
       <c r="F27">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G27" t="s">
         <v>38</v>
@@ -4636,7 +4633,7 @@
         <v>37</v>
       </c>
       <c r="F28">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G28" t="s">
         <v>38</v>
@@ -4662,7 +4659,7 @@
         <v>37</v>
       </c>
       <c r="F29">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s">
         <v>38</v>
@@ -4688,7 +4685,7 @@
         <v>37</v>
       </c>
       <c r="F30">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G30" t="s">
         <v>38</v>
@@ -4714,7 +4711,7 @@
         <v>37</v>
       </c>
       <c r="F31">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G31" t="s">
         <v>38</v>
@@ -4740,7 +4737,7 @@
         <v>37</v>
       </c>
       <c r="F32">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G32" t="s">
         <v>38</v>
@@ -4766,7 +4763,7 @@
         <v>37</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G33" t="s">
         <v>38</v>
@@ -4792,7 +4789,7 @@
         <v>37</v>
       </c>
       <c r="F34">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G34" t="s">
         <v>38</v>
@@ -4818,7 +4815,7 @@
         <v>37</v>
       </c>
       <c r="F35">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G35" t="s">
         <v>38</v>
@@ -4844,7 +4841,7 @@
         <v>37</v>
       </c>
       <c r="F36">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="G36" t="s">
         <v>38</v>
@@ -4870,7 +4867,7 @@
         <v>37</v>
       </c>
       <c r="F37">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G37" t="s">
         <v>38</v>
@@ -4896,7 +4893,7 @@
         <v>37</v>
       </c>
       <c r="F38">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G38" t="s">
         <v>38</v>
@@ -4922,7 +4919,7 @@
         <v>37</v>
       </c>
       <c r="F39">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="G39" t="s">
         <v>38</v>
@@ -4948,7 +4945,7 @@
         <v>37</v>
       </c>
       <c r="F40">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G40" t="s">
         <v>38</v>
@@ -4974,7 +4971,7 @@
         <v>37</v>
       </c>
       <c r="F41">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G41" t="s">
         <v>38</v>
@@ -5000,7 +4997,7 @@
         <v>37</v>
       </c>
       <c r="F42">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G42" t="s">
         <v>38</v>
@@ -5026,7 +5023,7 @@
         <v>37</v>
       </c>
       <c r="F43">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G43" t="s">
         <v>38</v>
@@ -5052,7 +5049,7 @@
         <v>37</v>
       </c>
       <c r="F44">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="G44" t="s">
         <v>38</v>
@@ -5078,7 +5075,7 @@
         <v>37</v>
       </c>
       <c r="F45">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G45" t="s">
         <v>38</v>
@@ -5104,7 +5101,7 @@
         <v>37</v>
       </c>
       <c r="F46">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="G46" t="s">
         <v>38</v>
@@ -5130,7 +5127,7 @@
         <v>37</v>
       </c>
       <c r="F47">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G47" t="s">
         <v>38</v>
@@ -5156,7 +5153,7 @@
         <v>37</v>
       </c>
       <c r="F48">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G48" t="s">
         <v>38</v>
@@ -5182,7 +5179,7 @@
         <v>37</v>
       </c>
       <c r="F49">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="G49" t="s">
         <v>38</v>
@@ -5208,7 +5205,7 @@
         <v>37</v>
       </c>
       <c r="F50">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G50" t="s">
         <v>38</v>
@@ -5234,7 +5231,7 @@
         <v>37</v>
       </c>
       <c r="F51">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G51" t="s">
         <v>38</v>
@@ -5260,7 +5257,7 @@
         <v>37</v>
       </c>
       <c r="F52">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G52" t="s">
         <v>38</v>
@@ -5286,7 +5283,7 @@
         <v>37</v>
       </c>
       <c r="F53">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G53" t="s">
         <v>38</v>
@@ -5312,7 +5309,7 @@
         <v>37</v>
       </c>
       <c r="F54">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G54" t="s">
         <v>38</v>
@@ -5338,7 +5335,7 @@
         <v>37</v>
       </c>
       <c r="F55">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G55" t="s">
         <v>38</v>
@@ -5364,7 +5361,7 @@
         <v>37</v>
       </c>
       <c r="F56">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G56" t="s">
         <v>38</v>
@@ -5390,7 +5387,7 @@
         <v>37</v>
       </c>
       <c r="F57">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="G57" t="s">
         <v>38</v>
@@ -5416,7 +5413,7 @@
         <v>37</v>
       </c>
       <c r="F58">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G58" t="s">
         <v>38</v>
@@ -5442,7 +5439,7 @@
         <v>37</v>
       </c>
       <c r="F59">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G59" t="s">
         <v>38</v>
@@ -5468,7 +5465,7 @@
         <v>37</v>
       </c>
       <c r="F60">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="G60" t="s">
         <v>38</v>
@@ -5494,7 +5491,7 @@
         <v>37</v>
       </c>
       <c r="F61">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
         <v>38</v>
@@ -5520,7 +5517,7 @@
         <v>37</v>
       </c>
       <c r="F62">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G62" t="s">
         <v>38</v>
@@ -5546,7 +5543,7 @@
         <v>37</v>
       </c>
       <c r="F63">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G63" t="s">
         <v>38</v>
@@ -5572,7 +5569,7 @@
         <v>37</v>
       </c>
       <c r="F64">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G64" t="s">
         <v>38</v>
@@ -5598,7 +5595,7 @@
         <v>37</v>
       </c>
       <c r="F65">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="G65" t="s">
         <v>38</v>
@@ -5624,7 +5621,7 @@
         <v>37</v>
       </c>
       <c r="F66">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="G66" t="s">
         <v>38</v>
@@ -5650,7 +5647,7 @@
         <v>37</v>
       </c>
       <c r="F67">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G67" t="s">
         <v>38</v>
@@ -5676,7 +5673,7 @@
         <v>37</v>
       </c>
       <c r="F68">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G68" t="s">
         <v>38</v>
@@ -5702,7 +5699,7 @@
         <v>37</v>
       </c>
       <c r="F69">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G69" t="s">
         <v>38</v>
@@ -5728,7 +5725,7 @@
         <v>37</v>
       </c>
       <c r="F70">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="G70" t="s">
         <v>38</v>
@@ -5754,7 +5751,7 @@
         <v>37</v>
       </c>
       <c r="F71">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G71" t="s">
         <v>38</v>
@@ -5780,7 +5777,7 @@
         <v>37</v>
       </c>
       <c r="F72">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G72" t="s">
         <v>38</v>
@@ -5806,7 +5803,7 @@
         <v>37</v>
       </c>
       <c r="F73">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G73" t="s">
         <v>38</v>
@@ -5832,7 +5829,7 @@
         <v>37</v>
       </c>
       <c r="F74">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G74" t="s">
         <v>38</v>
@@ -5858,7 +5855,7 @@
         <v>37</v>
       </c>
       <c r="F75">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G75" t="s">
         <v>38</v>
@@ -5884,7 +5881,7 @@
         <v>37</v>
       </c>
       <c r="F76">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G76" t="s">
         <v>38</v>
@@ -5910,7 +5907,7 @@
         <v>37</v>
       </c>
       <c r="F77">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="G77" t="s">
         <v>38</v>
@@ -5936,7 +5933,7 @@
         <v>37</v>
       </c>
       <c r="F78">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="G78" t="s">
         <v>38</v>
@@ -5962,7 +5959,7 @@
         <v>37</v>
       </c>
       <c r="F79">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G79" t="s">
         <v>38</v>
@@ -5988,7 +5985,7 @@
         <v>37</v>
       </c>
       <c r="F80">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G80" t="s">
         <v>38</v>
@@ -6014,7 +6011,7 @@
         <v>37</v>
       </c>
       <c r="F81">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G81" t="s">
         <v>38</v>
@@ -6066,7 +6063,7 @@
         <v>37</v>
       </c>
       <c r="F83">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G83" t="s">
         <v>38</v>
@@ -6092,7 +6089,7 @@
         <v>37</v>
       </c>
       <c r="F84">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G84" t="s">
         <v>38</v>
@@ -6118,7 +6115,7 @@
         <v>37</v>
       </c>
       <c r="F85">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G85" t="s">
         <v>38</v>
@@ -6144,7 +6141,7 @@
         <v>37</v>
       </c>
       <c r="F86">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G86" t="s">
         <v>38</v>
@@ -6170,7 +6167,7 @@
         <v>37</v>
       </c>
       <c r="F87">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G87" t="s">
         <v>38</v>
@@ -6196,7 +6193,7 @@
         <v>37</v>
       </c>
       <c r="F88">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G88" t="s">
         <v>38</v>
@@ -6222,7 +6219,7 @@
         <v>37</v>
       </c>
       <c r="F89">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G89" t="s">
         <v>38</v>
@@ -6248,7 +6245,7 @@
         <v>37</v>
       </c>
       <c r="F90">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G90" t="s">
         <v>38</v>
@@ -6274,7 +6271,7 @@
         <v>37</v>
       </c>
       <c r="F91">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G91" t="s">
         <v>38</v>
@@ -6300,7 +6297,7 @@
         <v>37</v>
       </c>
       <c r="F92">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="G92" t="s">
         <v>38</v>
@@ -6326,7 +6323,7 @@
         <v>37</v>
       </c>
       <c r="F93">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G93" t="s">
         <v>38</v>
@@ -6352,7 +6349,7 @@
         <v>37</v>
       </c>
       <c r="F94">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G94" t="s">
         <v>38</v>
@@ -6378,7 +6375,7 @@
         <v>37</v>
       </c>
       <c r="F95">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G95" t="s">
         <v>38</v>
@@ -6404,7 +6401,7 @@
         <v>37</v>
       </c>
       <c r="F96">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="G96" t="s">
         <v>38</v>
@@ -6430,7 +6427,7 @@
         <v>37</v>
       </c>
       <c r="F97">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G97" t="s">
         <v>38</v>
@@ -6456,7 +6453,7 @@
         <v>37</v>
       </c>
       <c r="F98">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="G98" t="s">
         <v>38</v>
@@ -6482,7 +6479,7 @@
         <v>37</v>
       </c>
       <c r="F99">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G99" t="s">
         <v>38</v>
@@ -6508,7 +6505,7 @@
         <v>37</v>
       </c>
       <c r="F100">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G100" t="s">
         <v>38</v>
@@ -6534,7 +6531,7 @@
         <v>37</v>
       </c>
       <c r="F101">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G101" t="s">
         <v>38</v>
@@ -6560,7 +6557,7 @@
         <v>37</v>
       </c>
       <c r="F102">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G102" t="s">
         <v>38</v>
@@ -6586,7 +6583,7 @@
         <v>37</v>
       </c>
       <c r="F103">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="G103" t="s">
         <v>38</v>
@@ -6612,7 +6609,7 @@
         <v>37</v>
       </c>
       <c r="F104">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="G104" t="s">
         <v>38</v>
@@ -6638,7 +6635,7 @@
         <v>37</v>
       </c>
       <c r="F105">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G105" t="s">
         <v>38</v>
@@ -6664,7 +6661,7 @@
         <v>37</v>
       </c>
       <c r="F106">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G106" t="s">
         <v>38</v>
@@ -6690,7 +6687,7 @@
         <v>37</v>
       </c>
       <c r="F107">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="G107" t="s">
         <v>38</v>
@@ -6716,7 +6713,7 @@
         <v>37</v>
       </c>
       <c r="F108">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G108" t="s">
         <v>38</v>
@@ -6742,7 +6739,7 @@
         <v>37</v>
       </c>
       <c r="F109">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G109" t="s">
         <v>38</v>
@@ -6768,7 +6765,7 @@
         <v>37</v>
       </c>
       <c r="F110">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G110" t="s">
         <v>38</v>
@@ -6794,7 +6791,7 @@
         <v>37</v>
       </c>
       <c r="F111">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G111" t="s">
         <v>38</v>
@@ -6820,7 +6817,7 @@
         <v>37</v>
       </c>
       <c r="F112">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="G112" t="s">
         <v>38</v>
@@ -6846,7 +6843,7 @@
         <v>37</v>
       </c>
       <c r="F113">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G113" t="s">
         <v>38</v>
@@ -6872,7 +6869,7 @@
         <v>37</v>
       </c>
       <c r="F114">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G114" t="s">
         <v>38</v>
@@ -6898,7 +6895,7 @@
         <v>37</v>
       </c>
       <c r="F115">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G115" t="s">
         <v>38</v>
@@ -6924,7 +6921,7 @@
         <v>37</v>
       </c>
       <c r="F116">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="G116" t="s">
         <v>38</v>
@@ -6950,7 +6947,7 @@
         <v>37</v>
       </c>
       <c r="F117">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="G117" t="s">
         <v>38</v>
@@ -6976,7 +6973,7 @@
         <v>37</v>
       </c>
       <c r="F118">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G118" t="s">
         <v>38</v>
@@ -7002,7 +6999,7 @@
         <v>37</v>
       </c>
       <c r="F119">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="G119" t="s">
         <v>38</v>
@@ -7028,7 +7025,7 @@
         <v>37</v>
       </c>
       <c r="F120">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="G120" t="s">
         <v>38</v>
@@ -7054,7 +7051,7 @@
         <v>37</v>
       </c>
       <c r="F121">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G121" t="s">
         <v>38</v>
@@ -7080,7 +7077,7 @@
         <v>37</v>
       </c>
       <c r="F122">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="G122" t="s">
         <v>38</v>
@@ -7106,7 +7103,7 @@
         <v>37</v>
       </c>
       <c r="F123">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G123" t="s">
         <v>38</v>
@@ -7132,7 +7129,7 @@
         <v>37</v>
       </c>
       <c r="F124">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G124" t="s">
         <v>38</v>
@@ -7158,7 +7155,7 @@
         <v>37</v>
       </c>
       <c r="F125">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="G125" t="s">
         <v>38</v>
@@ -7184,7 +7181,7 @@
         <v>37</v>
       </c>
       <c r="F126">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G126" t="s">
         <v>38</v>
@@ -7210,7 +7207,7 @@
         <v>37</v>
       </c>
       <c r="F127">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G127" t="s">
         <v>38</v>
@@ -7236,7 +7233,7 @@
         <v>37</v>
       </c>
       <c r="F128">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G128" t="s">
         <v>38</v>
@@ -7262,7 +7259,7 @@
         <v>37</v>
       </c>
       <c r="F129">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G129" t="s">
         <v>38</v>
@@ -7288,7 +7285,7 @@
         <v>37</v>
       </c>
       <c r="F130">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="G130" t="s">
         <v>38</v>
@@ -7314,7 +7311,7 @@
         <v>37</v>
       </c>
       <c r="F131">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="G131" t="s">
         <v>38</v>
@@ -7340,7 +7337,7 @@
         <v>37</v>
       </c>
       <c r="F132">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G132" t="s">
         <v>38</v>
@@ -7366,7 +7363,7 @@
         <v>37</v>
       </c>
       <c r="F133">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="G133" t="s">
         <v>38</v>
@@ -7418,7 +7415,7 @@
         <v>37</v>
       </c>
       <c r="F135">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G135" t="s">
         <v>38</v>
@@ -7444,7 +7441,7 @@
         <v>37</v>
       </c>
       <c r="F136">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G136" t="s">
         <v>38</v>
@@ -7470,7 +7467,7 @@
         <v>37</v>
       </c>
       <c r="F137">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G137" t="s">
         <v>38</v>
@@ -7496,7 +7493,7 @@
         <v>37</v>
       </c>
       <c r="F138">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G138" t="s">
         <v>38</v>
@@ -7522,7 +7519,7 @@
         <v>37</v>
       </c>
       <c r="F139">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G139" t="s">
         <v>38</v>
@@ -7548,7 +7545,7 @@
         <v>37</v>
       </c>
       <c r="F140">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G140" t="s">
         <v>38</v>
@@ -7574,7 +7571,7 @@
         <v>37</v>
       </c>
       <c r="F141">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G141" t="s">
         <v>38</v>
@@ -7600,7 +7597,7 @@
         <v>37</v>
       </c>
       <c r="F142">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G142" t="s">
         <v>38</v>
@@ -7626,7 +7623,7 @@
         <v>37</v>
       </c>
       <c r="F143">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G143" t="s">
         <v>38</v>
@@ -7652,7 +7649,7 @@
         <v>37</v>
       </c>
       <c r="F144">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G144" t="s">
         <v>38</v>
@@ -7678,7 +7675,7 @@
         <v>37</v>
       </c>
       <c r="F145">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G145" t="s">
         <v>38</v>
@@ -7704,7 +7701,7 @@
         <v>37</v>
       </c>
       <c r="F146">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G146" t="s">
         <v>38</v>
@@ -7730,7 +7727,7 @@
         <v>37</v>
       </c>
       <c r="F147">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G147" t="s">
         <v>38</v>
@@ -7756,7 +7753,7 @@
         <v>37</v>
       </c>
       <c r="F148">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G148" t="s">
         <v>38</v>
@@ -7782,7 +7779,7 @@
         <v>37</v>
       </c>
       <c r="F149">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G149" t="s">
         <v>38</v>
@@ -7808,7 +7805,7 @@
         <v>37</v>
       </c>
       <c r="F150">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="G150" t="s">
         <v>38</v>
@@ -7834,7 +7831,7 @@
         <v>37</v>
       </c>
       <c r="F151">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G151" t="s">
         <v>38</v>
@@ -7860,7 +7857,7 @@
         <v>37</v>
       </c>
       <c r="F152">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G152" t="s">
         <v>38</v>
@@ -7886,7 +7883,7 @@
         <v>37</v>
       </c>
       <c r="F153">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G153" t="s">
         <v>38</v>
@@ -7912,7 +7909,7 @@
         <v>37</v>
       </c>
       <c r="F154">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G154" t="s">
         <v>38</v>
@@ -7938,7 +7935,7 @@
         <v>37</v>
       </c>
       <c r="F155">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G155" t="s">
         <v>38</v>
@@ -7964,7 +7961,7 @@
         <v>37</v>
       </c>
       <c r="F156">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="G156" t="s">
         <v>38</v>
@@ -7990,7 +7987,7 @@
         <v>37</v>
       </c>
       <c r="F157">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="G157" t="s">
         <v>38</v>
@@ -8016,7 +8013,7 @@
         <v>37</v>
       </c>
       <c r="F158">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="G158" t="s">
         <v>38</v>
@@ -8042,7 +8039,7 @@
         <v>37</v>
       </c>
       <c r="F159">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G159" t="s">
         <v>38</v>
@@ -8068,7 +8065,7 @@
         <v>37</v>
       </c>
       <c r="F160">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G160" t="s">
         <v>38</v>
@@ -8094,7 +8091,7 @@
         <v>37</v>
       </c>
       <c r="F161">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G161" t="s">
         <v>38</v>
@@ -8120,7 +8117,7 @@
         <v>37</v>
       </c>
       <c r="F162">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="G162" t="s">
         <v>38</v>
@@ -8146,7 +8143,7 @@
         <v>37</v>
       </c>
       <c r="F163">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G163" t="s">
         <v>38</v>
@@ -8172,7 +8169,7 @@
         <v>37</v>
       </c>
       <c r="F164">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G164" t="s">
         <v>38</v>
@@ -8198,7 +8195,7 @@
         <v>37</v>
       </c>
       <c r="F165">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G165" t="s">
         <v>38</v>
@@ -8224,7 +8221,7 @@
         <v>37</v>
       </c>
       <c r="F166">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="G166" t="s">
         <v>38</v>
@@ -8250,7 +8247,7 @@
         <v>37</v>
       </c>
       <c r="F167">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G167" t="s">
         <v>38</v>
@@ -8276,7 +8273,7 @@
         <v>37</v>
       </c>
       <c r="F168">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="G168" t="s">
         <v>38</v>
@@ -8302,7 +8299,7 @@
         <v>37</v>
       </c>
       <c r="F169">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G169" t="s">
         <v>38</v>
@@ -8328,7 +8325,7 @@
         <v>37</v>
       </c>
       <c r="F170">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G170" t="s">
         <v>38</v>
@@ -8354,7 +8351,7 @@
         <v>37</v>
       </c>
       <c r="F171">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="G171" t="s">
         <v>38</v>
@@ -8406,7 +8403,7 @@
         <v>37</v>
       </c>
       <c r="F173">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G173" t="s">
         <v>38</v>
@@ -8432,7 +8429,7 @@
         <v>37</v>
       </c>
       <c r="F174">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G174" t="s">
         <v>38</v>
@@ -8458,7 +8455,7 @@
         <v>37</v>
       </c>
       <c r="F175">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G175" t="s">
         <v>38</v>
@@ -8484,7 +8481,7 @@
         <v>37</v>
       </c>
       <c r="F176">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G176" t="s">
         <v>38</v>
@@ -8510,7 +8507,7 @@
         <v>37</v>
       </c>
       <c r="F177">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G177" t="s">
         <v>38</v>
@@ -8536,7 +8533,7 @@
         <v>37</v>
       </c>
       <c r="F178">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="G178" t="s">
         <v>38</v>
@@ -8562,7 +8559,7 @@
         <v>37</v>
       </c>
       <c r="F179">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G179" t="s">
         <v>38</v>
@@ -8588,7 +8585,7 @@
         <v>37</v>
       </c>
       <c r="F180">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G180" t="s">
         <v>38</v>
@@ -8614,7 +8611,7 @@
         <v>37</v>
       </c>
       <c r="F181">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G181" t="s">
         <v>38</v>
@@ -8640,7 +8637,7 @@
         <v>37</v>
       </c>
       <c r="F182">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G182" t="s">
         <v>38</v>
@@ -8666,7 +8663,7 @@
         <v>37</v>
       </c>
       <c r="F183">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G183" t="s">
         <v>38</v>
@@ -8692,7 +8689,7 @@
         <v>37</v>
       </c>
       <c r="F184">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G184" t="s">
         <v>38</v>
@@ -8718,7 +8715,7 @@
         <v>37</v>
       </c>
       <c r="F185">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G185" t="s">
         <v>38</v>
@@ -8744,7 +8741,7 @@
         <v>37</v>
       </c>
       <c r="F186">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G186" t="s">
         <v>38</v>
@@ -8770,7 +8767,7 @@
         <v>37</v>
       </c>
       <c r="F187">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G187" t="s">
         <v>38</v>
@@ -8796,7 +8793,7 @@
         <v>37</v>
       </c>
       <c r="F188">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G188" t="s">
         <v>38</v>
@@ -8822,7 +8819,7 @@
         <v>37</v>
       </c>
       <c r="F189">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G189" t="s">
         <v>38</v>
@@ -8848,7 +8845,7 @@
         <v>37</v>
       </c>
       <c r="F190">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="G190" t="s">
         <v>38</v>
@@ -8874,7 +8871,7 @@
         <v>37</v>
       </c>
       <c r="F191">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G191" t="s">
         <v>38</v>
@@ -8900,7 +8897,7 @@
         <v>37</v>
       </c>
       <c r="F192">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G192" t="s">
         <v>38</v>
@@ -8926,7 +8923,7 @@
         <v>37</v>
       </c>
       <c r="F193">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G193" t="s">
         <v>38</v>
@@ -8952,7 +8949,7 @@
         <v>37</v>
       </c>
       <c r="F194">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G194" t="s">
         <v>38</v>
@@ -8978,7 +8975,7 @@
         <v>37</v>
       </c>
       <c r="F195">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="G195" t="s">
         <v>38</v>
@@ -9004,7 +9001,7 @@
         <v>37</v>
       </c>
       <c r="F196">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G196" t="s">
         <v>38</v>
@@ -9030,7 +9027,7 @@
         <v>37</v>
       </c>
       <c r="F197">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G197" t="s">
         <v>38</v>
@@ -9056,7 +9053,7 @@
         <v>37</v>
       </c>
       <c r="F198">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G198" t="s">
         <v>38</v>
@@ -9082,7 +9079,7 @@
         <v>37</v>
       </c>
       <c r="F199">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="G199" t="s">
         <v>38</v>
@@ -9108,7 +9105,7 @@
         <v>37</v>
       </c>
       <c r="F200">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G200" t="s">
         <v>38</v>
@@ -9134,7 +9131,7 @@
         <v>37</v>
       </c>
       <c r="F201">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G201" t="s">
         <v>38</v>
@@ -9160,7 +9157,7 @@
         <v>37</v>
       </c>
       <c r="F202">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G202" t="s">
         <v>38</v>
@@ -9186,7 +9183,7 @@
         <v>37</v>
       </c>
       <c r="F203">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G203" t="s">
         <v>38</v>
@@ -9212,7 +9209,7 @@
         <v>37</v>
       </c>
       <c r="F204">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="G204" t="s">
         <v>38</v>
@@ -9238,7 +9235,7 @@
         <v>37</v>
       </c>
       <c r="F205">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="G205" t="s">
         <v>38</v>
@@ -9264,7 +9261,7 @@
         <v>37</v>
       </c>
       <c r="F206">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="G206" t="s">
         <v>38</v>
@@ -9290,7 +9287,7 @@
         <v>37</v>
       </c>
       <c r="F207">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G207" t="s">
         <v>38</v>
@@ -9316,7 +9313,7 @@
         <v>37</v>
       </c>
       <c r="F208">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="G208" t="s">
         <v>38</v>
@@ -9342,7 +9339,7 @@
         <v>37</v>
       </c>
       <c r="F209">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G209" t="s">
         <v>38</v>
@@ -9368,7 +9365,7 @@
         <v>37</v>
       </c>
       <c r="F210">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G210" t="s">
         <v>38</v>
@@ -9394,7 +9391,7 @@
         <v>37</v>
       </c>
       <c r="F211">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G211" t="s">
         <v>38</v>
@@ -9420,7 +9417,7 @@
         <v>37</v>
       </c>
       <c r="F212">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G212" t="s">
         <v>38</v>
@@ -9446,7 +9443,7 @@
         <v>37</v>
       </c>
       <c r="F213">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G213" t="s">
         <v>38</v>
@@ -9472,7 +9469,7 @@
         <v>37</v>
       </c>
       <c r="F214">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G214" t="s">
         <v>38</v>
@@ -9498,7 +9495,7 @@
         <v>37</v>
       </c>
       <c r="F215">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G215" t="s">
         <v>38</v>
@@ -9524,7 +9521,7 @@
         <v>37</v>
       </c>
       <c r="F216">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G216" t="s">
         <v>38</v>
@@ -9576,7 +9573,7 @@
         <v>37</v>
       </c>
       <c r="F218">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G218" t="s">
         <v>38</v>
@@ -9602,7 +9599,7 @@
         <v>37</v>
       </c>
       <c r="F219">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G219" t="s">
         <v>38</v>
@@ -9628,7 +9625,7 @@
         <v>37</v>
       </c>
       <c r="F220">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G220" t="s">
         <v>38</v>
@@ -9654,7 +9651,7 @@
         <v>37</v>
       </c>
       <c r="F221">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="G221" t="s">
         <v>38</v>
@@ -9680,7 +9677,7 @@
         <v>37</v>
       </c>
       <c r="F222">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G222" t="s">
         <v>38</v>
@@ -9706,7 +9703,7 @@
         <v>37</v>
       </c>
       <c r="F223">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G223" t="s">
         <v>38</v>
@@ -9732,7 +9729,7 @@
         <v>37</v>
       </c>
       <c r="F224">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G224" t="s">
         <v>38</v>
@@ -9758,7 +9755,7 @@
         <v>37</v>
       </c>
       <c r="F225">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G225" t="s">
         <v>38</v>
@@ -9784,7 +9781,7 @@
         <v>37</v>
       </c>
       <c r="F226">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G226" t="s">
         <v>38</v>
@@ -9810,7 +9807,7 @@
         <v>37</v>
       </c>
       <c r="F227">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="G227" t="s">
         <v>38</v>
@@ -9836,7 +9833,7 @@
         <v>37</v>
       </c>
       <c r="F228">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G228" t="s">
         <v>38</v>
@@ -9862,7 +9859,7 @@
         <v>37</v>
       </c>
       <c r="F229">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="G229" t="s">
         <v>38</v>
@@ -9888,7 +9885,7 @@
         <v>37</v>
       </c>
       <c r="F230">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="G230" t="s">
         <v>38</v>
@@ -9914,7 +9911,7 @@
         <v>37</v>
       </c>
       <c r="F231">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G231" t="s">
         <v>38</v>
@@ -9940,7 +9937,7 @@
         <v>37</v>
       </c>
       <c r="F232">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G232" t="s">
         <v>38</v>
@@ -9966,7 +9963,7 @@
         <v>37</v>
       </c>
       <c r="F233">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G233" t="s">
         <v>38</v>
@@ -9992,7 +9989,7 @@
         <v>37</v>
       </c>
       <c r="F234">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G234" t="s">
         <v>38</v>
@@ -10018,7 +10015,7 @@
         <v>37</v>
       </c>
       <c r="F235">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G235" t="s">
         <v>38</v>
@@ -10044,7 +10041,7 @@
         <v>37</v>
       </c>
       <c r="F236">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G236" t="s">
         <v>38</v>
@@ -10070,7 +10067,7 @@
         <v>37</v>
       </c>
       <c r="F237">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G237" t="s">
         <v>38</v>
@@ -10096,7 +10093,7 @@
         <v>37</v>
       </c>
       <c r="F238">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="G238" t="s">
         <v>38</v>
@@ -10122,7 +10119,7 @@
         <v>37</v>
       </c>
       <c r="F239">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="G239" t="s">
         <v>38</v>
@@ -10148,7 +10145,7 @@
         <v>37</v>
       </c>
       <c r="F240">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G240" t="s">
         <v>38</v>
@@ -10174,7 +10171,7 @@
         <v>37</v>
       </c>
       <c r="F241">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G241" t="s">
         <v>38</v>
@@ -10200,7 +10197,7 @@
         <v>37</v>
       </c>
       <c r="F242">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G242" t="s">
         <v>38</v>
@@ -10226,7 +10223,7 @@
         <v>37</v>
       </c>
       <c r="F243">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G243" t="s">
         <v>38</v>
@@ -10252,7 +10249,7 @@
         <v>37</v>
       </c>
       <c r="F244">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G244" t="s">
         <v>38</v>
@@ -10278,7 +10275,7 @@
         <v>37</v>
       </c>
       <c r="F245">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G245" t="s">
         <v>38</v>
@@ -10304,7 +10301,7 @@
         <v>37</v>
       </c>
       <c r="F246">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G246" t="s">
         <v>38</v>
@@ -10330,7 +10327,7 @@
         <v>37</v>
       </c>
       <c r="F247">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="G247" t="s">
         <v>38</v>
@@ -10356,7 +10353,7 @@
         <v>37</v>
       </c>
       <c r="F248">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G248" t="s">
         <v>38</v>
@@ -10382,7 +10379,7 @@
         <v>37</v>
       </c>
       <c r="F249">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G249" t="s">
         <v>38</v>
@@ -10408,7 +10405,7 @@
         <v>37</v>
       </c>
       <c r="F250">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G250" t="s">
         <v>38</v>
@@ -10434,7 +10431,7 @@
         <v>37</v>
       </c>
       <c r="F251">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G251" t="s">
         <v>38</v>
@@ -10460,7 +10457,7 @@
         <v>37</v>
       </c>
       <c r="F252">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G252" t="s">
         <v>38</v>
@@ -10486,7 +10483,7 @@
         <v>37</v>
       </c>
       <c r="F253">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G253" t="s">
         <v>38</v>
@@ -10512,7 +10509,7 @@
         <v>37</v>
       </c>
       <c r="F254">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G254" t="s">
         <v>38</v>
@@ -10538,7 +10535,7 @@
         <v>37</v>
       </c>
       <c r="F255">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G255" t="s">
         <v>38</v>
@@ -10564,7 +10561,7 @@
         <v>37</v>
       </c>
       <c r="F256">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G256" t="s">
         <v>38</v>
@@ -10590,7 +10587,7 @@
         <v>37</v>
       </c>
       <c r="F257">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G257" t="s">
         <v>38</v>
@@ -10616,7 +10613,7 @@
         <v>37</v>
       </c>
       <c r="F258">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G258" t="s">
         <v>38</v>
@@ -10642,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="F259">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G259" t="s">
         <v>38</v>
@@ -10668,7 +10665,7 @@
         <v>37</v>
       </c>
       <c r="F260">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G260" t="s">
         <v>38</v>
@@ -10694,7 +10691,7 @@
         <v>37</v>
       </c>
       <c r="F261">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G261" t="s">
         <v>38</v>
@@ -10720,7 +10717,7 @@
         <v>37</v>
       </c>
       <c r="F262">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G262" t="s">
         <v>38</v>
@@ -10746,7 +10743,7 @@
         <v>37</v>
       </c>
       <c r="F263">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G263" t="s">
         <v>38</v>
@@ -10772,7 +10769,7 @@
         <v>37</v>
       </c>
       <c r="F264">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="G264" t="s">
         <v>38</v>
@@ -10798,7 +10795,7 @@
         <v>37</v>
       </c>
       <c r="F265">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="G265" t="s">
         <v>38</v>
@@ -10824,7 +10821,7 @@
         <v>37</v>
       </c>
       <c r="F266">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G266" t="s">
         <v>38</v>
@@ -10850,7 +10847,7 @@
         <v>37</v>
       </c>
       <c r="F267">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G267" t="s">
         <v>38</v>
@@ -10876,7 +10873,7 @@
         <v>37</v>
       </c>
       <c r="F268">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G268" t="s">
         <v>38</v>
@@ -10902,7 +10899,7 @@
         <v>37</v>
       </c>
       <c r="F269">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G269" t="s">
         <v>38</v>
@@ -10928,7 +10925,7 @@
         <v>37</v>
       </c>
       <c r="F270">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G270" t="s">
         <v>38</v>
@@ -10954,7 +10951,7 @@
         <v>37</v>
       </c>
       <c r="F271">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G271" t="s">
         <v>38</v>
@@ -10980,7 +10977,7 @@
         <v>37</v>
       </c>
       <c r="F272">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G272" t="s">
         <v>38</v>
@@ -11006,7 +11003,7 @@
         <v>37</v>
       </c>
       <c r="F273">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G273" t="s">
         <v>38</v>
@@ -11032,7 +11029,7 @@
         <v>37</v>
       </c>
       <c r="F274">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G274" t="s">
         <v>38</v>
@@ -11058,7 +11055,7 @@
         <v>37</v>
       </c>
       <c r="F275">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G275" t="s">
         <v>38</v>
@@ -11084,7 +11081,7 @@
         <v>37</v>
       </c>
       <c r="F276">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G276" t="s">
         <v>38</v>
@@ -11110,7 +11107,7 @@
         <v>37</v>
       </c>
       <c r="F277">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G277" t="s">
         <v>38</v>
@@ -11136,7 +11133,7 @@
         <v>37</v>
       </c>
       <c r="F278">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G278" t="s">
         <v>38</v>
@@ -11162,7 +11159,7 @@
         <v>37</v>
       </c>
       <c r="F279">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G279" t="s">
         <v>38</v>
@@ -11188,7 +11185,7 @@
         <v>37</v>
       </c>
       <c r="F280">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G280" t="s">
         <v>38</v>
@@ -11214,7 +11211,7 @@
         <v>37</v>
       </c>
       <c r="F281">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="G281" t="s">
         <v>38</v>
@@ -11240,7 +11237,7 @@
         <v>37</v>
       </c>
       <c r="F282">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G282" t="s">
         <v>38</v>
@@ -11266,7 +11263,7 @@
         <v>37</v>
       </c>
       <c r="F283">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G283" t="s">
         <v>38</v>
@@ -11292,7 +11289,7 @@
         <v>37</v>
       </c>
       <c r="F284">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G284" t="s">
         <v>38</v>
@@ -11318,7 +11315,7 @@
         <v>37</v>
       </c>
       <c r="F285">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G285" t="s">
         <v>38</v>
@@ -11344,7 +11341,7 @@
         <v>37</v>
       </c>
       <c r="F286">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G286" t="s">
         <v>38</v>
@@ -11370,7 +11367,7 @@
         <v>37</v>
       </c>
       <c r="F287">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G287" t="s">
         <v>38</v>
@@ -11396,7 +11393,7 @@
         <v>37</v>
       </c>
       <c r="F288">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G288" t="s">
         <v>38</v>
@@ -11422,7 +11419,7 @@
         <v>37</v>
       </c>
       <c r="F289">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="G289" t="s">
         <v>38</v>
@@ -11448,7 +11445,7 @@
         <v>37</v>
       </c>
       <c r="F290">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G290" t="s">
         <v>38</v>
@@ -11474,7 +11471,7 @@
         <v>37</v>
       </c>
       <c r="F291">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G291" t="s">
         <v>38</v>
@@ -11500,7 +11497,7 @@
         <v>37</v>
       </c>
       <c r="F292">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="G292" t="s">
         <v>38</v>
@@ -11526,7 +11523,7 @@
         <v>37</v>
       </c>
       <c r="F293">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G293" t="s">
         <v>38</v>
@@ -11552,7 +11549,7 @@
         <v>37</v>
       </c>
       <c r="F294">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G294" t="s">
         <v>38</v>
@@ -11578,7 +11575,7 @@
         <v>37</v>
       </c>
       <c r="F295">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G295" t="s">
         <v>38</v>
@@ -11604,7 +11601,7 @@
         <v>37</v>
       </c>
       <c r="F296">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G296" t="s">
         <v>38</v>
@@ -11630,7 +11627,7 @@
         <v>37</v>
       </c>
       <c r="F297">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G297" t="s">
         <v>38</v>
@@ -11656,7 +11653,7 @@
         <v>37</v>
       </c>
       <c r="F298">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G298" t="s">
         <v>38</v>
@@ -11682,7 +11679,7 @@
         <v>37</v>
       </c>
       <c r="F299">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G299" t="s">
         <v>38</v>
@@ -11708,7 +11705,7 @@
         <v>37</v>
       </c>
       <c r="F300">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G300" t="s">
         <v>38</v>
@@ -11734,7 +11731,7 @@
         <v>37</v>
       </c>
       <c r="F301">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G301" t="s">
         <v>38</v>
@@ -11760,7 +11757,7 @@
         <v>37</v>
       </c>
       <c r="F302">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G302" t="s">
         <v>38</v>
@@ -11786,7 +11783,7 @@
         <v>37</v>
       </c>
       <c r="F303">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G303" t="s">
         <v>38</v>
@@ -11812,7 +11809,7 @@
         <v>37</v>
       </c>
       <c r="F304">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G304" t="s">
         <v>38</v>
@@ -11838,7 +11835,7 @@
         <v>37</v>
       </c>
       <c r="F305">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G305" t="s">
         <v>38</v>
@@ -11864,7 +11861,7 @@
         <v>37</v>
       </c>
       <c r="F306">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G306" t="s">
         <v>38</v>
@@ -11890,7 +11887,7 @@
         <v>37</v>
       </c>
       <c r="F307">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G307" t="s">
         <v>38</v>
@@ -11916,7 +11913,7 @@
         <v>37</v>
       </c>
       <c r="F308">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G308" t="s">
         <v>38</v>
@@ -11942,7 +11939,7 @@
         <v>37</v>
       </c>
       <c r="F309">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G309" t="s">
         <v>38</v>
@@ -11968,7 +11965,7 @@
         <v>37</v>
       </c>
       <c r="F310">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="G310" t="s">
         <v>38</v>
@@ -11994,7 +11991,7 @@
         <v>37</v>
       </c>
       <c r="F311">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G311" t="s">
         <v>38</v>
@@ -12020,7 +12017,7 @@
         <v>37</v>
       </c>
       <c r="F312">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G312" t="s">
         <v>38</v>
@@ -12046,7 +12043,7 @@
         <v>37</v>
       </c>
       <c r="F313">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G313" t="s">
         <v>38</v>
@@ -12072,7 +12069,7 @@
         <v>37</v>
       </c>
       <c r="F314">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G314" t="s">
         <v>38</v>
@@ -12098,7 +12095,7 @@
         <v>37</v>
       </c>
       <c r="F315">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="G315" t="s">
         <v>38</v>
@@ -12124,7 +12121,7 @@
         <v>37</v>
       </c>
       <c r="F316">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="G316" t="s">
         <v>38</v>
@@ -12150,7 +12147,7 @@
         <v>37</v>
       </c>
       <c r="F317">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G317" t="s">
         <v>38</v>
@@ -12176,7 +12173,7 @@
         <v>37</v>
       </c>
       <c r="F318">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G318" t="s">
         <v>38</v>
@@ -12202,7 +12199,7 @@
         <v>37</v>
       </c>
       <c r="F319">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G319" t="s">
         <v>38</v>
@@ -12228,7 +12225,7 @@
         <v>37</v>
       </c>
       <c r="F320">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G320" t="s">
         <v>38</v>
@@ -12254,7 +12251,7 @@
         <v>37</v>
       </c>
       <c r="F321">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G321" t="s">
         <v>38</v>
@@ -12280,7 +12277,7 @@
         <v>37</v>
       </c>
       <c r="F322">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G322" t="s">
         <v>38</v>
@@ -12306,7 +12303,7 @@
         <v>37</v>
       </c>
       <c r="F323">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G323" t="s">
         <v>38</v>
@@ -12332,7 +12329,7 @@
         <v>37</v>
       </c>
       <c r="F324">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G324" t="s">
         <v>38</v>
@@ -12358,7 +12355,7 @@
         <v>37</v>
       </c>
       <c r="F325">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G325" t="s">
         <v>38</v>
@@ -12384,7 +12381,7 @@
         <v>37</v>
       </c>
       <c r="F326">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G326" t="s">
         <v>38</v>
@@ -12410,7 +12407,7 @@
         <v>37</v>
       </c>
       <c r="F327">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G327" t="s">
         <v>38</v>
@@ -12436,7 +12433,7 @@
         <v>37</v>
       </c>
       <c r="F328">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G328" t="s">
         <v>38</v>
@@ -12462,7 +12459,7 @@
         <v>37</v>
       </c>
       <c r="F329">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G329" t="s">
         <v>38</v>
@@ -12488,7 +12485,7 @@
         <v>37</v>
       </c>
       <c r="F330">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G330" t="s">
         <v>38</v>
@@ -12514,7 +12511,7 @@
         <v>37</v>
       </c>
       <c r="F331">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G331" t="s">
         <v>38</v>
@@ -12540,10 +12537,10 @@
         <v>37</v>
       </c>
       <c r="F332">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G332" t="s">
-        <v>702</v>
+        <v>38</v>
       </c>
       <c r="H332" t="s">
         <v>13</v>
@@ -12551,13 +12548,13 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B333" t="s">
         <v>23</v>
       </c>
       <c r="C333" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D333" t="s">
         <v>139</v>
@@ -12566,10 +12563,10 @@
         <v>37</v>
       </c>
       <c r="F333">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G333" t="s">
-        <v>702</v>
+        <v>38</v>
       </c>
       <c r="H333" t="s">
         <v>13</v>
@@ -12577,13 +12574,13 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B334" t="s">
         <v>23</v>
       </c>
       <c r="C334" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D334" t="s">
         <v>139</v>
@@ -12592,10 +12589,10 @@
         <v>37</v>
       </c>
       <c r="F334">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G334" t="s">
-        <v>702</v>
+        <v>38</v>
       </c>
       <c r="H334" t="s">
         <v>13</v>
@@ -12603,13 +12600,13 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B335" t="s">
         <v>23</v>
       </c>
       <c r="C335" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D335" t="s">
         <v>139</v>
@@ -12618,10 +12615,10 @@
         <v>37</v>
       </c>
       <c r="F335">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G335" t="s">
-        <v>702</v>
+        <v>38</v>
       </c>
       <c r="H335" t="s">
         <v>13</v>
@@ -12629,13 +12626,13 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B336" t="s">
         <v>23</v>
       </c>
       <c r="C336" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D336" t="s">
         <v>139</v>
@@ -12644,10 +12641,10 @@
         <v>37</v>
       </c>
       <c r="F336">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G336" t="s">
-        <v>702</v>
+        <v>38</v>
       </c>
       <c r="H336" t="s">
         <v>13</v>
@@ -12655,13 +12652,13 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B337" t="s">
         <v>23</v>
       </c>
       <c r="C337" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D337" t="s">
         <v>139</v>
@@ -12670,10 +12667,10 @@
         <v>37</v>
       </c>
       <c r="F337">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G337" t="s">
-        <v>702</v>
+        <v>38</v>
       </c>
       <c r="H337" t="s">
         <v>13</v>
@@ -12681,13 +12678,13 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B338" t="s">
         <v>23</v>
       </c>
       <c r="C338" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D338" t="s">
         <v>139</v>
@@ -12696,10 +12693,10 @@
         <v>37</v>
       </c>
       <c r="F338">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G338" t="s">
-        <v>702</v>
+        <v>38</v>
       </c>
       <c r="H338" t="s">
         <v>13</v>
@@ -12707,13 +12704,13 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B339" t="s">
         <v>23</v>
       </c>
       <c r="C339" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D339" t="s">
         <v>139</v>
@@ -12722,10 +12719,10 @@
         <v>37</v>
       </c>
       <c r="F339">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G339" t="s">
-        <v>702</v>
+        <v>38</v>
       </c>
       <c r="H339" t="s">
         <v>13</v>
@@ -12733,13 +12730,13 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B340" t="s">
         <v>23</v>
       </c>
       <c r="C340" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D340" t="s">
         <v>139</v>
@@ -12748,10 +12745,10 @@
         <v>37</v>
       </c>
       <c r="F340">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="G340" t="s">
-        <v>702</v>
+        <v>38</v>
       </c>
       <c r="H340" t="s">
         <v>13</v>
@@ -12759,13 +12756,13 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B341" t="s">
         <v>23</v>
       </c>
       <c r="C341" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D341" t="s">
         <v>139</v>
@@ -12774,10 +12771,10 @@
         <v>37</v>
       </c>
       <c r="F341">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G341" t="s">
-        <v>702</v>
+        <v>38</v>
       </c>
       <c r="H341" t="s">
         <v>13</v>
@@ -12785,13 +12782,13 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B342" t="s">
         <v>23</v>
       </c>
       <c r="C342" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D342" t="s">
         <v>139</v>
@@ -12800,7 +12797,7 @@
         <v>37</v>
       </c>
       <c r="F342">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="G342" t="s">
         <v>38</v>
@@ -12811,13 +12808,13 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B343" t="s">
         <v>23</v>
       </c>
       <c r="C343" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D343" t="s">
         <v>139</v>
@@ -12826,7 +12823,7 @@
         <v>37</v>
       </c>
       <c r="F343">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G343" t="s">
         <v>38</v>
@@ -12837,13 +12834,13 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B344" t="s">
         <v>23</v>
       </c>
       <c r="C344" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D344" t="s">
         <v>139</v>
@@ -12852,7 +12849,7 @@
         <v>37</v>
       </c>
       <c r="F344">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="G344" t="s">
         <v>38</v>
@@ -12863,13 +12860,13 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B345" t="s">
         <v>23</v>
       </c>
       <c r="C345" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D345" t="s">
         <v>139</v>
@@ -12878,7 +12875,7 @@
         <v>37</v>
       </c>
       <c r="F345">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G345" t="s">
         <v>38</v>
@@ -12889,13 +12886,13 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B346" t="s">
         <v>23</v>
       </c>
       <c r="C346" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D346" t="s">
         <v>139</v>
@@ -12904,7 +12901,7 @@
         <v>37</v>
       </c>
       <c r="F346">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G346" t="s">
         <v>38</v>
@@ -12915,13 +12912,13 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B347" t="s">
         <v>23</v>
       </c>
       <c r="C347" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D347" t="s">
         <v>139</v>
@@ -12930,7 +12927,7 @@
         <v>37</v>
       </c>
       <c r="F347">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G347" t="s">
         <v>38</v>
@@ -12941,13 +12938,13 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B348" t="s">
         <v>23</v>
       </c>
       <c r="C348" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D348" t="s">
         <v>139</v>
@@ -12956,7 +12953,7 @@
         <v>37</v>
       </c>
       <c r="F348">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G348" t="s">
         <v>38</v>
@@ -12967,13 +12964,13 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B349" t="s">
         <v>23</v>
       </c>
       <c r="C349" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D349" t="s">
         <v>139</v>
@@ -12982,7 +12979,7 @@
         <v>37</v>
       </c>
       <c r="F349">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G349" t="s">
         <v>38</v>
@@ -12993,13 +12990,13 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B350" t="s">
         <v>23</v>
       </c>
       <c r="C350" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D350" t="s">
         <v>139</v>
@@ -13008,7 +13005,7 @@
         <v>37</v>
       </c>
       <c r="F350">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G350" t="s">
         <v>38</v>
@@ -13019,13 +13016,13 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B351" t="s">
         <v>23</v>
       </c>
       <c r="C351" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D351" t="s">
         <v>139</v>
@@ -13034,7 +13031,7 @@
         <v>37</v>
       </c>
       <c r="F351">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G351" t="s">
         <v>38</v>
@@ -13045,13 +13042,13 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B352" t="s">
         <v>24</v>
       </c>
       <c r="C352" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D352" t="s">
         <v>36</v>
@@ -13060,7 +13057,7 @@
         <v>37</v>
       </c>
       <c r="F352">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G352" t="s">
         <v>38</v>
@@ -13071,13 +13068,13 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B353" t="s">
         <v>24</v>
       </c>
       <c r="C353" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D353" t="s">
         <v>36</v>
@@ -13086,7 +13083,7 @@
         <v>37</v>
       </c>
       <c r="F353">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="G353" t="s">
         <v>38</v>
@@ -13097,13 +13094,13 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B354" t="s">
         <v>24</v>
       </c>
       <c r="C354" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D354" t="s">
         <v>36</v>
@@ -13112,7 +13109,7 @@
         <v>37</v>
       </c>
       <c r="F354">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="G354" t="s">
         <v>38</v>
@@ -13123,13 +13120,13 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B355" t="s">
         <v>24</v>
       </c>
       <c r="C355" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D355" t="s">
         <v>36</v>
@@ -13138,7 +13135,7 @@
         <v>37</v>
       </c>
       <c r="F355">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G355" t="s">
         <v>38</v>
@@ -13149,13 +13146,13 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B356" t="s">
         <v>24</v>
       </c>
       <c r="C356" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D356" t="s">
         <v>36</v>
@@ -13164,7 +13161,7 @@
         <v>37</v>
       </c>
       <c r="F356">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="G356" t="s">
         <v>38</v>
@@ -13175,13 +13172,13 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B357" t="s">
         <v>24</v>
       </c>
       <c r="C357" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D357" t="s">
         <v>36</v>
@@ -13201,13 +13198,13 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B358" t="s">
         <v>24</v>
       </c>
       <c r="C358" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D358" t="s">
         <v>36</v>
@@ -13216,7 +13213,7 @@
         <v>37</v>
       </c>
       <c r="F358">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G358" t="s">
         <v>38</v>
@@ -13227,13 +13224,13 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B359" t="s">
         <v>24</v>
       </c>
       <c r="C359" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D359" t="s">
         <v>36</v>
@@ -13242,7 +13239,7 @@
         <v>37</v>
       </c>
       <c r="F359">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G359" t="s">
         <v>38</v>
@@ -13253,13 +13250,13 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B360" t="s">
         <v>24</v>
       </c>
       <c r="C360" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D360" t="s">
         <v>36</v>
@@ -13268,7 +13265,7 @@
         <v>37</v>
       </c>
       <c r="F360">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G360" t="s">
         <v>38</v>
@@ -13279,13 +13276,13 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B361" t="s">
         <v>24</v>
       </c>
       <c r="C361" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D361" t="s">
         <v>36</v>
@@ -13294,7 +13291,7 @@
         <v>37</v>
       </c>
       <c r="F361">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G361" t="s">
         <v>38</v>
@@ -13305,13 +13302,13 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B362" t="s">
         <v>24</v>
       </c>
       <c r="C362" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D362" t="s">
         <v>36</v>
@@ -13320,7 +13317,7 @@
         <v>37</v>
       </c>
       <c r="F362">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G362" t="s">
         <v>38</v>
@@ -13331,13 +13328,13 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B363" t="s">
         <v>24</v>
       </c>
       <c r="C363" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D363" t="s">
         <v>36</v>
@@ -13346,7 +13343,7 @@
         <v>37</v>
       </c>
       <c r="F363">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G363" t="s">
         <v>38</v>
@@ -13357,13 +13354,13 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B364" t="s">
         <v>24</v>
       </c>
       <c r="C364" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D364" t="s">
         <v>36</v>
@@ -13372,7 +13369,7 @@
         <v>37</v>
       </c>
       <c r="F364">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G364" t="s">
         <v>38</v>
@@ -13383,13 +13380,13 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B365" t="s">
         <v>24</v>
       </c>
       <c r="C365" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D365" t="s">
         <v>36</v>
@@ -13398,7 +13395,7 @@
         <v>37</v>
       </c>
       <c r="F365">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G365" t="s">
         <v>38</v>
@@ -13409,13 +13406,13 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B366" t="s">
         <v>24</v>
       </c>
       <c r="C366" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D366" t="s">
         <v>36</v>
@@ -13424,7 +13421,7 @@
         <v>37</v>
       </c>
       <c r="F366">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G366" t="s">
         <v>38</v>
@@ -13435,13 +13432,13 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B367" t="s">
         <v>24</v>
       </c>
       <c r="C367" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D367" t="s">
         <v>36</v>
@@ -13450,7 +13447,7 @@
         <v>37</v>
       </c>
       <c r="F367">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G367" t="s">
         <v>38</v>
@@ -13461,13 +13458,13 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B368" t="s">
         <v>24</v>
       </c>
       <c r="C368" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D368" t="s">
         <v>36</v>
@@ -13476,7 +13473,7 @@
         <v>37</v>
       </c>
       <c r="F368">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="G368" t="s">
         <v>38</v>
@@ -13487,13 +13484,13 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B369" t="s">
         <v>24</v>
       </c>
       <c r="C369" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D369" t="s">
         <v>36</v>
@@ -13502,7 +13499,7 @@
         <v>37</v>
       </c>
       <c r="F369">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G369" t="s">
         <v>38</v>
@@ -13513,13 +13510,13 @@
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B370" t="s">
         <v>24</v>
       </c>
       <c r="C370" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D370" t="s">
         <v>36</v>
@@ -13528,7 +13525,7 @@
         <v>37</v>
       </c>
       <c r="F370">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G370" t="s">
         <v>38</v>
@@ -13539,13 +13536,13 @@
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B371" t="s">
         <v>24</v>
       </c>
       <c r="C371" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D371" t="s">
         <v>36</v>
@@ -13554,7 +13551,7 @@
         <v>37</v>
       </c>
       <c r="F371">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G371" t="s">
         <v>38</v>
@@ -13565,13 +13562,13 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B372" t="s">
         <v>24</v>
       </c>
       <c r="C372" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D372" t="s">
         <v>36</v>
@@ -13580,7 +13577,7 @@
         <v>37</v>
       </c>
       <c r="F372">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G372" t="s">
         <v>38</v>
@@ -13591,13 +13588,13 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B373" t="s">
         <v>24</v>
       </c>
       <c r="C373" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D373" t="s">
         <v>36</v>
@@ -13606,7 +13603,7 @@
         <v>37</v>
       </c>
       <c r="F373">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G373" t="s">
         <v>38</v>
@@ -13617,13 +13614,13 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B374" t="s">
         <v>24</v>
       </c>
       <c r="C374" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D374" t="s">
         <v>36</v>
@@ -13632,7 +13629,7 @@
         <v>37</v>
       </c>
       <c r="F374">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="G374" t="s">
         <v>38</v>
@@ -13643,13 +13640,13 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B375" t="s">
         <v>24</v>
       </c>
       <c r="C375" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D375" t="s">
         <v>36</v>
@@ -13658,7 +13655,7 @@
         <v>37</v>
       </c>
       <c r="F375">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G375" t="s">
         <v>38</v>
@@ -13669,13 +13666,13 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B376" t="s">
         <v>24</v>
       </c>
       <c r="C376" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D376" t="s">
         <v>36</v>
@@ -13684,7 +13681,7 @@
         <v>37</v>
       </c>
       <c r="F376">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G376" t="s">
         <v>38</v>
@@ -13695,13 +13692,13 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B377" t="s">
         <v>24</v>
       </c>
       <c r="C377" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D377" t="s">
         <v>36</v>
@@ -13710,7 +13707,7 @@
         <v>37</v>
       </c>
       <c r="F377">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G377" t="s">
         <v>38</v>
@@ -13721,13 +13718,13 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B378" t="s">
         <v>24</v>
       </c>
       <c r="C378" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D378" t="s">
         <v>36</v>
@@ -13736,7 +13733,7 @@
         <v>37</v>
       </c>
       <c r="F378">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G378" t="s">
         <v>38</v>
@@ -13747,13 +13744,13 @@
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B379" t="s">
         <v>24</v>
       </c>
       <c r="C379" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D379" t="s">
         <v>36</v>
@@ -13762,7 +13759,7 @@
         <v>37</v>
       </c>
       <c r="F379">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G379" t="s">
         <v>38</v>
@@ -13773,13 +13770,13 @@
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B380" t="s">
         <v>24</v>
       </c>
       <c r="C380" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D380" t="s">
         <v>36</v>
@@ -13788,7 +13785,7 @@
         <v>37</v>
       </c>
       <c r="F380">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G380" t="s">
         <v>38</v>
@@ -13799,13 +13796,13 @@
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B381" t="s">
         <v>24</v>
       </c>
       <c r="C381" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D381" t="s">
         <v>36</v>
@@ -13814,7 +13811,7 @@
         <v>37</v>
       </c>
       <c r="F381">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G381" t="s">
         <v>38</v>
@@ -13825,13 +13822,13 @@
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B382" t="s">
         <v>24</v>
       </c>
       <c r="C382" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D382" t="s">
         <v>36</v>
@@ -13840,7 +13837,7 @@
         <v>37</v>
       </c>
       <c r="F382">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G382" t="s">
         <v>38</v>
@@ -13851,13 +13848,13 @@
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B383" t="s">
         <v>24</v>
       </c>
       <c r="C383" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D383" t="s">
         <v>36</v>
@@ -13866,7 +13863,7 @@
         <v>37</v>
       </c>
       <c r="F383">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G383" t="s">
         <v>38</v>
@@ -13877,13 +13874,13 @@
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B384" t="s">
         <v>24</v>
       </c>
       <c r="C384" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D384" t="s">
         <v>36</v>
@@ -13892,7 +13889,7 @@
         <v>37</v>
       </c>
       <c r="F384">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G384" t="s">
         <v>38</v>
@@ -13903,13 +13900,13 @@
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B385" t="s">
         <v>24</v>
       </c>
       <c r="C385" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D385" t="s">
         <v>36</v>
@@ -13918,7 +13915,7 @@
         <v>37</v>
       </c>
       <c r="F385">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G385" t="s">
         <v>38</v>
@@ -13929,13 +13926,13 @@
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B386" t="s">
         <v>24</v>
       </c>
       <c r="C386" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D386" t="s">
         <v>36</v>
@@ -13944,7 +13941,7 @@
         <v>37</v>
       </c>
       <c r="F386">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="G386" t="s">
         <v>38</v>
@@ -13955,13 +13952,13 @@
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B387" t="s">
         <v>24</v>
       </c>
       <c r="C387" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D387" t="s">
         <v>36</v>
@@ -13970,7 +13967,7 @@
         <v>37</v>
       </c>
       <c r="F387">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G387" t="s">
         <v>38</v>
@@ -13981,13 +13978,13 @@
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B388" t="s">
         <v>24</v>
       </c>
       <c r="C388" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D388" t="s">
         <v>36</v>
@@ -13996,7 +13993,7 @@
         <v>37</v>
       </c>
       <c r="F388">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G388" t="s">
         <v>38</v>
@@ -14007,13 +14004,13 @@
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B389" t="s">
         <v>24</v>
       </c>
       <c r="C389" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D389" t="s">
         <v>36</v>
@@ -14022,7 +14019,7 @@
         <v>37</v>
       </c>
       <c r="F389">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G389" t="s">
         <v>38</v>
@@ -14033,13 +14030,13 @@
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B390" t="s">
         <v>24</v>
       </c>
       <c r="C390" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D390" t="s">
         <v>36</v>
@@ -14048,7 +14045,7 @@
         <v>37</v>
       </c>
       <c r="F390">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G390" t="s">
         <v>38</v>
@@ -14059,13 +14056,13 @@
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B391" t="s">
         <v>24</v>
       </c>
       <c r="C391" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D391" t="s">
         <v>36</v>
@@ -14074,7 +14071,7 @@
         <v>37</v>
       </c>
       <c r="F391">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G391" t="s">
         <v>38</v>
@@ -14085,13 +14082,13 @@
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B392" t="s">
         <v>24</v>
       </c>
       <c r="C392" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D392" t="s">
         <v>36</v>
@@ -14100,7 +14097,7 @@
         <v>37</v>
       </c>
       <c r="F392">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G392" t="s">
         <v>38</v>
@@ -14111,13 +14108,13 @@
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B393" t="s">
         <v>24</v>
       </c>
       <c r="C393" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D393" t="s">
         <v>36</v>
@@ -14126,7 +14123,7 @@
         <v>37</v>
       </c>
       <c r="F393">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G393" t="s">
         <v>38</v>
@@ -14137,13 +14134,13 @@
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B394" t="s">
         <v>24</v>
       </c>
       <c r="C394" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D394" t="s">
         <v>36</v>
@@ -14152,7 +14149,7 @@
         <v>37</v>
       </c>
       <c r="F394">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G394" t="s">
         <v>38</v>
@@ -14163,13 +14160,13 @@
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B395" t="s">
         <v>24</v>
       </c>
       <c r="C395" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D395" t="s">
         <v>36</v>
@@ -14178,7 +14175,7 @@
         <v>37</v>
       </c>
       <c r="F395">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G395" t="s">
         <v>38</v>
@@ -14189,13 +14186,13 @@
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B396" t="s">
         <v>24</v>
       </c>
       <c r="C396" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D396" t="s">
         <v>36</v>
@@ -14204,7 +14201,7 @@
         <v>37</v>
       </c>
       <c r="F396">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G396" t="s">
         <v>38</v>
@@ -14215,13 +14212,13 @@
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B397" t="s">
         <v>24</v>
       </c>
       <c r="C397" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D397" t="s">
         <v>36</v>
@@ -14230,7 +14227,7 @@
         <v>37</v>
       </c>
       <c r="F397">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G397" t="s">
         <v>38</v>
@@ -14241,13 +14238,13 @@
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B398" t="s">
         <v>24</v>
       </c>
       <c r="C398" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D398" t="s">
         <v>36</v>
@@ -14256,7 +14253,7 @@
         <v>37</v>
       </c>
       <c r="F398">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G398" t="s">
         <v>38</v>
@@ -14267,13 +14264,13 @@
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B399" t="s">
         <v>24</v>
       </c>
       <c r="C399" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D399" t="s">
         <v>36</v>
@@ -14282,7 +14279,7 @@
         <v>37</v>
       </c>
       <c r="F399">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G399" t="s">
         <v>38</v>
@@ -14293,13 +14290,13 @@
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B400" t="s">
         <v>24</v>
       </c>
       <c r="C400" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D400" t="s">
         <v>36</v>
@@ -14308,7 +14305,7 @@
         <v>37</v>
       </c>
       <c r="F400">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G400" t="s">
         <v>38</v>
@@ -14319,13 +14316,13 @@
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B401" t="s">
         <v>24</v>
       </c>
       <c r="C401" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D401" t="s">
         <v>36</v>
@@ -14334,7 +14331,7 @@
         <v>37</v>
       </c>
       <c r="F401">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G401" t="s">
         <v>38</v>
@@ -14345,13 +14342,13 @@
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B402" t="s">
         <v>25</v>
       </c>
       <c r="C402" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D402" t="s">
         <v>36</v>
@@ -14371,13 +14368,13 @@
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B403" t="s">
         <v>25</v>
       </c>
       <c r="C403" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D403" t="s">
         <v>36</v>
@@ -14386,7 +14383,7 @@
         <v>37</v>
       </c>
       <c r="F403">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G403" t="s">
         <v>38</v>
@@ -14397,13 +14394,13 @@
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B404" t="s">
         <v>25</v>
       </c>
       <c r="C404" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D404" t="s">
         <v>36</v>
@@ -14412,7 +14409,7 @@
         <v>37</v>
       </c>
       <c r="F404">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G404" t="s">
         <v>38</v>
@@ -14423,13 +14420,13 @@
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B405" t="s">
         <v>25</v>
       </c>
       <c r="C405" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D405" t="s">
         <v>36</v>
@@ -14438,7 +14435,7 @@
         <v>37</v>
       </c>
       <c r="F405">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G405" t="s">
         <v>38</v>
@@ -14449,13 +14446,13 @@
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B406" t="s">
         <v>25</v>
       </c>
       <c r="C406" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D406" t="s">
         <v>36</v>
@@ -14464,7 +14461,7 @@
         <v>37</v>
       </c>
       <c r="F406">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G406" t="s">
         <v>38</v>
@@ -14475,13 +14472,13 @@
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B407" t="s">
         <v>25</v>
       </c>
       <c r="C407" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D407" t="s">
         <v>36</v>
@@ -14490,7 +14487,7 @@
         <v>37</v>
       </c>
       <c r="F407">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G407" t="s">
         <v>38</v>
@@ -14501,13 +14498,13 @@
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B408" t="s">
         <v>25</v>
       </c>
       <c r="C408" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D408" t="s">
         <v>36</v>
@@ -14516,7 +14513,7 @@
         <v>37</v>
       </c>
       <c r="F408">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G408" t="s">
         <v>38</v>
@@ -14527,13 +14524,13 @@
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B409" t="s">
         <v>25</v>
       </c>
       <c r="C409" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D409" t="s">
         <v>36</v>
@@ -14542,7 +14539,7 @@
         <v>37</v>
       </c>
       <c r="F409">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G409" t="s">
         <v>38</v>
@@ -14553,13 +14550,13 @@
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B410" t="s">
         <v>25</v>
       </c>
       <c r="C410" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D410" t="s">
         <v>36</v>
@@ -14568,7 +14565,7 @@
         <v>37</v>
       </c>
       <c r="F410">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G410" t="s">
         <v>38</v>
@@ -14579,13 +14576,13 @@
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B411" t="s">
         <v>25</v>
       </c>
       <c r="C411" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D411" t="s">
         <v>36</v>
@@ -14594,7 +14591,7 @@
         <v>37</v>
       </c>
       <c r="F411">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G411" t="s">
         <v>38</v>
@@ -14605,13 +14602,13 @@
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B412" t="s">
         <v>25</v>
       </c>
       <c r="C412" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D412" t="s">
         <v>36</v>
@@ -14620,7 +14617,7 @@
         <v>37</v>
       </c>
       <c r="F412">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G412" t="s">
         <v>38</v>
@@ -14631,13 +14628,13 @@
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B413" t="s">
         <v>25</v>
       </c>
       <c r="C413" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="D413" t="s">
         <v>36</v>
@@ -14646,7 +14643,7 @@
         <v>37</v>
       </c>
       <c r="F413">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="G413" t="s">
         <v>38</v>
@@ -14657,13 +14654,13 @@
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B414" t="s">
         <v>25</v>
       </c>
       <c r="C414" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D414" t="s">
         <v>36</v>
@@ -14683,13 +14680,13 @@
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B415" t="s">
         <v>25</v>
       </c>
       <c r="C415" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D415" t="s">
         <v>36</v>
@@ -14698,7 +14695,7 @@
         <v>37</v>
       </c>
       <c r="F415">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="G415" t="s">
         <v>38</v>
@@ -14709,13 +14706,13 @@
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B416" t="s">
         <v>25</v>
       </c>
       <c r="C416" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D416" t="s">
         <v>36</v>
@@ -14724,7 +14721,7 @@
         <v>37</v>
       </c>
       <c r="F416">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G416" t="s">
         <v>38</v>
@@ -14735,13 +14732,13 @@
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B417" t="s">
         <v>25</v>
       </c>
       <c r="C417" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="D417" t="s">
         <v>36</v>
@@ -14750,7 +14747,7 @@
         <v>37</v>
       </c>
       <c r="F417">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G417" t="s">
         <v>38</v>
@@ -14761,13 +14758,13 @@
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B418" t="s">
         <v>25</v>
       </c>
       <c r="C418" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D418" t="s">
         <v>36</v>
@@ -14776,7 +14773,7 @@
         <v>37</v>
       </c>
       <c r="F418">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G418" t="s">
         <v>38</v>
@@ -14787,13 +14784,13 @@
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B419" t="s">
         <v>25</v>
       </c>
       <c r="C419" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D419" t="s">
         <v>36</v>
@@ -14802,7 +14799,7 @@
         <v>37</v>
       </c>
       <c r="F419">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G419" t="s">
         <v>38</v>
@@ -14813,13 +14810,13 @@
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B420" t="s">
         <v>25</v>
       </c>
       <c r="C420" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D420" t="s">
         <v>36</v>
@@ -14828,7 +14825,7 @@
         <v>37</v>
       </c>
       <c r="F420">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G420" t="s">
         <v>38</v>
@@ -14839,13 +14836,13 @@
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B421" t="s">
         <v>25</v>
       </c>
       <c r="C421" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D421" t="s">
         <v>36</v>
@@ -14854,7 +14851,7 @@
         <v>37</v>
       </c>
       <c r="F421">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G421" t="s">
         <v>38</v>
@@ -14865,13 +14862,13 @@
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B422" t="s">
         <v>25</v>
       </c>
       <c r="C422" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D422" t="s">
         <v>36</v>
@@ -14880,7 +14877,7 @@
         <v>37</v>
       </c>
       <c r="F422">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="G422" t="s">
         <v>38</v>
@@ -14891,13 +14888,13 @@
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B423" t="s">
         <v>25</v>
       </c>
       <c r="C423" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D423" t="s">
         <v>36</v>
@@ -14906,7 +14903,7 @@
         <v>37</v>
       </c>
       <c r="F423">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G423" t="s">
         <v>38</v>
@@ -14917,13 +14914,13 @@
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B424" t="s">
         <v>25</v>
       </c>
       <c r="C424" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D424" t="s">
         <v>36</v>
@@ -14932,7 +14929,7 @@
         <v>37</v>
       </c>
       <c r="F424">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G424" t="s">
         <v>38</v>
@@ -14943,13 +14940,13 @@
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B425" t="s">
         <v>25</v>
       </c>
       <c r="C425" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D425" t="s">
         <v>36</v>
@@ -14958,7 +14955,7 @@
         <v>37</v>
       </c>
       <c r="F425">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G425" t="s">
         <v>38</v>
@@ -14969,13 +14966,13 @@
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B426" t="s">
         <v>25</v>
       </c>
       <c r="C426" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D426" t="s">
         <v>36</v>
@@ -14984,7 +14981,7 @@
         <v>37</v>
       </c>
       <c r="F426">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G426" t="s">
         <v>38</v>
@@ -14995,13 +14992,13 @@
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B427" t="s">
         <v>25</v>
       </c>
       <c r="C427" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D427" t="s">
         <v>36</v>
@@ -15010,7 +15007,7 @@
         <v>37</v>
       </c>
       <c r="F427">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="G427" t="s">
         <v>38</v>
@@ -15021,13 +15018,13 @@
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B428" t="s">
         <v>25</v>
       </c>
       <c r="C428" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D428" t="s">
         <v>36</v>
@@ -15036,7 +15033,7 @@
         <v>37</v>
       </c>
       <c r="F428">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G428" t="s">
         <v>38</v>
@@ -15047,13 +15044,13 @@
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B429" t="s">
         <v>25</v>
       </c>
       <c r="C429" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D429" t="s">
         <v>36</v>
@@ -15062,7 +15059,7 @@
         <v>37</v>
       </c>
       <c r="F429">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G429" t="s">
         <v>38</v>
@@ -15073,13 +15070,13 @@
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B430" t="s">
         <v>25</v>
       </c>
       <c r="C430" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D430" t="s">
         <v>36</v>
@@ -15088,7 +15085,7 @@
         <v>37</v>
       </c>
       <c r="F430">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G430" t="s">
         <v>38</v>
@@ -15099,13 +15096,13 @@
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B431" t="s">
         <v>25</v>
       </c>
       <c r="C431" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D431" t="s">
         <v>36</v>
@@ -15114,7 +15111,7 @@
         <v>37</v>
       </c>
       <c r="F431">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="G431" t="s">
         <v>38</v>
@@ -15125,13 +15122,13 @@
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B432" t="s">
         <v>25</v>
       </c>
       <c r="C432" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D432" t="s">
         <v>36</v>
@@ -15140,7 +15137,7 @@
         <v>37</v>
       </c>
       <c r="F432">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G432" t="s">
         <v>38</v>
@@ -15151,13 +15148,13 @@
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B433" t="s">
         <v>25</v>
       </c>
       <c r="C433" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D433" t="s">
         <v>36</v>
@@ -15166,7 +15163,7 @@
         <v>37</v>
       </c>
       <c r="F433">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G433" t="s">
         <v>38</v>
@@ -15177,13 +15174,13 @@
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B434" t="s">
         <v>25</v>
       </c>
       <c r="C434" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D434" t="s">
         <v>36</v>
@@ -15192,7 +15189,7 @@
         <v>37</v>
       </c>
       <c r="F434">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G434" t="s">
         <v>38</v>
@@ -15203,13 +15200,13 @@
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B435" t="s">
         <v>25</v>
       </c>
       <c r="C435" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D435" t="s">
         <v>36</v>
@@ -15218,7 +15215,7 @@
         <v>37</v>
       </c>
       <c r="F435">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="G435" t="s">
         <v>38</v>
@@ -15229,13 +15226,13 @@
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B436" t="s">
         <v>25</v>
       </c>
       <c r="C436" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D436" t="s">
         <v>36</v>
@@ -15244,7 +15241,7 @@
         <v>37</v>
       </c>
       <c r="F436">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G436" t="s">
         <v>38</v>
@@ -15255,13 +15252,13 @@
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B437" t="s">
         <v>25</v>
       </c>
       <c r="C437" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D437" t="s">
         <v>36</v>
@@ -15270,7 +15267,7 @@
         <v>37</v>
       </c>
       <c r="F437">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G437" t="s">
         <v>38</v>
@@ -15281,13 +15278,13 @@
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B438" t="s">
         <v>25</v>
       </c>
       <c r="C438" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D438" t="s">
         <v>36</v>
@@ -15296,7 +15293,7 @@
         <v>37</v>
       </c>
       <c r="F438">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G438" t="s">
         <v>38</v>
@@ -15307,13 +15304,13 @@
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B439" t="s">
         <v>25</v>
       </c>
       <c r="C439" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D439" t="s">
         <v>36</v>
@@ -15322,7 +15319,7 @@
         <v>37</v>
       </c>
       <c r="F439">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G439" t="s">
         <v>38</v>
@@ -15333,13 +15330,13 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B440" t="s">
         <v>25</v>
       </c>
       <c r="C440" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D440" t="s">
         <v>36</v>
@@ -15348,7 +15345,7 @@
         <v>37</v>
       </c>
       <c r="F440">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G440" t="s">
         <v>38</v>
@@ -15359,13 +15356,13 @@
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B441" t="s">
         <v>25</v>
       </c>
       <c r="C441" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D441" t="s">
         <v>36</v>
@@ -15374,7 +15371,7 @@
         <v>37</v>
       </c>
       <c r="F441">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G441" t="s">
         <v>38</v>
@@ -15385,13 +15382,13 @@
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B442" t="s">
         <v>25</v>
       </c>
       <c r="C442" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D442" t="s">
         <v>36</v>
@@ -15400,7 +15397,7 @@
         <v>37</v>
       </c>
       <c r="F442">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G442" t="s">
         <v>38</v>
@@ -15411,13 +15408,13 @@
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B443" t="s">
         <v>25</v>
       </c>
       <c r="C443" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D443" t="s">
         <v>36</v>
@@ -15426,7 +15423,7 @@
         <v>37</v>
       </c>
       <c r="F443">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G443" t="s">
         <v>38</v>
@@ -15437,13 +15434,13 @@
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B444" t="s">
         <v>25</v>
       </c>
       <c r="C444" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D444" t="s">
         <v>36</v>
@@ -15452,7 +15449,7 @@
         <v>37</v>
       </c>
       <c r="F444">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G444" t="s">
         <v>38</v>
@@ -15463,13 +15460,13 @@
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B445" t="s">
         <v>25</v>
       </c>
       <c r="C445" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D445" t="s">
         <v>36</v>
@@ -15478,7 +15475,7 @@
         <v>37</v>
       </c>
       <c r="F445">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G445" t="s">
         <v>38</v>
@@ -15489,13 +15486,13 @@
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B446" t="s">
         <v>25</v>
       </c>
       <c r="C446" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D446" t="s">
         <v>36</v>
@@ -15504,7 +15501,7 @@
         <v>37</v>
       </c>
       <c r="F446">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G446" t="s">
         <v>38</v>
@@ -15515,13 +15512,13 @@
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B447" t="s">
         <v>25</v>
       </c>
       <c r="C447" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D447" t="s">
         <v>36</v>
@@ -15530,7 +15527,7 @@
         <v>37</v>
       </c>
       <c r="F447">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G447" t="s">
         <v>38</v>
@@ -15541,13 +15538,13 @@
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B448" t="s">
         <v>25</v>
       </c>
       <c r="C448" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D448" t="s">
         <v>36</v>
@@ -15556,7 +15553,7 @@
         <v>37</v>
       </c>
       <c r="F448">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G448" t="s">
         <v>38</v>
@@ -15567,13 +15564,13 @@
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B449" t="s">
         <v>25</v>
       </c>
       <c r="C449" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D449" t="s">
         <v>36</v>
@@ -15582,7 +15579,7 @@
         <v>37</v>
       </c>
       <c r="F449">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G449" t="s">
         <v>38</v>
@@ -15593,13 +15590,13 @@
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B450" t="s">
         <v>25</v>
       </c>
       <c r="C450" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D450" t="s">
         <v>36</v>
@@ -15619,13 +15616,13 @@
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B451" t="s">
         <v>25</v>
       </c>
       <c r="C451" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D451" t="s">
         <v>36</v>
@@ -15634,7 +15631,7 @@
         <v>37</v>
       </c>
       <c r="F451">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="G451" t="s">
         <v>38</v>
@@ -15645,13 +15642,13 @@
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B452" t="s">
         <v>26</v>
       </c>
       <c r="C452" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D452" t="s">
         <v>36</v>
@@ -15660,7 +15657,7 @@
         <v>37</v>
       </c>
       <c r="F452">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G452" t="s">
         <v>38</v>
@@ -15671,13 +15668,13 @@
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B453" t="s">
         <v>26</v>
       </c>
       <c r="C453" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D453" t="s">
         <v>36</v>
@@ -15686,7 +15683,7 @@
         <v>37</v>
       </c>
       <c r="F453">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G453" t="s">
         <v>38</v>
@@ -15697,13 +15694,13 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B454" t="s">
         <v>26</v>
       </c>
       <c r="C454" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D454" t="s">
         <v>36</v>
@@ -15712,7 +15709,7 @@
         <v>37</v>
       </c>
       <c r="F454">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G454" t="s">
         <v>38</v>
@@ -15723,13 +15720,13 @@
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B455" t="s">
         <v>26</v>
       </c>
       <c r="C455" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D455" t="s">
         <v>36</v>
@@ -15738,7 +15735,7 @@
         <v>37</v>
       </c>
       <c r="F455">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="G455" t="s">
         <v>38</v>
@@ -15749,13 +15746,13 @@
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B456" t="s">
         <v>26</v>
       </c>
       <c r="C456" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D456" t="s">
         <v>36</v>
@@ -15764,7 +15761,7 @@
         <v>37</v>
       </c>
       <c r="F456">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="G456" t="s">
         <v>38</v>
@@ -15775,13 +15772,13 @@
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B457" t="s">
         <v>26</v>
       </c>
       <c r="C457" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="D457" t="s">
         <v>36</v>
@@ -15790,7 +15787,7 @@
         <v>37</v>
       </c>
       <c r="F457">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G457" t="s">
         <v>38</v>
@@ -15801,13 +15798,13 @@
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B458" t="s">
         <v>26</v>
       </c>
       <c r="C458" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D458" t="s">
         <v>36</v>
@@ -15816,7 +15813,7 @@
         <v>37</v>
       </c>
       <c r="F458">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G458" t="s">
         <v>38</v>
@@ -15827,13 +15824,13 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B459" t="s">
         <v>26</v>
       </c>
       <c r="C459" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="D459" t="s">
         <v>36</v>
@@ -15842,7 +15839,7 @@
         <v>37</v>
       </c>
       <c r="F459">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G459" t="s">
         <v>38</v>
@@ -15853,13 +15850,13 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B460" t="s">
         <v>26</v>
       </c>
       <c r="C460" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D460" t="s">
         <v>36</v>
@@ -15868,7 +15865,7 @@
         <v>37</v>
       </c>
       <c r="F460">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G460" t="s">
         <v>38</v>
@@ -15879,13 +15876,13 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B461" t="s">
         <v>26</v>
       </c>
       <c r="C461" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D461" t="s">
         <v>36</v>
@@ -15894,7 +15891,7 @@
         <v>37</v>
       </c>
       <c r="F461">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G461" t="s">
         <v>38</v>
@@ -15905,13 +15902,13 @@
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B462" t="s">
         <v>26</v>
       </c>
       <c r="C462" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D462" t="s">
         <v>36</v>
@@ -15920,7 +15917,7 @@
         <v>37</v>
       </c>
       <c r="F462">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="G462" t="s">
         <v>38</v>
@@ -15931,13 +15928,13 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B463" t="s">
         <v>26</v>
       </c>
       <c r="C463" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="D463" t="s">
         <v>36</v>
@@ -15946,7 +15943,7 @@
         <v>37</v>
       </c>
       <c r="F463">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G463" t="s">
         <v>38</v>
@@ -15957,13 +15954,13 @@
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B464" t="s">
         <v>26</v>
       </c>
       <c r="C464" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D464" t="s">
         <v>36</v>
@@ -15972,7 +15969,7 @@
         <v>37</v>
       </c>
       <c r="F464">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G464" t="s">
         <v>38</v>
@@ -15983,13 +15980,13 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B465" t="s">
         <v>26</v>
       </c>
       <c r="C465" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D465" t="s">
         <v>36</v>
@@ -15998,7 +15995,7 @@
         <v>37</v>
       </c>
       <c r="F465">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G465" t="s">
         <v>38</v>
@@ -16009,13 +16006,13 @@
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B466" t="s">
         <v>26</v>
       </c>
       <c r="C466" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D466" t="s">
         <v>36</v>
@@ -16035,13 +16032,13 @@
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B467" t="s">
         <v>26</v>
       </c>
       <c r="C467" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D467" t="s">
         <v>36</v>
@@ -16050,7 +16047,7 @@
         <v>37</v>
       </c>
       <c r="F467">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G467" t="s">
         <v>38</v>
@@ -16061,13 +16058,13 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B468" t="s">
         <v>26</v>
       </c>
       <c r="C468" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D468" t="s">
         <v>36</v>
@@ -16076,7 +16073,7 @@
         <v>37</v>
       </c>
       <c r="F468">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="G468" t="s">
         <v>38</v>
@@ -16087,13 +16084,13 @@
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B469" t="s">
         <v>26</v>
       </c>
       <c r="C469" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D469" t="s">
         <v>36</v>
@@ -16102,7 +16099,7 @@
         <v>37</v>
       </c>
       <c r="F469">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G469" t="s">
         <v>38</v>
@@ -16113,13 +16110,13 @@
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B470" t="s">
         <v>26</v>
       </c>
       <c r="C470" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D470" t="s">
         <v>36</v>
@@ -16128,7 +16125,7 @@
         <v>37</v>
       </c>
       <c r="F470">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G470" t="s">
         <v>38</v>
@@ -16139,13 +16136,13 @@
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B471" t="s">
         <v>26</v>
       </c>
       <c r="C471" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D471" t="s">
         <v>36</v>
@@ -16154,7 +16151,7 @@
         <v>37</v>
       </c>
       <c r="F471">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G471" t="s">
         <v>38</v>
@@ -16165,13 +16162,13 @@
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B472" t="s">
         <v>26</v>
       </c>
       <c r="C472" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D472" t="s">
         <v>36</v>
@@ -16180,7 +16177,7 @@
         <v>37</v>
       </c>
       <c r="F472">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="G472" t="s">
         <v>38</v>
@@ -16191,13 +16188,13 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B473" t="s">
         <v>26</v>
       </c>
       <c r="C473" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D473" t="s">
         <v>36</v>
@@ -16206,7 +16203,7 @@
         <v>37</v>
       </c>
       <c r="F473">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G473" t="s">
         <v>38</v>
@@ -16217,13 +16214,13 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B474" t="s">
         <v>26</v>
       </c>
       <c r="C474" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="D474" t="s">
         <v>36</v>
@@ -16232,7 +16229,7 @@
         <v>37</v>
       </c>
       <c r="F474">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G474" t="s">
         <v>38</v>
@@ -16243,13 +16240,13 @@
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B475" t="s">
         <v>26</v>
       </c>
       <c r="C475" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D475" t="s">
         <v>36</v>
@@ -16258,7 +16255,7 @@
         <v>37</v>
       </c>
       <c r="F475">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="G475" t="s">
         <v>38</v>
@@ -16269,13 +16266,13 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B476" t="s">
         <v>26</v>
       </c>
       <c r="C476" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D476" t="s">
         <v>36</v>
@@ -16284,7 +16281,7 @@
         <v>37</v>
       </c>
       <c r="F476">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="G476" t="s">
         <v>38</v>
@@ -16295,13 +16292,13 @@
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B477" t="s">
         <v>26</v>
       </c>
       <c r="C477" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D477" t="s">
         <v>36</v>
@@ -16310,7 +16307,7 @@
         <v>37</v>
       </c>
       <c r="F477">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G477" t="s">
         <v>38</v>
@@ -16321,13 +16318,13 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B478" t="s">
         <v>26</v>
       </c>
       <c r="C478" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D478" t="s">
         <v>36</v>
@@ -16336,7 +16333,7 @@
         <v>37</v>
       </c>
       <c r="F478">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G478" t="s">
         <v>38</v>
@@ -16347,13 +16344,13 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B479" t="s">
         <v>26</v>
       </c>
       <c r="C479" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D479" t="s">
         <v>36</v>
@@ -16362,7 +16359,7 @@
         <v>37</v>
       </c>
       <c r="F479">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G479" t="s">
         <v>38</v>
@@ -16373,13 +16370,13 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B480" t="s">
         <v>26</v>
       </c>
       <c r="C480" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D480" t="s">
         <v>36</v>
@@ -16388,7 +16385,7 @@
         <v>37</v>
       </c>
       <c r="F480">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G480" t="s">
         <v>38</v>
@@ -16399,13 +16396,13 @@
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B481" t="s">
         <v>26</v>
       </c>
       <c r="C481" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D481" t="s">
         <v>36</v>
@@ -16414,7 +16411,7 @@
         <v>37</v>
       </c>
       <c r="F481">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G481" t="s">
         <v>38</v>
@@ -16425,13 +16422,13 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B482" t="s">
         <v>26</v>
       </c>
       <c r="C482" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D482" t="s">
         <v>36</v>
@@ -16440,7 +16437,7 @@
         <v>37</v>
       </c>
       <c r="F482">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="G482" t="s">
         <v>38</v>
@@ -16451,13 +16448,13 @@
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B483" t="s">
         <v>26</v>
       </c>
       <c r="C483" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D483" t="s">
         <v>36</v>
@@ -16466,7 +16463,7 @@
         <v>37</v>
       </c>
       <c r="F483">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G483" t="s">
         <v>38</v>
@@ -16477,13 +16474,13 @@
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B484" t="s">
         <v>26</v>
       </c>
       <c r="C484" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D484" t="s">
         <v>36</v>
@@ -16492,7 +16489,7 @@
         <v>37</v>
       </c>
       <c r="F484">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G484" t="s">
         <v>38</v>
@@ -16503,13 +16500,13 @@
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B485" t="s">
         <v>26</v>
       </c>
       <c r="C485" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D485" t="s">
         <v>36</v>
@@ -16518,7 +16515,7 @@
         <v>37</v>
       </c>
       <c r="F485">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="G485" t="s">
         <v>38</v>
@@ -16529,13 +16526,13 @@
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B486" t="s">
         <v>26</v>
       </c>
       <c r="C486" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D486" t="s">
         <v>36</v>
@@ -16544,7 +16541,7 @@
         <v>37</v>
       </c>
       <c r="F486">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="G486" t="s">
         <v>38</v>
@@ -16555,13 +16552,13 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B487" t="s">
         <v>26</v>
       </c>
       <c r="C487" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D487" t="s">
         <v>36</v>
@@ -16581,13 +16578,13 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B488" t="s">
         <v>26</v>
       </c>
       <c r="C488" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D488" t="s">
         <v>36</v>
@@ -16596,7 +16593,7 @@
         <v>37</v>
       </c>
       <c r="F488">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G488" t="s">
         <v>38</v>
@@ -16607,13 +16604,13 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B489" t="s">
         <v>26</v>
       </c>
       <c r="C489" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D489" t="s">
         <v>36</v>
@@ -16622,7 +16619,7 @@
         <v>37</v>
       </c>
       <c r="F489">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G489" t="s">
         <v>38</v>
@@ -16633,13 +16630,13 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B490" t="s">
         <v>26</v>
       </c>
       <c r="C490" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="D490" t="s">
         <v>36</v>
@@ -16648,7 +16645,7 @@
         <v>37</v>
       </c>
       <c r="F490">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G490" t="s">
         <v>38</v>
@@ -16659,13 +16656,13 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B491" t="s">
         <v>26</v>
       </c>
       <c r="C491" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D491" t="s">
         <v>36</v>
@@ -16674,7 +16671,7 @@
         <v>37</v>
       </c>
       <c r="F491">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G491" t="s">
         <v>38</v>
@@ -16685,13 +16682,13 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B492" t="s">
         <v>26</v>
       </c>
       <c r="C492" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D492" t="s">
         <v>36</v>
@@ -16700,7 +16697,7 @@
         <v>37</v>
       </c>
       <c r="F492">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G492" t="s">
         <v>38</v>
@@ -16711,13 +16708,13 @@
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B493" t="s">
         <v>26</v>
       </c>
       <c r="C493" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="D493" t="s">
         <v>36</v>
@@ -16726,7 +16723,7 @@
         <v>37</v>
       </c>
       <c r="F493">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G493" t="s">
         <v>38</v>
@@ -16737,13 +16734,13 @@
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B494" t="s">
         <v>26</v>
       </c>
       <c r="C494" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="D494" t="s">
         <v>36</v>
@@ -16752,7 +16749,7 @@
         <v>37</v>
       </c>
       <c r="F494">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G494" t="s">
         <v>38</v>
@@ -16763,13 +16760,13 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B495" t="s">
         <v>26</v>
       </c>
       <c r="C495" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="D495" t="s">
         <v>36</v>
@@ -16778,7 +16775,7 @@
         <v>37</v>
       </c>
       <c r="F495">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="G495" t="s">
         <v>38</v>
@@ -16789,13 +16786,13 @@
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B496" t="s">
         <v>26</v>
       </c>
       <c r="C496" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D496" t="s">
         <v>36</v>
@@ -16804,7 +16801,7 @@
         <v>37</v>
       </c>
       <c r="F496">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G496" t="s">
         <v>38</v>
@@ -16815,13 +16812,13 @@
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B497" t="s">
         <v>26</v>
       </c>
       <c r="C497" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D497" t="s">
         <v>36</v>
@@ -16830,7 +16827,7 @@
         <v>37</v>
       </c>
       <c r="F497">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G497" t="s">
         <v>38</v>
@@ -16841,13 +16838,13 @@
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B498" t="s">
         <v>26</v>
       </c>
       <c r="C498" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D498" t="s">
         <v>36</v>
@@ -16856,7 +16853,7 @@
         <v>37</v>
       </c>
       <c r="F498">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G498" t="s">
         <v>38</v>
@@ -16867,13 +16864,13 @@
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B499" t="s">
         <v>26</v>
       </c>
       <c r="C499" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D499" t="s">
         <v>36</v>
@@ -16882,7 +16879,7 @@
         <v>37</v>
       </c>
       <c r="F499">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G499" t="s">
         <v>38</v>
@@ -16893,13 +16890,13 @@
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B500" t="s">
         <v>26</v>
       </c>
       <c r="C500" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D500" t="s">
         <v>36</v>
@@ -16908,7 +16905,7 @@
         <v>37</v>
       </c>
       <c r="F500">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G500" t="s">
         <v>38</v>
@@ -16919,13 +16916,13 @@
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B501" t="s">
         <v>26</v>
       </c>
       <c r="C501" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D501" t="s">
         <v>36</v>
@@ -16934,7 +16931,7 @@
         <v>37</v>
       </c>
       <c r="F501">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G501" t="s">
         <v>38</v>

--- a/e2e-tests/reports/test-report.xlsx
+++ b/e2e-tests/reports/test-report.xlsx
@@ -42,19 +42,19 @@
     <t>Total Execution Time</t>
   </si>
   <si>
-    <t>17.27s</t>
+    <t>17.19s</t>
   </si>
   <si>
     <t>Average Test Duration</t>
   </si>
   <si>
-    <t>34.55ms</t>
+    <t>34.37ms</t>
   </si>
   <si>
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>7/23/2026, 2:30:55 PM</t>
+    <t>7/23/2026, 3:23:00 PM</t>
   </si>
   <si>
     <t>Category</t>
@@ -3684,7 +3684,7 @@
         <v>100</v>
       </c>
       <c r="G2">
-        <v>35.6</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3707,7 +3707,7 @@
         <v>100</v>
       </c>
       <c r="G3">
-        <v>32.66</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3730,7 +3730,7 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>35.04</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3753,7 +3753,7 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>34.24</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3776,7 +3776,7 @@
         <v>100</v>
       </c>
       <c r="G6">
-        <v>36.94</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3799,7 +3799,7 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>35.1</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3822,7 +3822,7 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>32</v>
+        <v>34.64</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3845,7 +3845,7 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>34.78</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3868,7 +3868,7 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>35.46</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3891,7 +3891,7 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>33.64</v>
+        <v>36.04</v>
       </c>
     </row>
   </sheetData>
@@ -3957,7 +3957,7 @@
         <v>37</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
         <v>38</v>
@@ -3983,7 +3983,7 @@
         <v>37</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
@@ -4035,7 +4035,7 @@
         <v>37</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
         <v>38</v>
@@ -4061,7 +4061,7 @@
         <v>37</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
         <v>38</v>
@@ -4139,7 +4139,7 @@
         <v>37</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
         <v>38</v>
@@ -4191,7 +4191,7 @@
         <v>37</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
         <v>38</v>
@@ -4217,7 +4217,7 @@
         <v>37</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
         <v>38</v>
@@ -4243,7 +4243,7 @@
         <v>37</v>
       </c>
       <c r="F13">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G13" t="s">
         <v>38</v>
@@ -4269,7 +4269,7 @@
         <v>37</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
         <v>38</v>
@@ -4295,7 +4295,7 @@
         <v>37</v>
       </c>
       <c r="F15">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
         <v>38</v>
@@ -4321,7 +4321,7 @@
         <v>37</v>
       </c>
       <c r="F16">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
         <v>38</v>
@@ -4347,7 +4347,7 @@
         <v>37</v>
       </c>
       <c r="F17">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="G17" t="s">
         <v>38</v>
@@ -4373,7 +4373,7 @@
         <v>37</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G18" t="s">
         <v>38</v>
@@ -4399,7 +4399,7 @@
         <v>37</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
         <v>38</v>
@@ -4425,7 +4425,7 @@
         <v>37</v>
       </c>
       <c r="F20">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
         <v>38</v>
@@ -4451,7 +4451,7 @@
         <v>37</v>
       </c>
       <c r="F21">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
         <v>38</v>
@@ -4503,7 +4503,7 @@
         <v>37</v>
       </c>
       <c r="F23">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
         <v>38</v>
@@ -4529,7 +4529,7 @@
         <v>37</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G24" t="s">
         <v>38</v>
@@ -4555,7 +4555,7 @@
         <v>37</v>
       </c>
       <c r="F25">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
         <v>38</v>
@@ -4581,7 +4581,7 @@
         <v>37</v>
       </c>
       <c r="F26">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G26" t="s">
         <v>38</v>
@@ -4607,7 +4607,7 @@
         <v>37</v>
       </c>
       <c r="F27">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>38</v>
@@ -4633,7 +4633,7 @@
         <v>37</v>
       </c>
       <c r="F28">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G28" t="s">
         <v>38</v>
@@ -4659,7 +4659,7 @@
         <v>37</v>
       </c>
       <c r="F29">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G29" t="s">
         <v>38</v>
@@ -4685,7 +4685,7 @@
         <v>37</v>
       </c>
       <c r="F30">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
         <v>38</v>
@@ -4711,7 +4711,7 @@
         <v>37</v>
       </c>
       <c r="F31">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G31" t="s">
         <v>38</v>
@@ -4737,7 +4737,7 @@
         <v>37</v>
       </c>
       <c r="F32">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G32" t="s">
         <v>38</v>
@@ -4763,7 +4763,7 @@
         <v>37</v>
       </c>
       <c r="F33">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
         <v>38</v>
@@ -4789,7 +4789,7 @@
         <v>37</v>
       </c>
       <c r="F34">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G34" t="s">
         <v>38</v>
@@ -4815,7 +4815,7 @@
         <v>37</v>
       </c>
       <c r="F35">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G35" t="s">
         <v>38</v>
@@ -4841,7 +4841,7 @@
         <v>37</v>
       </c>
       <c r="F36">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="G36" t="s">
         <v>38</v>
@@ -4867,7 +4867,7 @@
         <v>37</v>
       </c>
       <c r="F37">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="G37" t="s">
         <v>38</v>
@@ -4893,7 +4893,7 @@
         <v>37</v>
       </c>
       <c r="F38">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G38" t="s">
         <v>38</v>
@@ -4919,7 +4919,7 @@
         <v>37</v>
       </c>
       <c r="F39">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G39" t="s">
         <v>38</v>
@@ -4945,7 +4945,7 @@
         <v>37</v>
       </c>
       <c r="F40">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="G40" t="s">
         <v>38</v>
@@ -4971,7 +4971,7 @@
         <v>37</v>
       </c>
       <c r="F41">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="G41" t="s">
         <v>38</v>
@@ -4997,7 +4997,7 @@
         <v>37</v>
       </c>
       <c r="F42">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G42" t="s">
         <v>38</v>
@@ -5023,7 +5023,7 @@
         <v>37</v>
       </c>
       <c r="F43">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G43" t="s">
         <v>38</v>
@@ -5049,7 +5049,7 @@
         <v>37</v>
       </c>
       <c r="F44">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="G44" t="s">
         <v>38</v>
@@ -5075,7 +5075,7 @@
         <v>37</v>
       </c>
       <c r="F45">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G45" t="s">
         <v>38</v>
@@ -5101,7 +5101,7 @@
         <v>37</v>
       </c>
       <c r="F46">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s">
         <v>38</v>
@@ -5127,7 +5127,7 @@
         <v>37</v>
       </c>
       <c r="F47">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G47" t="s">
         <v>38</v>
@@ -5153,7 +5153,7 @@
         <v>37</v>
       </c>
       <c r="F48">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G48" t="s">
         <v>38</v>
@@ -5179,7 +5179,7 @@
         <v>37</v>
       </c>
       <c r="F49">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G49" t="s">
         <v>38</v>
@@ -5205,7 +5205,7 @@
         <v>37</v>
       </c>
       <c r="F50">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G50" t="s">
         <v>38</v>
@@ -5231,7 +5231,7 @@
         <v>37</v>
       </c>
       <c r="F51">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G51" t="s">
         <v>38</v>
@@ -5257,7 +5257,7 @@
         <v>37</v>
       </c>
       <c r="F52">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G52" t="s">
         <v>38</v>
@@ -5283,7 +5283,7 @@
         <v>37</v>
       </c>
       <c r="F53">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G53" t="s">
         <v>38</v>
@@ -5309,7 +5309,7 @@
         <v>37</v>
       </c>
       <c r="F54">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G54" t="s">
         <v>38</v>
@@ -5335,7 +5335,7 @@
         <v>37</v>
       </c>
       <c r="F55">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G55" t="s">
         <v>38</v>
@@ -5361,7 +5361,7 @@
         <v>37</v>
       </c>
       <c r="F56">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G56" t="s">
         <v>38</v>
@@ -5387,7 +5387,7 @@
         <v>37</v>
       </c>
       <c r="F57">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G57" t="s">
         <v>38</v>
@@ -5413,7 +5413,7 @@
         <v>37</v>
       </c>
       <c r="F58">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G58" t="s">
         <v>38</v>
@@ -5439,7 +5439,7 @@
         <v>37</v>
       </c>
       <c r="F59">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G59" t="s">
         <v>38</v>
@@ -5465,7 +5465,7 @@
         <v>37</v>
       </c>
       <c r="F60">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G60" t="s">
         <v>38</v>
@@ -5491,7 +5491,7 @@
         <v>37</v>
       </c>
       <c r="F61">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G61" t="s">
         <v>38</v>
@@ -5517,7 +5517,7 @@
         <v>37</v>
       </c>
       <c r="F62">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G62" t="s">
         <v>38</v>
@@ -5543,7 +5543,7 @@
         <v>37</v>
       </c>
       <c r="F63">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G63" t="s">
         <v>38</v>
@@ -5569,7 +5569,7 @@
         <v>37</v>
       </c>
       <c r="F64">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G64" t="s">
         <v>38</v>
@@ -5595,7 +5595,7 @@
         <v>37</v>
       </c>
       <c r="F65">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G65" t="s">
         <v>38</v>
@@ -5621,7 +5621,7 @@
         <v>37</v>
       </c>
       <c r="F66">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G66" t="s">
         <v>38</v>
@@ -5647,7 +5647,7 @@
         <v>37</v>
       </c>
       <c r="F67">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G67" t="s">
         <v>38</v>
@@ -5673,7 +5673,7 @@
         <v>37</v>
       </c>
       <c r="F68">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G68" t="s">
         <v>38</v>
@@ -5699,7 +5699,7 @@
         <v>37</v>
       </c>
       <c r="F69">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G69" t="s">
         <v>38</v>
@@ -5725,7 +5725,7 @@
         <v>37</v>
       </c>
       <c r="F70">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G70" t="s">
         <v>38</v>
@@ -5751,7 +5751,7 @@
         <v>37</v>
       </c>
       <c r="F71">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G71" t="s">
         <v>38</v>
@@ -5777,7 +5777,7 @@
         <v>37</v>
       </c>
       <c r="F72">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G72" t="s">
         <v>38</v>
@@ -5803,7 +5803,7 @@
         <v>37</v>
       </c>
       <c r="F73">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G73" t="s">
         <v>38</v>
@@ -5829,7 +5829,7 @@
         <v>37</v>
       </c>
       <c r="F74">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G74" t="s">
         <v>38</v>
@@ -5855,7 +5855,7 @@
         <v>37</v>
       </c>
       <c r="F75">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G75" t="s">
         <v>38</v>
@@ -5881,7 +5881,7 @@
         <v>37</v>
       </c>
       <c r="F76">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G76" t="s">
         <v>38</v>
@@ -5907,7 +5907,7 @@
         <v>37</v>
       </c>
       <c r="F77">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G77" t="s">
         <v>38</v>
@@ -5933,7 +5933,7 @@
         <v>37</v>
       </c>
       <c r="F78">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G78" t="s">
         <v>38</v>
@@ -5959,7 +5959,7 @@
         <v>37</v>
       </c>
       <c r="F79">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G79" t="s">
         <v>38</v>
@@ -5985,7 +5985,7 @@
         <v>37</v>
       </c>
       <c r="F80">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G80" t="s">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>37</v>
       </c>
       <c r="F81">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G81" t="s">
         <v>38</v>
@@ -6037,7 +6037,7 @@
         <v>37</v>
       </c>
       <c r="F82">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G82" t="s">
         <v>38</v>
@@ -6063,7 +6063,7 @@
         <v>37</v>
       </c>
       <c r="F83">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G83" t="s">
         <v>38</v>
@@ -6089,7 +6089,7 @@
         <v>37</v>
       </c>
       <c r="F84">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="G84" t="s">
         <v>38</v>
@@ -6115,7 +6115,7 @@
         <v>37</v>
       </c>
       <c r="F85">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G85" t="s">
         <v>38</v>
@@ -6141,7 +6141,7 @@
         <v>37</v>
       </c>
       <c r="F86">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G86" t="s">
         <v>38</v>
@@ -6193,7 +6193,7 @@
         <v>37</v>
       </c>
       <c r="F88">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G88" t="s">
         <v>38</v>
@@ -6219,7 +6219,7 @@
         <v>37</v>
       </c>
       <c r="F89">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G89" t="s">
         <v>38</v>
@@ -6245,7 +6245,7 @@
         <v>37</v>
       </c>
       <c r="F90">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="G90" t="s">
         <v>38</v>
@@ -6271,7 +6271,7 @@
         <v>37</v>
       </c>
       <c r="F91">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G91" t="s">
         <v>38</v>
@@ -6297,7 +6297,7 @@
         <v>37</v>
       </c>
       <c r="F92">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="G92" t="s">
         <v>38</v>
@@ -6323,7 +6323,7 @@
         <v>37</v>
       </c>
       <c r="F93">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G93" t="s">
         <v>38</v>
@@ -6349,7 +6349,7 @@
         <v>37</v>
       </c>
       <c r="F94">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G94" t="s">
         <v>38</v>
@@ -6375,7 +6375,7 @@
         <v>37</v>
       </c>
       <c r="F95">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G95" t="s">
         <v>38</v>
@@ -6401,7 +6401,7 @@
         <v>37</v>
       </c>
       <c r="F96">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G96" t="s">
         <v>38</v>
@@ -6427,7 +6427,7 @@
         <v>37</v>
       </c>
       <c r="F97">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G97" t="s">
         <v>38</v>
@@ -6453,7 +6453,7 @@
         <v>37</v>
       </c>
       <c r="F98">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G98" t="s">
         <v>38</v>
@@ -6479,7 +6479,7 @@
         <v>37</v>
       </c>
       <c r="F99">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G99" t="s">
         <v>38</v>
@@ -6505,7 +6505,7 @@
         <v>37</v>
       </c>
       <c r="F100">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G100" t="s">
         <v>38</v>
@@ -6531,7 +6531,7 @@
         <v>37</v>
       </c>
       <c r="F101">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G101" t="s">
         <v>38</v>
@@ -6557,7 +6557,7 @@
         <v>37</v>
       </c>
       <c r="F102">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G102" t="s">
         <v>38</v>
@@ -6583,7 +6583,7 @@
         <v>37</v>
       </c>
       <c r="F103">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G103" t="s">
         <v>38</v>
@@ -6609,7 +6609,7 @@
         <v>37</v>
       </c>
       <c r="F104">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G104" t="s">
         <v>38</v>
@@ -6635,7 +6635,7 @@
         <v>37</v>
       </c>
       <c r="F105">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G105" t="s">
         <v>38</v>
@@ -6661,7 +6661,7 @@
         <v>37</v>
       </c>
       <c r="F106">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G106" t="s">
         <v>38</v>
@@ -6687,7 +6687,7 @@
         <v>37</v>
       </c>
       <c r="F107">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="G107" t="s">
         <v>38</v>
@@ -6713,7 +6713,7 @@
         <v>37</v>
       </c>
       <c r="F108">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="G108" t="s">
         <v>38</v>
@@ -6739,7 +6739,7 @@
         <v>37</v>
       </c>
       <c r="F109">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G109" t="s">
         <v>38</v>
@@ -6765,7 +6765,7 @@
         <v>37</v>
       </c>
       <c r="F110">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G110" t="s">
         <v>38</v>
@@ -6791,7 +6791,7 @@
         <v>37</v>
       </c>
       <c r="F111">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G111" t="s">
         <v>38</v>
@@ -6817,7 +6817,7 @@
         <v>37</v>
       </c>
       <c r="F112">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G112" t="s">
         <v>38</v>
@@ -6843,7 +6843,7 @@
         <v>37</v>
       </c>
       <c r="F113">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G113" t="s">
         <v>38</v>
@@ -6869,7 +6869,7 @@
         <v>37</v>
       </c>
       <c r="F114">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G114" t="s">
         <v>38</v>
@@ -6895,7 +6895,7 @@
         <v>37</v>
       </c>
       <c r="F115">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G115" t="s">
         <v>38</v>
@@ -6921,7 +6921,7 @@
         <v>37</v>
       </c>
       <c r="F116">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G116" t="s">
         <v>38</v>
@@ -6947,7 +6947,7 @@
         <v>37</v>
       </c>
       <c r="F117">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="G117" t="s">
         <v>38</v>
@@ -6973,7 +6973,7 @@
         <v>37</v>
       </c>
       <c r="F118">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G118" t="s">
         <v>38</v>
@@ -6999,7 +6999,7 @@
         <v>37</v>
       </c>
       <c r="F119">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G119" t="s">
         <v>38</v>
@@ -7025,7 +7025,7 @@
         <v>37</v>
       </c>
       <c r="F120">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G120" t="s">
         <v>38</v>
@@ -7051,7 +7051,7 @@
         <v>37</v>
       </c>
       <c r="F121">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G121" t="s">
         <v>38</v>
@@ -7077,7 +7077,7 @@
         <v>37</v>
       </c>
       <c r="F122">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G122" t="s">
         <v>38</v>
@@ -7129,7 +7129,7 @@
         <v>37</v>
       </c>
       <c r="F124">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G124" t="s">
         <v>38</v>
@@ -7155,7 +7155,7 @@
         <v>37</v>
       </c>
       <c r="F125">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G125" t="s">
         <v>38</v>
@@ -7181,7 +7181,7 @@
         <v>37</v>
       </c>
       <c r="F126">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G126" t="s">
         <v>38</v>
@@ -7207,7 +7207,7 @@
         <v>37</v>
       </c>
       <c r="F127">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G127" t="s">
         <v>38</v>
@@ -7233,7 +7233,7 @@
         <v>37</v>
       </c>
       <c r="F128">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G128" t="s">
         <v>38</v>
@@ -7259,7 +7259,7 @@
         <v>37</v>
       </c>
       <c r="F129">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G129" t="s">
         <v>38</v>
@@ -7285,7 +7285,7 @@
         <v>37</v>
       </c>
       <c r="F130">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G130" t="s">
         <v>38</v>
@@ -7311,7 +7311,7 @@
         <v>37</v>
       </c>
       <c r="F131">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G131" t="s">
         <v>38</v>
@@ -7337,7 +7337,7 @@
         <v>37</v>
       </c>
       <c r="F132">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G132" t="s">
         <v>38</v>
@@ -7363,7 +7363,7 @@
         <v>37</v>
       </c>
       <c r="F133">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G133" t="s">
         <v>38</v>
@@ -7389,7 +7389,7 @@
         <v>37</v>
       </c>
       <c r="F134">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G134" t="s">
         <v>38</v>
@@ -7415,7 +7415,7 @@
         <v>37</v>
       </c>
       <c r="F135">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="G135" t="s">
         <v>38</v>
@@ -7441,7 +7441,7 @@
         <v>37</v>
       </c>
       <c r="F136">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G136" t="s">
         <v>38</v>
@@ -7467,7 +7467,7 @@
         <v>37</v>
       </c>
       <c r="F137">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G137" t="s">
         <v>38</v>
@@ -7493,7 +7493,7 @@
         <v>37</v>
       </c>
       <c r="F138">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G138" t="s">
         <v>38</v>
@@ -7519,7 +7519,7 @@
         <v>37</v>
       </c>
       <c r="F139">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="G139" t="s">
         <v>38</v>
@@ -7545,7 +7545,7 @@
         <v>37</v>
       </c>
       <c r="F140">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="G140" t="s">
         <v>38</v>
@@ -7571,7 +7571,7 @@
         <v>37</v>
       </c>
       <c r="F141">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G141" t="s">
         <v>38</v>
@@ -7597,7 +7597,7 @@
         <v>37</v>
       </c>
       <c r="F142">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G142" t="s">
         <v>38</v>
@@ -7623,7 +7623,7 @@
         <v>37</v>
       </c>
       <c r="F143">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G143" t="s">
         <v>38</v>
@@ -7649,7 +7649,7 @@
         <v>37</v>
       </c>
       <c r="F144">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G144" t="s">
         <v>38</v>
@@ -7675,7 +7675,7 @@
         <v>37</v>
       </c>
       <c r="F145">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G145" t="s">
         <v>38</v>
@@ -7701,7 +7701,7 @@
         <v>37</v>
       </c>
       <c r="F146">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G146" t="s">
         <v>38</v>
@@ -7727,7 +7727,7 @@
         <v>37</v>
       </c>
       <c r="F147">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G147" t="s">
         <v>38</v>
@@ -7753,7 +7753,7 @@
         <v>37</v>
       </c>
       <c r="F148">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="G148" t="s">
         <v>38</v>
@@ -7779,7 +7779,7 @@
         <v>37</v>
       </c>
       <c r="F149">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G149" t="s">
         <v>38</v>
@@ -7805,7 +7805,7 @@
         <v>37</v>
       </c>
       <c r="F150">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G150" t="s">
         <v>38</v>
@@ -7831,7 +7831,7 @@
         <v>37</v>
       </c>
       <c r="F151">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G151" t="s">
         <v>38</v>
@@ -7857,7 +7857,7 @@
         <v>37</v>
       </c>
       <c r="F152">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G152" t="s">
         <v>38</v>
@@ -7883,7 +7883,7 @@
         <v>37</v>
       </c>
       <c r="F153">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="G153" t="s">
         <v>38</v>
@@ -7909,7 +7909,7 @@
         <v>37</v>
       </c>
       <c r="F154">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G154" t="s">
         <v>38</v>
@@ -7935,7 +7935,7 @@
         <v>37</v>
       </c>
       <c r="F155">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G155" t="s">
         <v>38</v>
@@ -7961,7 +7961,7 @@
         <v>37</v>
       </c>
       <c r="F156">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G156" t="s">
         <v>38</v>
@@ -8039,7 +8039,7 @@
         <v>37</v>
       </c>
       <c r="F159">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G159" t="s">
         <v>38</v>
@@ -8065,7 +8065,7 @@
         <v>37</v>
       </c>
       <c r="F160">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G160" t="s">
         <v>38</v>
@@ -8091,7 +8091,7 @@
         <v>37</v>
       </c>
       <c r="F161">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G161" t="s">
         <v>38</v>
@@ -8117,7 +8117,7 @@
         <v>37</v>
       </c>
       <c r="F162">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G162" t="s">
         <v>38</v>
@@ -8143,7 +8143,7 @@
         <v>37</v>
       </c>
       <c r="F163">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G163" t="s">
         <v>38</v>
@@ -8169,7 +8169,7 @@
         <v>37</v>
       </c>
       <c r="F164">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="G164" t="s">
         <v>38</v>
@@ -8195,7 +8195,7 @@
         <v>37</v>
       </c>
       <c r="F165">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G165" t="s">
         <v>38</v>
@@ -8221,7 +8221,7 @@
         <v>37</v>
       </c>
       <c r="F166">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="G166" t="s">
         <v>38</v>
@@ -8247,7 +8247,7 @@
         <v>37</v>
       </c>
       <c r="F167">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G167" t="s">
         <v>38</v>
@@ -8273,7 +8273,7 @@
         <v>37</v>
       </c>
       <c r="F168">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G168" t="s">
         <v>38</v>
@@ -8299,7 +8299,7 @@
         <v>37</v>
       </c>
       <c r="F169">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G169" t="s">
         <v>38</v>
@@ -8325,7 +8325,7 @@
         <v>37</v>
       </c>
       <c r="F170">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G170" t="s">
         <v>38</v>
@@ -8351,7 +8351,7 @@
         <v>37</v>
       </c>
       <c r="F171">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G171" t="s">
         <v>38</v>
@@ -8377,7 +8377,7 @@
         <v>37</v>
       </c>
       <c r="F172">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="G172" t="s">
         <v>38</v>
@@ -8403,7 +8403,7 @@
         <v>37</v>
       </c>
       <c r="F173">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G173" t="s">
         <v>38</v>
@@ -8429,7 +8429,7 @@
         <v>37</v>
       </c>
       <c r="F174">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G174" t="s">
         <v>38</v>
@@ -8455,7 +8455,7 @@
         <v>37</v>
       </c>
       <c r="F175">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G175" t="s">
         <v>38</v>
@@ -8481,7 +8481,7 @@
         <v>37</v>
       </c>
       <c r="F176">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G176" t="s">
         <v>38</v>
@@ -8507,7 +8507,7 @@
         <v>37</v>
       </c>
       <c r="F177">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="G177" t="s">
         <v>38</v>
@@ -8533,7 +8533,7 @@
         <v>37</v>
       </c>
       <c r="F178">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G178" t="s">
         <v>38</v>
@@ -8559,7 +8559,7 @@
         <v>37</v>
       </c>
       <c r="F179">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G179" t="s">
         <v>38</v>
@@ -8585,7 +8585,7 @@
         <v>37</v>
       </c>
       <c r="F180">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G180" t="s">
         <v>38</v>
@@ -8611,7 +8611,7 @@
         <v>37</v>
       </c>
       <c r="F181">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G181" t="s">
         <v>38</v>
@@ -8637,7 +8637,7 @@
         <v>37</v>
       </c>
       <c r="F182">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G182" t="s">
         <v>38</v>
@@ -8663,7 +8663,7 @@
         <v>37</v>
       </c>
       <c r="F183">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G183" t="s">
         <v>38</v>
@@ -8689,7 +8689,7 @@
         <v>37</v>
       </c>
       <c r="F184">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G184" t="s">
         <v>38</v>
@@ -8715,7 +8715,7 @@
         <v>37</v>
       </c>
       <c r="F185">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G185" t="s">
         <v>38</v>
@@ -8767,7 +8767,7 @@
         <v>37</v>
       </c>
       <c r="F187">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="G187" t="s">
         <v>38</v>
@@ -8793,7 +8793,7 @@
         <v>37</v>
       </c>
       <c r="F188">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G188" t="s">
         <v>38</v>
@@ -8819,7 +8819,7 @@
         <v>37</v>
       </c>
       <c r="F189">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G189" t="s">
         <v>38</v>
@@ -8871,7 +8871,7 @@
         <v>37</v>
       </c>
       <c r="F191">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G191" t="s">
         <v>38</v>
@@ -8897,7 +8897,7 @@
         <v>37</v>
       </c>
       <c r="F192">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G192" t="s">
         <v>38</v>
@@ -8923,7 +8923,7 @@
         <v>37</v>
       </c>
       <c r="F193">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G193" t="s">
         <v>38</v>
@@ -8949,7 +8949,7 @@
         <v>37</v>
       </c>
       <c r="F194">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G194" t="s">
         <v>38</v>
@@ -8975,7 +8975,7 @@
         <v>37</v>
       </c>
       <c r="F195">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G195" t="s">
         <v>38</v>
@@ -9001,7 +9001,7 @@
         <v>37</v>
       </c>
       <c r="F196">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G196" t="s">
         <v>38</v>
@@ -9027,7 +9027,7 @@
         <v>37</v>
       </c>
       <c r="F197">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G197" t="s">
         <v>38</v>
@@ -9053,7 +9053,7 @@
         <v>37</v>
       </c>
       <c r="F198">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G198" t="s">
         <v>38</v>
@@ -9079,7 +9079,7 @@
         <v>37</v>
       </c>
       <c r="F199">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="G199" t="s">
         <v>38</v>
@@ -9105,7 +9105,7 @@
         <v>37</v>
       </c>
       <c r="F200">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G200" t="s">
         <v>38</v>
@@ -9131,7 +9131,7 @@
         <v>37</v>
       </c>
       <c r="F201">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G201" t="s">
         <v>38</v>
@@ -9157,7 +9157,7 @@
         <v>37</v>
       </c>
       <c r="F202">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G202" t="s">
         <v>38</v>
@@ -9183,7 +9183,7 @@
         <v>37</v>
       </c>
       <c r="F203">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G203" t="s">
         <v>38</v>
@@ -9209,7 +9209,7 @@
         <v>37</v>
       </c>
       <c r="F204">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G204" t="s">
         <v>38</v>
@@ -9235,7 +9235,7 @@
         <v>37</v>
       </c>
       <c r="F205">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G205" t="s">
         <v>38</v>
@@ -9261,7 +9261,7 @@
         <v>37</v>
       </c>
       <c r="F206">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="G206" t="s">
         <v>38</v>
@@ -9287,7 +9287,7 @@
         <v>37</v>
       </c>
       <c r="F207">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G207" t="s">
         <v>38</v>
@@ -9313,7 +9313,7 @@
         <v>37</v>
       </c>
       <c r="F208">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="G208" t="s">
         <v>38</v>
@@ -9339,7 +9339,7 @@
         <v>37</v>
       </c>
       <c r="F209">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G209" t="s">
         <v>38</v>
@@ -9365,7 +9365,7 @@
         <v>37</v>
       </c>
       <c r="F210">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="G210" t="s">
         <v>38</v>
@@ -9391,7 +9391,7 @@
         <v>37</v>
       </c>
       <c r="F211">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G211" t="s">
         <v>38</v>
@@ -9417,7 +9417,7 @@
         <v>37</v>
       </c>
       <c r="F212">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G212" t="s">
         <v>38</v>
@@ -9443,7 +9443,7 @@
         <v>37</v>
       </c>
       <c r="F213">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G213" t="s">
         <v>38</v>
@@ -9469,7 +9469,7 @@
         <v>37</v>
       </c>
       <c r="F214">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G214" t="s">
         <v>38</v>
@@ -9495,7 +9495,7 @@
         <v>37</v>
       </c>
       <c r="F215">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G215" t="s">
         <v>38</v>
@@ -9521,7 +9521,7 @@
         <v>37</v>
       </c>
       <c r="F216">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G216" t="s">
         <v>38</v>
@@ -9547,7 +9547,7 @@
         <v>37</v>
       </c>
       <c r="F217">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="G217" t="s">
         <v>38</v>
@@ -9573,7 +9573,7 @@
         <v>37</v>
       </c>
       <c r="F218">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G218" t="s">
         <v>38</v>
@@ -9599,7 +9599,7 @@
         <v>37</v>
       </c>
       <c r="F219">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="G219" t="s">
         <v>38</v>
@@ -9625,7 +9625,7 @@
         <v>37</v>
       </c>
       <c r="F220">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="G220" t="s">
         <v>38</v>
@@ -9651,7 +9651,7 @@
         <v>37</v>
       </c>
       <c r="F221">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G221" t="s">
         <v>38</v>
@@ -9677,7 +9677,7 @@
         <v>37</v>
       </c>
       <c r="F222">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G222" t="s">
         <v>38</v>
@@ -9703,7 +9703,7 @@
         <v>37</v>
       </c>
       <c r="F223">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G223" t="s">
         <v>38</v>
@@ -9729,7 +9729,7 @@
         <v>37</v>
       </c>
       <c r="F224">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G224" t="s">
         <v>38</v>
@@ -9755,7 +9755,7 @@
         <v>37</v>
       </c>
       <c r="F225">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G225" t="s">
         <v>38</v>
@@ -9781,7 +9781,7 @@
         <v>37</v>
       </c>
       <c r="F226">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G226" t="s">
         <v>38</v>
@@ -9807,7 +9807,7 @@
         <v>37</v>
       </c>
       <c r="F227">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G227" t="s">
         <v>38</v>
@@ -9833,7 +9833,7 @@
         <v>37</v>
       </c>
       <c r="F228">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G228" t="s">
         <v>38</v>
@@ -9859,7 +9859,7 @@
         <v>37</v>
       </c>
       <c r="F229">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G229" t="s">
         <v>38</v>
@@ -9885,7 +9885,7 @@
         <v>37</v>
       </c>
       <c r="F230">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G230" t="s">
         <v>38</v>
@@ -9911,7 +9911,7 @@
         <v>37</v>
       </c>
       <c r="F231">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G231" t="s">
         <v>38</v>
@@ -9937,7 +9937,7 @@
         <v>37</v>
       </c>
       <c r="F232">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G232" t="s">
         <v>38</v>
@@ -9963,7 +9963,7 @@
         <v>37</v>
       </c>
       <c r="F233">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="G233" t="s">
         <v>38</v>
@@ -9989,7 +9989,7 @@
         <v>37</v>
       </c>
       <c r="F234">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G234" t="s">
         <v>38</v>
@@ -10015,7 +10015,7 @@
         <v>37</v>
       </c>
       <c r="F235">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G235" t="s">
         <v>38</v>
@@ -10041,7 +10041,7 @@
         <v>37</v>
       </c>
       <c r="F236">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="G236" t="s">
         <v>38</v>
@@ -10067,7 +10067,7 @@
         <v>37</v>
       </c>
       <c r="F237">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G237" t="s">
         <v>38</v>
@@ -10093,7 +10093,7 @@
         <v>37</v>
       </c>
       <c r="F238">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G238" t="s">
         <v>38</v>
@@ -10119,7 +10119,7 @@
         <v>37</v>
       </c>
       <c r="F239">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G239" t="s">
         <v>38</v>
@@ -10145,7 +10145,7 @@
         <v>37</v>
       </c>
       <c r="F240">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="G240" t="s">
         <v>38</v>
@@ -10171,7 +10171,7 @@
         <v>37</v>
       </c>
       <c r="F241">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G241" t="s">
         <v>38</v>
@@ -10197,7 +10197,7 @@
         <v>37</v>
       </c>
       <c r="F242">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G242" t="s">
         <v>38</v>
@@ -10223,7 +10223,7 @@
         <v>37</v>
       </c>
       <c r="F243">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="G243" t="s">
         <v>38</v>
@@ -10249,7 +10249,7 @@
         <v>37</v>
       </c>
       <c r="F244">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G244" t="s">
         <v>38</v>
@@ -10275,7 +10275,7 @@
         <v>37</v>
       </c>
       <c r="F245">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G245" t="s">
         <v>38</v>
@@ -10301,7 +10301,7 @@
         <v>37</v>
       </c>
       <c r="F246">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G246" t="s">
         <v>38</v>
@@ -10327,7 +10327,7 @@
         <v>37</v>
       </c>
       <c r="F247">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G247" t="s">
         <v>38</v>
@@ -10353,7 +10353,7 @@
         <v>37</v>
       </c>
       <c r="F248">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G248" t="s">
         <v>38</v>
@@ -10379,7 +10379,7 @@
         <v>37</v>
       </c>
       <c r="F249">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="G249" t="s">
         <v>38</v>
@@ -10431,7 +10431,7 @@
         <v>37</v>
       </c>
       <c r="F251">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G251" t="s">
         <v>38</v>
@@ -10457,7 +10457,7 @@
         <v>37</v>
       </c>
       <c r="F252">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G252" t="s">
         <v>38</v>
@@ -10483,7 +10483,7 @@
         <v>37</v>
       </c>
       <c r="F253">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G253" t="s">
         <v>38</v>
@@ -10509,7 +10509,7 @@
         <v>37</v>
       </c>
       <c r="F254">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G254" t="s">
         <v>38</v>
@@ -10561,7 +10561,7 @@
         <v>37</v>
       </c>
       <c r="F256">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G256" t="s">
         <v>38</v>
@@ -10587,7 +10587,7 @@
         <v>37</v>
       </c>
       <c r="F257">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G257" t="s">
         <v>38</v>
@@ -10613,7 +10613,7 @@
         <v>37</v>
       </c>
       <c r="F258">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="G258" t="s">
         <v>38</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="F259">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="G259" t="s">
         <v>38</v>
@@ -10665,7 +10665,7 @@
         <v>37</v>
       </c>
       <c r="F260">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G260" t="s">
         <v>38</v>
@@ -10691,7 +10691,7 @@
         <v>37</v>
       </c>
       <c r="F261">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G261" t="s">
         <v>38</v>
@@ -10717,7 +10717,7 @@
         <v>37</v>
       </c>
       <c r="F262">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G262" t="s">
         <v>38</v>
@@ -10743,7 +10743,7 @@
         <v>37</v>
       </c>
       <c r="F263">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G263" t="s">
         <v>38</v>
@@ -10769,7 +10769,7 @@
         <v>37</v>
       </c>
       <c r="F264">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G264" t="s">
         <v>38</v>
@@ -10795,7 +10795,7 @@
         <v>37</v>
       </c>
       <c r="F265">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="G265" t="s">
         <v>38</v>
@@ -10821,7 +10821,7 @@
         <v>37</v>
       </c>
       <c r="F266">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G266" t="s">
         <v>38</v>
@@ -10847,7 +10847,7 @@
         <v>37</v>
       </c>
       <c r="F267">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G267" t="s">
         <v>38</v>
@@ -10873,7 +10873,7 @@
         <v>37</v>
       </c>
       <c r="F268">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="G268" t="s">
         <v>38</v>
@@ -10899,7 +10899,7 @@
         <v>37</v>
       </c>
       <c r="F269">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G269" t="s">
         <v>38</v>
@@ -10925,7 +10925,7 @@
         <v>37</v>
       </c>
       <c r="F270">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G270" t="s">
         <v>38</v>
@@ -10951,7 +10951,7 @@
         <v>37</v>
       </c>
       <c r="F271">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G271" t="s">
         <v>38</v>
@@ -10977,7 +10977,7 @@
         <v>37</v>
       </c>
       <c r="F272">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G272" t="s">
         <v>38</v>
@@ -11003,7 +11003,7 @@
         <v>37</v>
       </c>
       <c r="F273">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G273" t="s">
         <v>38</v>
@@ -11029,7 +11029,7 @@
         <v>37</v>
       </c>
       <c r="F274">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="G274" t="s">
         <v>38</v>
@@ -11055,7 +11055,7 @@
         <v>37</v>
       </c>
       <c r="F275">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G275" t="s">
         <v>38</v>
@@ -11081,7 +11081,7 @@
         <v>37</v>
       </c>
       <c r="F276">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G276" t="s">
         <v>38</v>
@@ -11107,7 +11107,7 @@
         <v>37</v>
       </c>
       <c r="F277">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G277" t="s">
         <v>38</v>
@@ -11133,7 +11133,7 @@
         <v>37</v>
       </c>
       <c r="F278">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G278" t="s">
         <v>38</v>
@@ -11159,7 +11159,7 @@
         <v>37</v>
       </c>
       <c r="F279">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G279" t="s">
         <v>38</v>
@@ -11185,7 +11185,7 @@
         <v>37</v>
       </c>
       <c r="F280">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G280" t="s">
         <v>38</v>
@@ -11211,7 +11211,7 @@
         <v>37</v>
       </c>
       <c r="F281">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G281" t="s">
         <v>38</v>
@@ -11263,7 +11263,7 @@
         <v>37</v>
       </c>
       <c r="F283">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G283" t="s">
         <v>38</v>
@@ -11289,7 +11289,7 @@
         <v>37</v>
       </c>
       <c r="F284">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G284" t="s">
         <v>38</v>
@@ -11315,7 +11315,7 @@
         <v>37</v>
       </c>
       <c r="F285">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G285" t="s">
         <v>38</v>
@@ -11341,7 +11341,7 @@
         <v>37</v>
       </c>
       <c r="F286">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G286" t="s">
         <v>38</v>
@@ -11367,7 +11367,7 @@
         <v>37</v>
       </c>
       <c r="F287">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G287" t="s">
         <v>38</v>
@@ -11393,7 +11393,7 @@
         <v>37</v>
       </c>
       <c r="F288">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G288" t="s">
         <v>38</v>
@@ -11419,7 +11419,7 @@
         <v>37</v>
       </c>
       <c r="F289">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="G289" t="s">
         <v>38</v>
@@ -11445,7 +11445,7 @@
         <v>37</v>
       </c>
       <c r="F290">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G290" t="s">
         <v>38</v>
@@ -11471,7 +11471,7 @@
         <v>37</v>
       </c>
       <c r="F291">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G291" t="s">
         <v>38</v>
@@ -11497,7 +11497,7 @@
         <v>37</v>
       </c>
       <c r="F292">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G292" t="s">
         <v>38</v>
@@ -11523,7 +11523,7 @@
         <v>37</v>
       </c>
       <c r="F293">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G293" t="s">
         <v>38</v>
@@ -11549,7 +11549,7 @@
         <v>37</v>
       </c>
       <c r="F294">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G294" t="s">
         <v>38</v>
@@ -11575,7 +11575,7 @@
         <v>37</v>
       </c>
       <c r="F295">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G295" t="s">
         <v>38</v>
@@ -11601,7 +11601,7 @@
         <v>37</v>
       </c>
       <c r="F296">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G296" t="s">
         <v>38</v>
@@ -11653,7 +11653,7 @@
         <v>37</v>
       </c>
       <c r="F298">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="G298" t="s">
         <v>38</v>
@@ -11679,7 +11679,7 @@
         <v>37</v>
       </c>
       <c r="F299">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G299" t="s">
         <v>38</v>
@@ -11705,7 +11705,7 @@
         <v>37</v>
       </c>
       <c r="F300">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="G300" t="s">
         <v>38</v>
@@ -11757,7 +11757,7 @@
         <v>37</v>
       </c>
       <c r="F302">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G302" t="s">
         <v>38</v>
@@ -11783,7 +11783,7 @@
         <v>37</v>
       </c>
       <c r="F303">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G303" t="s">
         <v>38</v>
@@ -11809,7 +11809,7 @@
         <v>37</v>
       </c>
       <c r="F304">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G304" t="s">
         <v>38</v>
@@ -11835,7 +11835,7 @@
         <v>37</v>
       </c>
       <c r="F305">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G305" t="s">
         <v>38</v>
@@ -11861,7 +11861,7 @@
         <v>37</v>
       </c>
       <c r="F306">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G306" t="s">
         <v>38</v>
@@ -11887,7 +11887,7 @@
         <v>37</v>
       </c>
       <c r="F307">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G307" t="s">
         <v>38</v>
@@ -11913,7 +11913,7 @@
         <v>37</v>
       </c>
       <c r="F308">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G308" t="s">
         <v>38</v>
@@ -11939,7 +11939,7 @@
         <v>37</v>
       </c>
       <c r="F309">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="G309" t="s">
         <v>38</v>
@@ -11965,7 +11965,7 @@
         <v>37</v>
       </c>
       <c r="F310">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G310" t="s">
         <v>38</v>
@@ -11991,7 +11991,7 @@
         <v>37</v>
       </c>
       <c r="F311">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G311" t="s">
         <v>38</v>
@@ -12017,7 +12017,7 @@
         <v>37</v>
       </c>
       <c r="F312">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G312" t="s">
         <v>38</v>
@@ -12043,7 +12043,7 @@
         <v>37</v>
       </c>
       <c r="F313">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G313" t="s">
         <v>38</v>
@@ -12069,7 +12069,7 @@
         <v>37</v>
       </c>
       <c r="F314">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G314" t="s">
         <v>38</v>
@@ -12095,7 +12095,7 @@
         <v>37</v>
       </c>
       <c r="F315">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G315" t="s">
         <v>38</v>
@@ -12121,7 +12121,7 @@
         <v>37</v>
       </c>
       <c r="F316">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="G316" t="s">
         <v>38</v>
@@ -12147,7 +12147,7 @@
         <v>37</v>
       </c>
       <c r="F317">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G317" t="s">
         <v>38</v>
@@ -12173,7 +12173,7 @@
         <v>37</v>
       </c>
       <c r="F318">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G318" t="s">
         <v>38</v>
@@ -12199,7 +12199,7 @@
         <v>37</v>
       </c>
       <c r="F319">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G319" t="s">
         <v>38</v>
@@ -12225,7 +12225,7 @@
         <v>37</v>
       </c>
       <c r="F320">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G320" t="s">
         <v>38</v>
@@ -12251,7 +12251,7 @@
         <v>37</v>
       </c>
       <c r="F321">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G321" t="s">
         <v>38</v>
@@ -12277,7 +12277,7 @@
         <v>37</v>
       </c>
       <c r="F322">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G322" t="s">
         <v>38</v>
@@ -12303,7 +12303,7 @@
         <v>37</v>
       </c>
       <c r="F323">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G323" t="s">
         <v>38</v>
@@ -12329,7 +12329,7 @@
         <v>37</v>
       </c>
       <c r="F324">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G324" t="s">
         <v>38</v>
@@ -12355,7 +12355,7 @@
         <v>37</v>
       </c>
       <c r="F325">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G325" t="s">
         <v>38</v>
@@ -12381,7 +12381,7 @@
         <v>37</v>
       </c>
       <c r="F326">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G326" t="s">
         <v>38</v>
@@ -12407,7 +12407,7 @@
         <v>37</v>
       </c>
       <c r="F327">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G327" t="s">
         <v>38</v>
@@ -12459,7 +12459,7 @@
         <v>37</v>
       </c>
       <c r="F329">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G329" t="s">
         <v>38</v>
@@ -12485,7 +12485,7 @@
         <v>37</v>
       </c>
       <c r="F330">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="G330" t="s">
         <v>38</v>
@@ -12511,7 +12511,7 @@
         <v>37</v>
       </c>
       <c r="F331">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G331" t="s">
         <v>38</v>
@@ -12537,7 +12537,7 @@
         <v>37</v>
       </c>
       <c r="F332">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G332" t="s">
         <v>38</v>
@@ -12563,7 +12563,7 @@
         <v>37</v>
       </c>
       <c r="F333">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G333" t="s">
         <v>38</v>
@@ -12589,7 +12589,7 @@
         <v>37</v>
       </c>
       <c r="F334">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G334" t="s">
         <v>38</v>
@@ -12641,7 +12641,7 @@
         <v>37</v>
       </c>
       <c r="F336">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G336" t="s">
         <v>38</v>
@@ -12667,7 +12667,7 @@
         <v>37</v>
       </c>
       <c r="F337">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G337" t="s">
         <v>38</v>
@@ -12693,7 +12693,7 @@
         <v>37</v>
       </c>
       <c r="F338">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G338" t="s">
         <v>38</v>
@@ -12719,7 +12719,7 @@
         <v>37</v>
       </c>
       <c r="F339">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G339" t="s">
         <v>38</v>
@@ -12745,7 +12745,7 @@
         <v>37</v>
       </c>
       <c r="F340">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G340" t="s">
         <v>38</v>
@@ -12771,7 +12771,7 @@
         <v>37</v>
       </c>
       <c r="F341">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G341" t="s">
         <v>38</v>
@@ -12797,7 +12797,7 @@
         <v>37</v>
       </c>
       <c r="F342">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G342" t="s">
         <v>38</v>
@@ -12823,7 +12823,7 @@
         <v>37</v>
       </c>
       <c r="F343">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G343" t="s">
         <v>38</v>
@@ -12849,7 +12849,7 @@
         <v>37</v>
       </c>
       <c r="F344">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="G344" t="s">
         <v>38</v>
@@ -12875,7 +12875,7 @@
         <v>37</v>
       </c>
       <c r="F345">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G345" t="s">
         <v>38</v>
@@ -12901,7 +12901,7 @@
         <v>37</v>
       </c>
       <c r="F346">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G346" t="s">
         <v>38</v>
@@ -12927,7 +12927,7 @@
         <v>37</v>
       </c>
       <c r="F347">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="G347" t="s">
         <v>38</v>
@@ -12953,7 +12953,7 @@
         <v>37</v>
       </c>
       <c r="F348">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="G348" t="s">
         <v>38</v>
@@ -12979,7 +12979,7 @@
         <v>37</v>
       </c>
       <c r="F349">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G349" t="s">
         <v>38</v>
@@ -13005,7 +13005,7 @@
         <v>37</v>
       </c>
       <c r="F350">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G350" t="s">
         <v>38</v>
@@ -13031,7 +13031,7 @@
         <v>37</v>
       </c>
       <c r="F351">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G351" t="s">
         <v>38</v>
@@ -13057,7 +13057,7 @@
         <v>37</v>
       </c>
       <c r="F352">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G352" t="s">
         <v>38</v>
@@ -13083,7 +13083,7 @@
         <v>37</v>
       </c>
       <c r="F353">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G353" t="s">
         <v>38</v>
@@ -13109,7 +13109,7 @@
         <v>37</v>
       </c>
       <c r="F354">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G354" t="s">
         <v>38</v>
@@ -13135,7 +13135,7 @@
         <v>37</v>
       </c>
       <c r="F355">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G355" t="s">
         <v>38</v>
@@ -13161,7 +13161,7 @@
         <v>37</v>
       </c>
       <c r="F356">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G356" t="s">
         <v>38</v>
@@ -13187,7 +13187,7 @@
         <v>37</v>
       </c>
       <c r="F357">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G357" t="s">
         <v>38</v>
@@ -13213,7 +13213,7 @@
         <v>37</v>
       </c>
       <c r="F358">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G358" t="s">
         <v>38</v>
@@ -13239,7 +13239,7 @@
         <v>37</v>
       </c>
       <c r="F359">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G359" t="s">
         <v>38</v>
@@ -13265,7 +13265,7 @@
         <v>37</v>
       </c>
       <c r="F360">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G360" t="s">
         <v>38</v>
@@ -13291,7 +13291,7 @@
         <v>37</v>
       </c>
       <c r="F361">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G361" t="s">
         <v>38</v>
@@ -13317,7 +13317,7 @@
         <v>37</v>
       </c>
       <c r="F362">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G362" t="s">
         <v>38</v>
@@ -13343,7 +13343,7 @@
         <v>37</v>
       </c>
       <c r="F363">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="G363" t="s">
         <v>38</v>
@@ -13369,7 +13369,7 @@
         <v>37</v>
       </c>
       <c r="F364">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G364" t="s">
         <v>38</v>
@@ -13395,7 +13395,7 @@
         <v>37</v>
       </c>
       <c r="F365">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="G365" t="s">
         <v>38</v>
@@ -13421,7 +13421,7 @@
         <v>37</v>
       </c>
       <c r="F366">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G366" t="s">
         <v>38</v>
@@ -13447,7 +13447,7 @@
         <v>37</v>
       </c>
       <c r="F367">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G367" t="s">
         <v>38</v>
@@ -13473,7 +13473,7 @@
         <v>37</v>
       </c>
       <c r="F368">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G368" t="s">
         <v>38</v>
@@ -13499,7 +13499,7 @@
         <v>37</v>
       </c>
       <c r="F369">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G369" t="s">
         <v>38</v>
@@ -13525,7 +13525,7 @@
         <v>37</v>
       </c>
       <c r="F370">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G370" t="s">
         <v>38</v>
@@ -13551,7 +13551,7 @@
         <v>37</v>
       </c>
       <c r="F371">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G371" t="s">
         <v>38</v>
@@ -13577,7 +13577,7 @@
         <v>37</v>
       </c>
       <c r="F372">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G372" t="s">
         <v>38</v>
@@ -13603,7 +13603,7 @@
         <v>37</v>
       </c>
       <c r="F373">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G373" t="s">
         <v>38</v>
@@ -13629,7 +13629,7 @@
         <v>37</v>
       </c>
       <c r="F374">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G374" t="s">
         <v>38</v>
@@ -13655,7 +13655,7 @@
         <v>37</v>
       </c>
       <c r="F375">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G375" t="s">
         <v>38</v>
@@ -13681,7 +13681,7 @@
         <v>37</v>
       </c>
       <c r="F376">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="G376" t="s">
         <v>38</v>
@@ -13707,7 +13707,7 @@
         <v>37</v>
       </c>
       <c r="F377">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="G377" t="s">
         <v>38</v>
@@ -13733,7 +13733,7 @@
         <v>37</v>
       </c>
       <c r="F378">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G378" t="s">
         <v>38</v>
@@ -13759,7 +13759,7 @@
         <v>37</v>
       </c>
       <c r="F379">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G379" t="s">
         <v>38</v>
@@ -13785,7 +13785,7 @@
         <v>37</v>
       </c>
       <c r="F380">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G380" t="s">
         <v>38</v>
@@ -13811,7 +13811,7 @@
         <v>37</v>
       </c>
       <c r="F381">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G381" t="s">
         <v>38</v>
@@ -13837,7 +13837,7 @@
         <v>37</v>
       </c>
       <c r="F382">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G382" t="s">
         <v>38</v>
@@ -13863,7 +13863,7 @@
         <v>37</v>
       </c>
       <c r="F383">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G383" t="s">
         <v>38</v>
@@ -13889,7 +13889,7 @@
         <v>37</v>
       </c>
       <c r="F384">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="G384" t="s">
         <v>38</v>
@@ -13915,7 +13915,7 @@
         <v>37</v>
       </c>
       <c r="F385">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G385" t="s">
         <v>38</v>
@@ -13941,7 +13941,7 @@
         <v>37</v>
       </c>
       <c r="F386">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G386" t="s">
         <v>38</v>
@@ -13967,7 +13967,7 @@
         <v>37</v>
       </c>
       <c r="F387">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G387" t="s">
         <v>38</v>
@@ -13993,7 +13993,7 @@
         <v>37</v>
       </c>
       <c r="F388">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G388" t="s">
         <v>38</v>
@@ -14019,7 +14019,7 @@
         <v>37</v>
       </c>
       <c r="F389">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G389" t="s">
         <v>38</v>
@@ -14045,7 +14045,7 @@
         <v>37</v>
       </c>
       <c r="F390">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G390" t="s">
         <v>38</v>
@@ -14071,7 +14071,7 @@
         <v>37</v>
       </c>
       <c r="F391">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G391" t="s">
         <v>38</v>
@@ -14097,7 +14097,7 @@
         <v>37</v>
       </c>
       <c r="F392">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G392" t="s">
         <v>38</v>
@@ -14123,7 +14123,7 @@
         <v>37</v>
       </c>
       <c r="F393">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="G393" t="s">
         <v>38</v>
@@ -14149,7 +14149,7 @@
         <v>37</v>
       </c>
       <c r="F394">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G394" t="s">
         <v>38</v>
@@ -14175,7 +14175,7 @@
         <v>37</v>
       </c>
       <c r="F395">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G395" t="s">
         <v>38</v>
@@ -14201,7 +14201,7 @@
         <v>37</v>
       </c>
       <c r="F396">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G396" t="s">
         <v>38</v>
@@ -14227,7 +14227,7 @@
         <v>37</v>
       </c>
       <c r="F397">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="G397" t="s">
         <v>38</v>
@@ -14253,7 +14253,7 @@
         <v>37</v>
       </c>
       <c r="F398">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G398" t="s">
         <v>38</v>
@@ -14279,7 +14279,7 @@
         <v>37</v>
       </c>
       <c r="F399">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G399" t="s">
         <v>38</v>
@@ -14305,7 +14305,7 @@
         <v>37</v>
       </c>
       <c r="F400">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G400" t="s">
         <v>38</v>
@@ -14331,7 +14331,7 @@
         <v>37</v>
       </c>
       <c r="F401">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G401" t="s">
         <v>38</v>
@@ -14357,7 +14357,7 @@
         <v>37</v>
       </c>
       <c r="F402">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G402" t="s">
         <v>38</v>
@@ -14383,7 +14383,7 @@
         <v>37</v>
       </c>
       <c r="F403">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G403" t="s">
         <v>38</v>
@@ -14409,7 +14409,7 @@
         <v>37</v>
       </c>
       <c r="F404">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G404" t="s">
         <v>38</v>
@@ -14435,7 +14435,7 @@
         <v>37</v>
       </c>
       <c r="F405">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G405" t="s">
         <v>38</v>
@@ -14461,7 +14461,7 @@
         <v>37</v>
       </c>
       <c r="F406">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G406" t="s">
         <v>38</v>
@@ -14487,7 +14487,7 @@
         <v>37</v>
       </c>
       <c r="F407">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G407" t="s">
         <v>38</v>
@@ -14513,7 +14513,7 @@
         <v>37</v>
       </c>
       <c r="F408">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G408" t="s">
         <v>38</v>
@@ -14539,7 +14539,7 @@
         <v>37</v>
       </c>
       <c r="F409">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="G409" t="s">
         <v>38</v>
@@ -14565,7 +14565,7 @@
         <v>37</v>
       </c>
       <c r="F410">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G410" t="s">
         <v>38</v>
@@ -14591,7 +14591,7 @@
         <v>37</v>
       </c>
       <c r="F411">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G411" t="s">
         <v>38</v>
@@ -14617,7 +14617,7 @@
         <v>37</v>
       </c>
       <c r="F412">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G412" t="s">
         <v>38</v>
@@ -14643,7 +14643,7 @@
         <v>37</v>
       </c>
       <c r="F413">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="G413" t="s">
         <v>38</v>
@@ -14669,7 +14669,7 @@
         <v>37</v>
       </c>
       <c r="F414">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G414" t="s">
         <v>38</v>
@@ -14695,7 +14695,7 @@
         <v>37</v>
       </c>
       <c r="F415">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G415" t="s">
         <v>38</v>
@@ -14721,7 +14721,7 @@
         <v>37</v>
       </c>
       <c r="F416">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G416" t="s">
         <v>38</v>
@@ -14747,7 +14747,7 @@
         <v>37</v>
       </c>
       <c r="F417">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G417" t="s">
         <v>38</v>
@@ -14773,7 +14773,7 @@
         <v>37</v>
       </c>
       <c r="F418">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G418" t="s">
         <v>38</v>
@@ -14799,7 +14799,7 @@
         <v>37</v>
       </c>
       <c r="F419">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G419" t="s">
         <v>38</v>
@@ -14825,7 +14825,7 @@
         <v>37</v>
       </c>
       <c r="F420">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G420" t="s">
         <v>38</v>
@@ -14851,7 +14851,7 @@
         <v>37</v>
       </c>
       <c r="F421">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G421" t="s">
         <v>38</v>
@@ -14877,7 +14877,7 @@
         <v>37</v>
       </c>
       <c r="F422">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="G422" t="s">
         <v>38</v>
@@ -14903,7 +14903,7 @@
         <v>37</v>
       </c>
       <c r="F423">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G423" t="s">
         <v>38</v>
@@ -14929,7 +14929,7 @@
         <v>37</v>
       </c>
       <c r="F424">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G424" t="s">
         <v>38</v>
@@ -14955,7 +14955,7 @@
         <v>37</v>
       </c>
       <c r="F425">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G425" t="s">
         <v>38</v>
@@ -14981,7 +14981,7 @@
         <v>37</v>
       </c>
       <c r="F426">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G426" t="s">
         <v>38</v>
@@ -15007,7 +15007,7 @@
         <v>37</v>
       </c>
       <c r="F427">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G427" t="s">
         <v>38</v>
@@ -15033,7 +15033,7 @@
         <v>37</v>
       </c>
       <c r="F428">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G428" t="s">
         <v>38</v>
@@ -15059,7 +15059,7 @@
         <v>37</v>
       </c>
       <c r="F429">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G429" t="s">
         <v>38</v>
@@ -15085,7 +15085,7 @@
         <v>37</v>
       </c>
       <c r="F430">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G430" t="s">
         <v>38</v>
@@ -15111,7 +15111,7 @@
         <v>37</v>
       </c>
       <c r="F431">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G431" t="s">
         <v>38</v>
@@ -15137,7 +15137,7 @@
         <v>37</v>
       </c>
       <c r="F432">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="G432" t="s">
         <v>38</v>
@@ -15163,7 +15163,7 @@
         <v>37</v>
       </c>
       <c r="F433">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G433" t="s">
         <v>38</v>
@@ -15189,7 +15189,7 @@
         <v>37</v>
       </c>
       <c r="F434">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="G434" t="s">
         <v>38</v>
@@ -15241,7 +15241,7 @@
         <v>37</v>
       </c>
       <c r="F436">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G436" t="s">
         <v>38</v>
@@ -15267,7 +15267,7 @@
         <v>37</v>
       </c>
       <c r="F437">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G437" t="s">
         <v>38</v>
@@ -15293,7 +15293,7 @@
         <v>37</v>
       </c>
       <c r="F438">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="G438" t="s">
         <v>38</v>
@@ -15319,7 +15319,7 @@
         <v>37</v>
       </c>
       <c r="F439">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G439" t="s">
         <v>38</v>
@@ -15345,7 +15345,7 @@
         <v>37</v>
       </c>
       <c r="F440">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G440" t="s">
         <v>38</v>
@@ -15371,7 +15371,7 @@
         <v>37</v>
       </c>
       <c r="F441">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G441" t="s">
         <v>38</v>
@@ -15397,7 +15397,7 @@
         <v>37</v>
       </c>
       <c r="F442">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G442" t="s">
         <v>38</v>
@@ -15423,7 +15423,7 @@
         <v>37</v>
       </c>
       <c r="F443">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G443" t="s">
         <v>38</v>
@@ -15449,7 +15449,7 @@
         <v>37</v>
       </c>
       <c r="F444">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G444" t="s">
         <v>38</v>
@@ -15475,7 +15475,7 @@
         <v>37</v>
       </c>
       <c r="F445">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G445" t="s">
         <v>38</v>
@@ -15501,7 +15501,7 @@
         <v>37</v>
       </c>
       <c r="F446">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G446" t="s">
         <v>38</v>
@@ -15527,7 +15527,7 @@
         <v>37</v>
       </c>
       <c r="F447">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G447" t="s">
         <v>38</v>
@@ -15553,7 +15553,7 @@
         <v>37</v>
       </c>
       <c r="F448">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G448" t="s">
         <v>38</v>
@@ -15579,7 +15579,7 @@
         <v>37</v>
       </c>
       <c r="F449">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G449" t="s">
         <v>38</v>
@@ -15605,7 +15605,7 @@
         <v>37</v>
       </c>
       <c r="F450">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G450" t="s">
         <v>38</v>
@@ -15631,7 +15631,7 @@
         <v>37</v>
       </c>
       <c r="F451">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G451" t="s">
         <v>38</v>
@@ -15657,7 +15657,7 @@
         <v>37</v>
       </c>
       <c r="F452">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G452" t="s">
         <v>38</v>
@@ -15683,7 +15683,7 @@
         <v>37</v>
       </c>
       <c r="F453">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G453" t="s">
         <v>38</v>
@@ -15709,7 +15709,7 @@
         <v>37</v>
       </c>
       <c r="F454">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G454" t="s">
         <v>38</v>
@@ -15735,7 +15735,7 @@
         <v>37</v>
       </c>
       <c r="F455">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G455" t="s">
         <v>38</v>
@@ -15761,7 +15761,7 @@
         <v>37</v>
       </c>
       <c r="F456">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G456" t="s">
         <v>38</v>
@@ -15787,7 +15787,7 @@
         <v>37</v>
       </c>
       <c r="F457">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G457" t="s">
         <v>38</v>
@@ -15813,7 +15813,7 @@
         <v>37</v>
       </c>
       <c r="F458">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G458" t="s">
         <v>38</v>
@@ -15839,7 +15839,7 @@
         <v>37</v>
       </c>
       <c r="F459">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G459" t="s">
         <v>38</v>
@@ -15865,7 +15865,7 @@
         <v>37</v>
       </c>
       <c r="F460">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="G460" t="s">
         <v>38</v>
@@ -15891,7 +15891,7 @@
         <v>37</v>
       </c>
       <c r="F461">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G461" t="s">
         <v>38</v>
@@ -15917,7 +15917,7 @@
         <v>37</v>
       </c>
       <c r="F462">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G462" t="s">
         <v>38</v>
@@ -15943,7 +15943,7 @@
         <v>37</v>
       </c>
       <c r="F463">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G463" t="s">
         <v>38</v>
@@ -15969,7 +15969,7 @@
         <v>37</v>
       </c>
       <c r="F464">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="G464" t="s">
         <v>38</v>
@@ -15995,7 +15995,7 @@
         <v>37</v>
       </c>
       <c r="F465">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G465" t="s">
         <v>38</v>
@@ -16021,7 +16021,7 @@
         <v>37</v>
       </c>
       <c r="F466">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G466" t="s">
         <v>38</v>
@@ -16047,7 +16047,7 @@
         <v>37</v>
       </c>
       <c r="F467">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="G467" t="s">
         <v>38</v>
@@ -16073,7 +16073,7 @@
         <v>37</v>
       </c>
       <c r="F468">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G468" t="s">
         <v>38</v>
@@ -16099,7 +16099,7 @@
         <v>37</v>
       </c>
       <c r="F469">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G469" t="s">
         <v>38</v>
@@ -16125,7 +16125,7 @@
         <v>37</v>
       </c>
       <c r="F470">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G470" t="s">
         <v>38</v>
@@ -16151,7 +16151,7 @@
         <v>37</v>
       </c>
       <c r="F471">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G471" t="s">
         <v>38</v>
@@ -16177,7 +16177,7 @@
         <v>37</v>
       </c>
       <c r="F472">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G472" t="s">
         <v>38</v>
@@ -16203,7 +16203,7 @@
         <v>37</v>
       </c>
       <c r="F473">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G473" t="s">
         <v>38</v>
@@ -16229,7 +16229,7 @@
         <v>37</v>
       </c>
       <c r="F474">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G474" t="s">
         <v>38</v>
@@ -16255,7 +16255,7 @@
         <v>37</v>
       </c>
       <c r="F475">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G475" t="s">
         <v>38</v>
@@ -16281,7 +16281,7 @@
         <v>37</v>
       </c>
       <c r="F476">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G476" t="s">
         <v>38</v>
@@ -16307,7 +16307,7 @@
         <v>37</v>
       </c>
       <c r="F477">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="G477" t="s">
         <v>38</v>
@@ -16333,7 +16333,7 @@
         <v>37</v>
       </c>
       <c r="F478">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G478" t="s">
         <v>38</v>
@@ -16359,7 +16359,7 @@
         <v>37</v>
       </c>
       <c r="F479">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G479" t="s">
         <v>38</v>
@@ -16385,7 +16385,7 @@
         <v>37</v>
       </c>
       <c r="F480">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G480" t="s">
         <v>38</v>
@@ -16411,7 +16411,7 @@
         <v>37</v>
       </c>
       <c r="F481">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G481" t="s">
         <v>38</v>
@@ -16437,7 +16437,7 @@
         <v>37</v>
       </c>
       <c r="F482">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G482" t="s">
         <v>38</v>
@@ -16463,7 +16463,7 @@
         <v>37</v>
       </c>
       <c r="F483">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G483" t="s">
         <v>38</v>
@@ -16489,7 +16489,7 @@
         <v>37</v>
       </c>
       <c r="F484">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G484" t="s">
         <v>38</v>
@@ -16515,7 +16515,7 @@
         <v>37</v>
       </c>
       <c r="F485">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G485" t="s">
         <v>38</v>
@@ -16541,7 +16541,7 @@
         <v>37</v>
       </c>
       <c r="F486">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G486" t="s">
         <v>38</v>
@@ -16567,7 +16567,7 @@
         <v>37</v>
       </c>
       <c r="F487">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="G487" t="s">
         <v>38</v>
@@ -16593,7 +16593,7 @@
         <v>37</v>
       </c>
       <c r="F488">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G488" t="s">
         <v>38</v>
@@ -16619,7 +16619,7 @@
         <v>37</v>
       </c>
       <c r="F489">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G489" t="s">
         <v>38</v>
@@ -16645,7 +16645,7 @@
         <v>37</v>
       </c>
       <c r="F490">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G490" t="s">
         <v>38</v>
@@ -16671,7 +16671,7 @@
         <v>37</v>
       </c>
       <c r="F491">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G491" t="s">
         <v>38</v>
@@ -16697,7 +16697,7 @@
         <v>37</v>
       </c>
       <c r="F492">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="G492" t="s">
         <v>38</v>
@@ -16723,7 +16723,7 @@
         <v>37</v>
       </c>
       <c r="F493">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G493" t="s">
         <v>38</v>
@@ -16749,7 +16749,7 @@
         <v>37</v>
       </c>
       <c r="F494">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G494" t="s">
         <v>38</v>
@@ -16775,7 +16775,7 @@
         <v>37</v>
       </c>
       <c r="F495">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="G495" t="s">
         <v>38</v>
@@ -16801,7 +16801,7 @@
         <v>37</v>
       </c>
       <c r="F496">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G496" t="s">
         <v>38</v>
@@ -16827,7 +16827,7 @@
         <v>37</v>
       </c>
       <c r="F497">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G497" t="s">
         <v>38</v>
@@ -16853,7 +16853,7 @@
         <v>37</v>
       </c>
       <c r="F498">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G498" t="s">
         <v>38</v>
@@ -16879,7 +16879,7 @@
         <v>37</v>
       </c>
       <c r="F499">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G499" t="s">
         <v>38</v>
@@ -16905,7 +16905,7 @@
         <v>37</v>
       </c>
       <c r="F500">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G500" t="s">
         <v>38</v>
@@ -16931,7 +16931,7 @@
         <v>37</v>
       </c>
       <c r="F501">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G501" t="s">
         <v>38</v>

--- a/e2e-tests/reports/test-report.xlsx
+++ b/e2e-tests/reports/test-report.xlsx
@@ -42,19 +42,19 @@
     <t>Total Execution Time</t>
   </si>
   <si>
-    <t>17.19s</t>
+    <t>17.54s</t>
   </si>
   <si>
     <t>Average Test Duration</t>
   </si>
   <si>
-    <t>34.37ms</t>
+    <t>35.08ms</t>
   </si>
   <si>
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>7/23/2026, 3:23:00 PM</t>
+    <t>7/23/2026, 3:53:34 PM</t>
   </si>
   <si>
     <t>Category</t>
@@ -3684,7 +3684,7 @@
         <v>100</v>
       </c>
       <c r="G2">
-        <v>34.46</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3707,7 +3707,7 @@
         <v>100</v>
       </c>
       <c r="G3">
-        <v>34.24</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3730,7 +3730,7 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>35.46</v>
+        <v>35.74</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3753,7 +3753,7 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>33.54</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3776,7 +3776,7 @@
         <v>100</v>
       </c>
       <c r="G6">
-        <v>36.26</v>
+        <v>33.18</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3799,7 +3799,7 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>33.88</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3822,7 +3822,7 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>34.64</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3845,7 +3845,7 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>31.58</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3868,7 +3868,7 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>33.64</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3891,7 +3891,7 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>36.04</v>
+        <v>38.32</v>
       </c>
     </row>
   </sheetData>
@@ -3957,7 +3957,7 @@
         <v>37</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
         <v>38</v>
@@ -3983,7 +3983,7 @@
         <v>37</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
@@ -4009,7 +4009,7 @@
         <v>37</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
         <v>38</v>
@@ -4035,7 +4035,7 @@
         <v>37</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
         <v>38</v>
@@ -4061,7 +4061,7 @@
         <v>37</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
         <v>38</v>
@@ -4087,7 +4087,7 @@
         <v>37</v>
       </c>
       <c r="F7">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
         <v>38</v>
@@ -4113,7 +4113,7 @@
         <v>37</v>
       </c>
       <c r="F8">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G8" t="s">
         <v>38</v>
@@ -4139,7 +4139,7 @@
         <v>37</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
         <v>38</v>
@@ -4165,7 +4165,7 @@
         <v>37</v>
       </c>
       <c r="F10">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
         <v>38</v>
@@ -4191,7 +4191,7 @@
         <v>37</v>
       </c>
       <c r="F11">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
         <v>38</v>
@@ -4217,7 +4217,7 @@
         <v>37</v>
       </c>
       <c r="F12">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
         <v>38</v>
@@ -4243,7 +4243,7 @@
         <v>37</v>
       </c>
       <c r="F13">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
         <v>38</v>
@@ -4269,7 +4269,7 @@
         <v>37</v>
       </c>
       <c r="F14">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
         <v>38</v>
@@ -4295,7 +4295,7 @@
         <v>37</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
         <v>38</v>
@@ -4321,7 +4321,7 @@
         <v>37</v>
       </c>
       <c r="F16">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
         <v>38</v>
@@ -4347,7 +4347,7 @@
         <v>37</v>
       </c>
       <c r="F17">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
         <v>38</v>
@@ -4373,7 +4373,7 @@
         <v>37</v>
       </c>
       <c r="F18">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
         <v>38</v>
@@ -4399,7 +4399,7 @@
         <v>37</v>
       </c>
       <c r="F19">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G19" t="s">
         <v>38</v>
@@ -4425,7 +4425,7 @@
         <v>37</v>
       </c>
       <c r="F20">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="G20" t="s">
         <v>38</v>
@@ -4451,7 +4451,7 @@
         <v>37</v>
       </c>
       <c r="F21">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G21" t="s">
         <v>38</v>
@@ -4477,7 +4477,7 @@
         <v>37</v>
       </c>
       <c r="F22">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
         <v>38</v>
@@ -4503,7 +4503,7 @@
         <v>37</v>
       </c>
       <c r="F23">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s">
         <v>38</v>
@@ -4529,7 +4529,7 @@
         <v>37</v>
       </c>
       <c r="F24">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="G24" t="s">
         <v>38</v>
@@ -4555,7 +4555,7 @@
         <v>37</v>
       </c>
       <c r="F25">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G25" t="s">
         <v>38</v>
@@ -4581,7 +4581,7 @@
         <v>37</v>
       </c>
       <c r="F26">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s">
         <v>38</v>
@@ -4607,7 +4607,7 @@
         <v>37</v>
       </c>
       <c r="F27">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="G27" t="s">
         <v>38</v>
@@ -4633,7 +4633,7 @@
         <v>37</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="G28" t="s">
         <v>38</v>
@@ -4659,7 +4659,7 @@
         <v>37</v>
       </c>
       <c r="F29">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G29" t="s">
         <v>38</v>
@@ -4685,7 +4685,7 @@
         <v>37</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G30" t="s">
         <v>38</v>
@@ -4711,7 +4711,7 @@
         <v>37</v>
       </c>
       <c r="F31">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G31" t="s">
         <v>38</v>
@@ -4737,7 +4737,7 @@
         <v>37</v>
       </c>
       <c r="F32">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="G32" t="s">
         <v>38</v>
@@ -4763,7 +4763,7 @@
         <v>37</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="G33" t="s">
         <v>38</v>
@@ -4789,7 +4789,7 @@
         <v>37</v>
       </c>
       <c r="F34">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G34" t="s">
         <v>38</v>
@@ -4815,7 +4815,7 @@
         <v>37</v>
       </c>
       <c r="F35">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G35" t="s">
         <v>38</v>
@@ -4841,7 +4841,7 @@
         <v>37</v>
       </c>
       <c r="F36">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="G36" t="s">
         <v>38</v>
@@ -4867,7 +4867,7 @@
         <v>37</v>
       </c>
       <c r="F37">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G37" t="s">
         <v>38</v>
@@ -4893,7 +4893,7 @@
         <v>37</v>
       </c>
       <c r="F38">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s">
         <v>38</v>
@@ -4919,7 +4919,7 @@
         <v>37</v>
       </c>
       <c r="F39">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G39" t="s">
         <v>38</v>
@@ -4945,7 +4945,7 @@
         <v>37</v>
       </c>
       <c r="F40">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G40" t="s">
         <v>38</v>
@@ -4971,7 +4971,7 @@
         <v>37</v>
       </c>
       <c r="F41">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G41" t="s">
         <v>38</v>
@@ -4997,7 +4997,7 @@
         <v>37</v>
       </c>
       <c r="F42">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G42" t="s">
         <v>38</v>
@@ -5023,7 +5023,7 @@
         <v>37</v>
       </c>
       <c r="F43">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G43" t="s">
         <v>38</v>
@@ -5049,7 +5049,7 @@
         <v>37</v>
       </c>
       <c r="F44">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="G44" t="s">
         <v>38</v>
@@ -5075,7 +5075,7 @@
         <v>37</v>
       </c>
       <c r="F45">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="G45" t="s">
         <v>38</v>
@@ -5101,7 +5101,7 @@
         <v>37</v>
       </c>
       <c r="F46">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G46" t="s">
         <v>38</v>
@@ -5127,7 +5127,7 @@
         <v>37</v>
       </c>
       <c r="F47">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="G47" t="s">
         <v>38</v>
@@ -5153,7 +5153,7 @@
         <v>37</v>
       </c>
       <c r="F48">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="G48" t="s">
         <v>38</v>
@@ -5179,7 +5179,7 @@
         <v>37</v>
       </c>
       <c r="F49">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="G49" t="s">
         <v>38</v>
@@ -5205,7 +5205,7 @@
         <v>37</v>
       </c>
       <c r="F50">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G50" t="s">
         <v>38</v>
@@ -5231,7 +5231,7 @@
         <v>37</v>
       </c>
       <c r="F51">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G51" t="s">
         <v>38</v>
@@ -5257,7 +5257,7 @@
         <v>37</v>
       </c>
       <c r="F52">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G52" t="s">
         <v>38</v>
@@ -5283,7 +5283,7 @@
         <v>37</v>
       </c>
       <c r="F53">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G53" t="s">
         <v>38</v>
@@ -5309,7 +5309,7 @@
         <v>37</v>
       </c>
       <c r="F54">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G54" t="s">
         <v>38</v>
@@ -5335,7 +5335,7 @@
         <v>37</v>
       </c>
       <c r="F55">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G55" t="s">
         <v>38</v>
@@ -5361,7 +5361,7 @@
         <v>37</v>
       </c>
       <c r="F56">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G56" t="s">
         <v>38</v>
@@ -5387,7 +5387,7 @@
         <v>37</v>
       </c>
       <c r="F57">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G57" t="s">
         <v>38</v>
@@ -5413,7 +5413,7 @@
         <v>37</v>
       </c>
       <c r="F58">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G58" t="s">
         <v>38</v>
@@ -5439,7 +5439,7 @@
         <v>37</v>
       </c>
       <c r="F59">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G59" t="s">
         <v>38</v>
@@ -5465,7 +5465,7 @@
         <v>37</v>
       </c>
       <c r="F60">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G60" t="s">
         <v>38</v>
@@ -5491,7 +5491,7 @@
         <v>37</v>
       </c>
       <c r="F61">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G61" t="s">
         <v>38</v>
@@ -5517,7 +5517,7 @@
         <v>37</v>
       </c>
       <c r="F62">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="G62" t="s">
         <v>38</v>
@@ -5543,7 +5543,7 @@
         <v>37</v>
       </c>
       <c r="F63">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G63" t="s">
         <v>38</v>
@@ -5595,7 +5595,7 @@
         <v>37</v>
       </c>
       <c r="F65">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G65" t="s">
         <v>38</v>
@@ -5621,7 +5621,7 @@
         <v>37</v>
       </c>
       <c r="F66">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G66" t="s">
         <v>38</v>
@@ -5647,7 +5647,7 @@
         <v>37</v>
       </c>
       <c r="F67">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="G67" t="s">
         <v>38</v>
@@ -5673,7 +5673,7 @@
         <v>37</v>
       </c>
       <c r="F68">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G68" t="s">
         <v>38</v>
@@ -5699,7 +5699,7 @@
         <v>37</v>
       </c>
       <c r="F69">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G69" t="s">
         <v>38</v>
@@ -5725,7 +5725,7 @@
         <v>37</v>
       </c>
       <c r="F70">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G70" t="s">
         <v>38</v>
@@ -5751,7 +5751,7 @@
         <v>37</v>
       </c>
       <c r="F71">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G71" t="s">
         <v>38</v>
@@ -5777,7 +5777,7 @@
         <v>37</v>
       </c>
       <c r="F72">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G72" t="s">
         <v>38</v>
@@ -5803,7 +5803,7 @@
         <v>37</v>
       </c>
       <c r="F73">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G73" t="s">
         <v>38</v>
@@ -5829,7 +5829,7 @@
         <v>37</v>
       </c>
       <c r="F74">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G74" t="s">
         <v>38</v>
@@ -5855,7 +5855,7 @@
         <v>37</v>
       </c>
       <c r="F75">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G75" t="s">
         <v>38</v>
@@ -5881,7 +5881,7 @@
         <v>37</v>
       </c>
       <c r="F76">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G76" t="s">
         <v>38</v>
@@ -5907,7 +5907,7 @@
         <v>37</v>
       </c>
       <c r="F77">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="G77" t="s">
         <v>38</v>
@@ -5933,7 +5933,7 @@
         <v>37</v>
       </c>
       <c r="F78">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G78" t="s">
         <v>38</v>
@@ -5959,7 +5959,7 @@
         <v>37</v>
       </c>
       <c r="F79">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G79" t="s">
         <v>38</v>
@@ -5985,7 +5985,7 @@
         <v>37</v>
       </c>
       <c r="F80">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G80" t="s">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>37</v>
       </c>
       <c r="F81">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G81" t="s">
         <v>38</v>
@@ -6037,7 +6037,7 @@
         <v>37</v>
       </c>
       <c r="F82">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G82" t="s">
         <v>38</v>
@@ -6063,7 +6063,7 @@
         <v>37</v>
       </c>
       <c r="F83">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s">
         <v>38</v>
@@ -6089,7 +6089,7 @@
         <v>37</v>
       </c>
       <c r="F84">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="G84" t="s">
         <v>38</v>
@@ -6115,7 +6115,7 @@
         <v>37</v>
       </c>
       <c r="F85">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G85" t="s">
         <v>38</v>
@@ -6141,7 +6141,7 @@
         <v>37</v>
       </c>
       <c r="F86">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G86" t="s">
         <v>38</v>
@@ -6167,7 +6167,7 @@
         <v>37</v>
       </c>
       <c r="F87">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G87" t="s">
         <v>38</v>
@@ -6193,7 +6193,7 @@
         <v>37</v>
       </c>
       <c r="F88">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G88" t="s">
         <v>38</v>
@@ -6219,7 +6219,7 @@
         <v>37</v>
       </c>
       <c r="F89">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G89" t="s">
         <v>38</v>
@@ -6245,7 +6245,7 @@
         <v>37</v>
       </c>
       <c r="F90">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G90" t="s">
         <v>38</v>
@@ -6271,7 +6271,7 @@
         <v>37</v>
       </c>
       <c r="F91">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G91" t="s">
         <v>38</v>
@@ -6297,7 +6297,7 @@
         <v>37</v>
       </c>
       <c r="F92">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G92" t="s">
         <v>38</v>
@@ -6323,7 +6323,7 @@
         <v>37</v>
       </c>
       <c r="F93">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G93" t="s">
         <v>38</v>
@@ -6349,7 +6349,7 @@
         <v>37</v>
       </c>
       <c r="F94">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G94" t="s">
         <v>38</v>
@@ -6375,7 +6375,7 @@
         <v>37</v>
       </c>
       <c r="F95">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G95" t="s">
         <v>38</v>
@@ -6401,7 +6401,7 @@
         <v>37</v>
       </c>
       <c r="F96">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G96" t="s">
         <v>38</v>
@@ -6427,7 +6427,7 @@
         <v>37</v>
       </c>
       <c r="F97">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G97" t="s">
         <v>38</v>
@@ -6453,7 +6453,7 @@
         <v>37</v>
       </c>
       <c r="F98">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G98" t="s">
         <v>38</v>
@@ -6479,7 +6479,7 @@
         <v>37</v>
       </c>
       <c r="F99">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G99" t="s">
         <v>38</v>
@@ -6505,7 +6505,7 @@
         <v>37</v>
       </c>
       <c r="F100">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G100" t="s">
         <v>38</v>
@@ -6531,7 +6531,7 @@
         <v>37</v>
       </c>
       <c r="F101">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="G101" t="s">
         <v>38</v>
@@ -6583,7 +6583,7 @@
         <v>37</v>
       </c>
       <c r="F103">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G103" t="s">
         <v>38</v>
@@ -6609,7 +6609,7 @@
         <v>37</v>
       </c>
       <c r="F104">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G104" t="s">
         <v>38</v>
@@ -6635,7 +6635,7 @@
         <v>37</v>
       </c>
       <c r="F105">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="G105" t="s">
         <v>38</v>
@@ -6661,7 +6661,7 @@
         <v>37</v>
       </c>
       <c r="F106">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G106" t="s">
         <v>38</v>
@@ -6687,7 +6687,7 @@
         <v>37</v>
       </c>
       <c r="F107">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G107" t="s">
         <v>38</v>
@@ -6713,7 +6713,7 @@
         <v>37</v>
       </c>
       <c r="F108">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G108" t="s">
         <v>38</v>
@@ -6739,7 +6739,7 @@
         <v>37</v>
       </c>
       <c r="F109">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G109" t="s">
         <v>38</v>
@@ -6765,7 +6765,7 @@
         <v>37</v>
       </c>
       <c r="F110">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G110" t="s">
         <v>38</v>
@@ -6791,7 +6791,7 @@
         <v>37</v>
       </c>
       <c r="F111">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="G111" t="s">
         <v>38</v>
@@ -6817,7 +6817,7 @@
         <v>37</v>
       </c>
       <c r="F112">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G112" t="s">
         <v>38</v>
@@ -6843,7 +6843,7 @@
         <v>37</v>
       </c>
       <c r="F113">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="G113" t="s">
         <v>38</v>
@@ -6869,7 +6869,7 @@
         <v>37</v>
       </c>
       <c r="F114">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G114" t="s">
         <v>38</v>
@@ -6895,7 +6895,7 @@
         <v>37</v>
       </c>
       <c r="F115">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G115" t="s">
         <v>38</v>
@@ -6921,7 +6921,7 @@
         <v>37</v>
       </c>
       <c r="F116">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G116" t="s">
         <v>38</v>
@@ -6947,7 +6947,7 @@
         <v>37</v>
       </c>
       <c r="F117">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G117" t="s">
         <v>38</v>
@@ -6973,7 +6973,7 @@
         <v>37</v>
       </c>
       <c r="F118">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G118" t="s">
         <v>38</v>
@@ -6999,7 +6999,7 @@
         <v>37</v>
       </c>
       <c r="F119">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G119" t="s">
         <v>38</v>
@@ -7025,7 +7025,7 @@
         <v>37</v>
       </c>
       <c r="F120">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G120" t="s">
         <v>38</v>
@@ -7051,7 +7051,7 @@
         <v>37</v>
       </c>
       <c r="F121">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G121" t="s">
         <v>38</v>
@@ -7077,7 +7077,7 @@
         <v>37</v>
       </c>
       <c r="F122">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G122" t="s">
         <v>38</v>
@@ -7103,7 +7103,7 @@
         <v>37</v>
       </c>
       <c r="F123">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G123" t="s">
         <v>38</v>
@@ -7129,7 +7129,7 @@
         <v>37</v>
       </c>
       <c r="F124">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G124" t="s">
         <v>38</v>
@@ -7155,7 +7155,7 @@
         <v>37</v>
       </c>
       <c r="F125">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G125" t="s">
         <v>38</v>
@@ -7181,7 +7181,7 @@
         <v>37</v>
       </c>
       <c r="F126">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G126" t="s">
         <v>38</v>
@@ -7207,7 +7207,7 @@
         <v>37</v>
       </c>
       <c r="F127">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G127" t="s">
         <v>38</v>
@@ -7233,7 +7233,7 @@
         <v>37</v>
       </c>
       <c r="F128">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G128" t="s">
         <v>38</v>
@@ -7259,7 +7259,7 @@
         <v>37</v>
       </c>
       <c r="F129">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G129" t="s">
         <v>38</v>
@@ -7285,7 +7285,7 @@
         <v>37</v>
       </c>
       <c r="F130">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G130" t="s">
         <v>38</v>
@@ -7311,7 +7311,7 @@
         <v>37</v>
       </c>
       <c r="F131">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G131" t="s">
         <v>38</v>
@@ -7337,7 +7337,7 @@
         <v>37</v>
       </c>
       <c r="F132">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G132" t="s">
         <v>38</v>
@@ -7363,7 +7363,7 @@
         <v>37</v>
       </c>
       <c r="F133">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G133" t="s">
         <v>38</v>
@@ -7389,7 +7389,7 @@
         <v>37</v>
       </c>
       <c r="F134">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G134" t="s">
         <v>38</v>
@@ -7415,7 +7415,7 @@
         <v>37</v>
       </c>
       <c r="F135">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G135" t="s">
         <v>38</v>
@@ -7441,7 +7441,7 @@
         <v>37</v>
       </c>
       <c r="F136">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G136" t="s">
         <v>38</v>
@@ -7467,7 +7467,7 @@
         <v>37</v>
       </c>
       <c r="F137">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G137" t="s">
         <v>38</v>
@@ -7493,7 +7493,7 @@
         <v>37</v>
       </c>
       <c r="F138">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G138" t="s">
         <v>38</v>
@@ -7519,7 +7519,7 @@
         <v>37</v>
       </c>
       <c r="F139">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G139" t="s">
         <v>38</v>
@@ -7545,7 +7545,7 @@
         <v>37</v>
       </c>
       <c r="F140">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G140" t="s">
         <v>38</v>
@@ -7571,7 +7571,7 @@
         <v>37</v>
       </c>
       <c r="F141">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="G141" t="s">
         <v>38</v>
@@ -7597,7 +7597,7 @@
         <v>37</v>
       </c>
       <c r="F142">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G142" t="s">
         <v>38</v>
@@ -7623,7 +7623,7 @@
         <v>37</v>
       </c>
       <c r="F143">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G143" t="s">
         <v>38</v>
@@ -7675,7 +7675,7 @@
         <v>37</v>
       </c>
       <c r="F145">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G145" t="s">
         <v>38</v>
@@ -7701,7 +7701,7 @@
         <v>37</v>
       </c>
       <c r="F146">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G146" t="s">
         <v>38</v>
@@ -7727,7 +7727,7 @@
         <v>37</v>
       </c>
       <c r="F147">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G147" t="s">
         <v>38</v>
@@ -7753,7 +7753,7 @@
         <v>37</v>
       </c>
       <c r="F148">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="G148" t="s">
         <v>38</v>
@@ -7779,7 +7779,7 @@
         <v>37</v>
       </c>
       <c r="F149">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="G149" t="s">
         <v>38</v>
@@ -7805,7 +7805,7 @@
         <v>37</v>
       </c>
       <c r="F150">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G150" t="s">
         <v>38</v>
@@ -7831,7 +7831,7 @@
         <v>37</v>
       </c>
       <c r="F151">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G151" t="s">
         <v>38</v>
@@ -7857,7 +7857,7 @@
         <v>37</v>
       </c>
       <c r="F152">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G152" t="s">
         <v>38</v>
@@ -7883,7 +7883,7 @@
         <v>37</v>
       </c>
       <c r="F153">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G153" t="s">
         <v>38</v>
@@ -7909,7 +7909,7 @@
         <v>37</v>
       </c>
       <c r="F154">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G154" t="s">
         <v>38</v>
@@ -7935,7 +7935,7 @@
         <v>37</v>
       </c>
       <c r="F155">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G155" t="s">
         <v>38</v>
@@ -7961,7 +7961,7 @@
         <v>37</v>
       </c>
       <c r="F156">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G156" t="s">
         <v>38</v>
@@ -7987,7 +7987,7 @@
         <v>37</v>
       </c>
       <c r="F157">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G157" t="s">
         <v>38</v>
@@ -8013,7 +8013,7 @@
         <v>37</v>
       </c>
       <c r="F158">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G158" t="s">
         <v>38</v>
@@ -8039,7 +8039,7 @@
         <v>37</v>
       </c>
       <c r="F159">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G159" t="s">
         <v>38</v>
@@ -8065,7 +8065,7 @@
         <v>37</v>
       </c>
       <c r="F160">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G160" t="s">
         <v>38</v>
@@ -8117,7 +8117,7 @@
         <v>37</v>
       </c>
       <c r="F162">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="G162" t="s">
         <v>38</v>
@@ -8143,7 +8143,7 @@
         <v>37</v>
       </c>
       <c r="F163">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G163" t="s">
         <v>38</v>
@@ -8169,7 +8169,7 @@
         <v>37</v>
       </c>
       <c r="F164">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G164" t="s">
         <v>38</v>
@@ -8195,7 +8195,7 @@
         <v>37</v>
       </c>
       <c r="F165">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="G165" t="s">
         <v>38</v>
@@ -8221,7 +8221,7 @@
         <v>37</v>
       </c>
       <c r="F166">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G166" t="s">
         <v>38</v>
@@ -8247,7 +8247,7 @@
         <v>37</v>
       </c>
       <c r="F167">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G167" t="s">
         <v>38</v>
@@ -8273,7 +8273,7 @@
         <v>37</v>
       </c>
       <c r="F168">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="G168" t="s">
         <v>38</v>
@@ -8299,7 +8299,7 @@
         <v>37</v>
       </c>
       <c r="F169">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G169" t="s">
         <v>38</v>
@@ -8325,7 +8325,7 @@
         <v>37</v>
       </c>
       <c r="F170">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="G170" t="s">
         <v>38</v>
@@ -8351,7 +8351,7 @@
         <v>37</v>
       </c>
       <c r="F171">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G171" t="s">
         <v>38</v>
@@ -8377,7 +8377,7 @@
         <v>37</v>
       </c>
       <c r="F172">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G172" t="s">
         <v>38</v>
@@ -8403,7 +8403,7 @@
         <v>37</v>
       </c>
       <c r="F173">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G173" t="s">
         <v>38</v>
@@ -8429,7 +8429,7 @@
         <v>37</v>
       </c>
       <c r="F174">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G174" t="s">
         <v>38</v>
@@ -8455,7 +8455,7 @@
         <v>37</v>
       </c>
       <c r="F175">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G175" t="s">
         <v>38</v>
@@ -8481,7 +8481,7 @@
         <v>37</v>
       </c>
       <c r="F176">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G176" t="s">
         <v>38</v>
@@ -8507,7 +8507,7 @@
         <v>37</v>
       </c>
       <c r="F177">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="G177" t="s">
         <v>38</v>
@@ -8533,7 +8533,7 @@
         <v>37</v>
       </c>
       <c r="F178">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G178" t="s">
         <v>38</v>
@@ -8559,7 +8559,7 @@
         <v>37</v>
       </c>
       <c r="F179">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G179" t="s">
         <v>38</v>
@@ -8585,7 +8585,7 @@
         <v>37</v>
       </c>
       <c r="F180">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="G180" t="s">
         <v>38</v>
@@ -8611,7 +8611,7 @@
         <v>37</v>
       </c>
       <c r="F181">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="G181" t="s">
         <v>38</v>
@@ -8637,7 +8637,7 @@
         <v>37</v>
       </c>
       <c r="F182">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G182" t="s">
         <v>38</v>
@@ -8663,7 +8663,7 @@
         <v>37</v>
       </c>
       <c r="F183">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G183" t="s">
         <v>38</v>
@@ -8689,7 +8689,7 @@
         <v>37</v>
       </c>
       <c r="F184">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G184" t="s">
         <v>38</v>
@@ -8715,7 +8715,7 @@
         <v>37</v>
       </c>
       <c r="F185">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G185" t="s">
         <v>38</v>
@@ -8741,7 +8741,7 @@
         <v>37</v>
       </c>
       <c r="F186">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G186" t="s">
         <v>38</v>
@@ -8767,7 +8767,7 @@
         <v>37</v>
       </c>
       <c r="F187">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G187" t="s">
         <v>38</v>
@@ -8793,7 +8793,7 @@
         <v>37</v>
       </c>
       <c r="F188">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G188" t="s">
         <v>38</v>
@@ -8845,7 +8845,7 @@
         <v>37</v>
       </c>
       <c r="F190">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G190" t="s">
         <v>38</v>
@@ -8871,7 +8871,7 @@
         <v>37</v>
       </c>
       <c r="F191">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G191" t="s">
         <v>38</v>
@@ -8897,7 +8897,7 @@
         <v>37</v>
       </c>
       <c r="F192">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G192" t="s">
         <v>38</v>
@@ -8923,7 +8923,7 @@
         <v>37</v>
       </c>
       <c r="F193">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G193" t="s">
         <v>38</v>
@@ -8949,7 +8949,7 @@
         <v>37</v>
       </c>
       <c r="F194">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G194" t="s">
         <v>38</v>
@@ -8975,7 +8975,7 @@
         <v>37</v>
       </c>
       <c r="F195">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G195" t="s">
         <v>38</v>
@@ -9001,7 +9001,7 @@
         <v>37</v>
       </c>
       <c r="F196">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G196" t="s">
         <v>38</v>
@@ -9027,7 +9027,7 @@
         <v>37</v>
       </c>
       <c r="F197">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G197" t="s">
         <v>38</v>
@@ -9053,7 +9053,7 @@
         <v>37</v>
       </c>
       <c r="F198">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G198" t="s">
         <v>38</v>
@@ -9079,7 +9079,7 @@
         <v>37</v>
       </c>
       <c r="F199">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="G199" t="s">
         <v>38</v>
@@ -9105,7 +9105,7 @@
         <v>37</v>
       </c>
       <c r="F200">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G200" t="s">
         <v>38</v>
@@ -9131,7 +9131,7 @@
         <v>37</v>
       </c>
       <c r="F201">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G201" t="s">
         <v>38</v>
@@ -9157,7 +9157,7 @@
         <v>37</v>
       </c>
       <c r="F202">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G202" t="s">
         <v>38</v>
@@ -9183,7 +9183,7 @@
         <v>37</v>
       </c>
       <c r="F203">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G203" t="s">
         <v>38</v>
@@ -9209,7 +9209,7 @@
         <v>37</v>
       </c>
       <c r="F204">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G204" t="s">
         <v>38</v>
@@ -9235,7 +9235,7 @@
         <v>37</v>
       </c>
       <c r="F205">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G205" t="s">
         <v>38</v>
@@ -9261,7 +9261,7 @@
         <v>37</v>
       </c>
       <c r="F206">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G206" t="s">
         <v>38</v>
@@ -9287,7 +9287,7 @@
         <v>37</v>
       </c>
       <c r="F207">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G207" t="s">
         <v>38</v>
@@ -9313,7 +9313,7 @@
         <v>37</v>
       </c>
       <c r="F208">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G208" t="s">
         <v>38</v>
@@ -9339,7 +9339,7 @@
         <v>37</v>
       </c>
       <c r="F209">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="G209" t="s">
         <v>38</v>
@@ -9365,7 +9365,7 @@
         <v>37</v>
       </c>
       <c r="F210">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G210" t="s">
         <v>38</v>
@@ -9391,7 +9391,7 @@
         <v>37</v>
       </c>
       <c r="F211">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G211" t="s">
         <v>38</v>
@@ -9417,7 +9417,7 @@
         <v>37</v>
       </c>
       <c r="F212">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="G212" t="s">
         <v>38</v>
@@ -9443,7 +9443,7 @@
         <v>37</v>
       </c>
       <c r="F213">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="G213" t="s">
         <v>38</v>
@@ -9469,7 +9469,7 @@
         <v>37</v>
       </c>
       <c r="F214">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G214" t="s">
         <v>38</v>
@@ -9495,7 +9495,7 @@
         <v>37</v>
       </c>
       <c r="F215">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G215" t="s">
         <v>38</v>
@@ -9521,7 +9521,7 @@
         <v>37</v>
       </c>
       <c r="F216">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G216" t="s">
         <v>38</v>
@@ -9547,7 +9547,7 @@
         <v>37</v>
       </c>
       <c r="F217">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G217" t="s">
         <v>38</v>
@@ -9573,7 +9573,7 @@
         <v>37</v>
       </c>
       <c r="F218">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G218" t="s">
         <v>38</v>
@@ -9599,7 +9599,7 @@
         <v>37</v>
       </c>
       <c r="F219">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G219" t="s">
         <v>38</v>
@@ -9625,7 +9625,7 @@
         <v>37</v>
       </c>
       <c r="F220">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G220" t="s">
         <v>38</v>
@@ -9651,7 +9651,7 @@
         <v>37</v>
       </c>
       <c r="F221">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G221" t="s">
         <v>38</v>
@@ -9677,7 +9677,7 @@
         <v>37</v>
       </c>
       <c r="F222">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G222" t="s">
         <v>38</v>
@@ -9703,7 +9703,7 @@
         <v>37</v>
       </c>
       <c r="F223">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G223" t="s">
         <v>38</v>
@@ -9729,7 +9729,7 @@
         <v>37</v>
       </c>
       <c r="F224">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G224" t="s">
         <v>38</v>
@@ -9755,7 +9755,7 @@
         <v>37</v>
       </c>
       <c r="F225">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G225" t="s">
         <v>38</v>
@@ -9781,7 +9781,7 @@
         <v>37</v>
       </c>
       <c r="F226">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="G226" t="s">
         <v>38</v>
@@ -9807,7 +9807,7 @@
         <v>37</v>
       </c>
       <c r="F227">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G227" t="s">
         <v>38</v>
@@ -9833,7 +9833,7 @@
         <v>37</v>
       </c>
       <c r="F228">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G228" t="s">
         <v>38</v>
@@ -9859,7 +9859,7 @@
         <v>37</v>
       </c>
       <c r="F229">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G229" t="s">
         <v>38</v>
@@ -9885,7 +9885,7 @@
         <v>37</v>
       </c>
       <c r="F230">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G230" t="s">
         <v>38</v>
@@ -9911,7 +9911,7 @@
         <v>37</v>
       </c>
       <c r="F231">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G231" t="s">
         <v>38</v>
@@ -9937,7 +9937,7 @@
         <v>37</v>
       </c>
       <c r="F232">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G232" t="s">
         <v>38</v>
@@ -9963,7 +9963,7 @@
         <v>37</v>
       </c>
       <c r="F233">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G233" t="s">
         <v>38</v>
@@ -9989,7 +9989,7 @@
         <v>37</v>
       </c>
       <c r="F234">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="G234" t="s">
         <v>38</v>
@@ -10015,7 +10015,7 @@
         <v>37</v>
       </c>
       <c r="F235">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G235" t="s">
         <v>38</v>
@@ -10041,7 +10041,7 @@
         <v>37</v>
       </c>
       <c r="F236">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G236" t="s">
         <v>38</v>
@@ -10067,7 +10067,7 @@
         <v>37</v>
       </c>
       <c r="F237">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="G237" t="s">
         <v>38</v>
@@ -10093,7 +10093,7 @@
         <v>37</v>
       </c>
       <c r="F238">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G238" t="s">
         <v>38</v>
@@ -10119,7 +10119,7 @@
         <v>37</v>
       </c>
       <c r="F239">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G239" t="s">
         <v>38</v>
@@ -10145,7 +10145,7 @@
         <v>37</v>
       </c>
       <c r="F240">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G240" t="s">
         <v>38</v>
@@ -10171,7 +10171,7 @@
         <v>37</v>
       </c>
       <c r="F241">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G241" t="s">
         <v>38</v>
@@ -10197,7 +10197,7 @@
         <v>37</v>
       </c>
       <c r="F242">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G242" t="s">
         <v>38</v>
@@ -10223,7 +10223,7 @@
         <v>37</v>
       </c>
       <c r="F243">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G243" t="s">
         <v>38</v>
@@ -10249,7 +10249,7 @@
         <v>37</v>
       </c>
       <c r="F244">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G244" t="s">
         <v>38</v>
@@ -10275,7 +10275,7 @@
         <v>37</v>
       </c>
       <c r="F245">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G245" t="s">
         <v>38</v>
@@ -10301,7 +10301,7 @@
         <v>37</v>
       </c>
       <c r="F246">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G246" t="s">
         <v>38</v>
@@ -10327,7 +10327,7 @@
         <v>37</v>
       </c>
       <c r="F247">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G247" t="s">
         <v>38</v>
@@ -10353,7 +10353,7 @@
         <v>37</v>
       </c>
       <c r="F248">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G248" t="s">
         <v>38</v>
@@ -10379,7 +10379,7 @@
         <v>37</v>
       </c>
       <c r="F249">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G249" t="s">
         <v>38</v>
@@ -10405,7 +10405,7 @@
         <v>37</v>
       </c>
       <c r="F250">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G250" t="s">
         <v>38</v>
@@ -10431,7 +10431,7 @@
         <v>37</v>
       </c>
       <c r="F251">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G251" t="s">
         <v>38</v>
@@ -10457,7 +10457,7 @@
         <v>37</v>
       </c>
       <c r="F252">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G252" t="s">
         <v>38</v>
@@ -10483,7 +10483,7 @@
         <v>37</v>
       </c>
       <c r="F253">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G253" t="s">
         <v>38</v>
@@ -10509,7 +10509,7 @@
         <v>37</v>
       </c>
       <c r="F254">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G254" t="s">
         <v>38</v>
@@ -10535,7 +10535,7 @@
         <v>37</v>
       </c>
       <c r="F255">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G255" t="s">
         <v>38</v>
@@ -10561,7 +10561,7 @@
         <v>37</v>
       </c>
       <c r="F256">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G256" t="s">
         <v>38</v>
@@ -10587,7 +10587,7 @@
         <v>37</v>
       </c>
       <c r="F257">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G257" t="s">
         <v>38</v>
@@ -10613,7 +10613,7 @@
         <v>37</v>
       </c>
       <c r="F258">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G258" t="s">
         <v>38</v>
@@ -10639,7 +10639,7 @@
         <v>37</v>
       </c>
       <c r="F259">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="G259" t="s">
         <v>38</v>
@@ -10665,7 +10665,7 @@
         <v>37</v>
       </c>
       <c r="F260">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G260" t="s">
         <v>38</v>
@@ -10691,7 +10691,7 @@
         <v>37</v>
       </c>
       <c r="F261">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G261" t="s">
         <v>38</v>
@@ -10717,7 +10717,7 @@
         <v>37</v>
       </c>
       <c r="F262">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G262" t="s">
         <v>38</v>
@@ -10743,7 +10743,7 @@
         <v>37</v>
       </c>
       <c r="F263">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="G263" t="s">
         <v>38</v>
@@ -10769,7 +10769,7 @@
         <v>37</v>
       </c>
       <c r="F264">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G264" t="s">
         <v>38</v>
@@ -10795,7 +10795,7 @@
         <v>37</v>
       </c>
       <c r="F265">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G265" t="s">
         <v>38</v>
@@ -10821,7 +10821,7 @@
         <v>37</v>
       </c>
       <c r="F266">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G266" t="s">
         <v>38</v>
@@ -10847,7 +10847,7 @@
         <v>37</v>
       </c>
       <c r="F267">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G267" t="s">
         <v>38</v>
@@ -10873,7 +10873,7 @@
         <v>37</v>
       </c>
       <c r="F268">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G268" t="s">
         <v>38</v>
@@ -10899,7 +10899,7 @@
         <v>37</v>
       </c>
       <c r="F269">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="G269" t="s">
         <v>38</v>
@@ -10925,7 +10925,7 @@
         <v>37</v>
       </c>
       <c r="F270">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G270" t="s">
         <v>38</v>
@@ -10951,7 +10951,7 @@
         <v>37</v>
       </c>
       <c r="F271">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="G271" t="s">
         <v>38</v>
@@ -10977,7 +10977,7 @@
         <v>37</v>
       </c>
       <c r="F272">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G272" t="s">
         <v>38</v>
@@ -11003,7 +11003,7 @@
         <v>37</v>
       </c>
       <c r="F273">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G273" t="s">
         <v>38</v>
@@ -11029,7 +11029,7 @@
         <v>37</v>
       </c>
       <c r="F274">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G274" t="s">
         <v>38</v>
@@ -11055,7 +11055,7 @@
         <v>37</v>
       </c>
       <c r="F275">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G275" t="s">
         <v>38</v>
@@ -11081,7 +11081,7 @@
         <v>37</v>
       </c>
       <c r="F276">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G276" t="s">
         <v>38</v>
@@ -11107,7 +11107,7 @@
         <v>37</v>
       </c>
       <c r="F277">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G277" t="s">
         <v>38</v>
@@ -11133,7 +11133,7 @@
         <v>37</v>
       </c>
       <c r="F278">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="G278" t="s">
         <v>38</v>
@@ -11185,7 +11185,7 @@
         <v>37</v>
       </c>
       <c r="F280">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G280" t="s">
         <v>38</v>
@@ -11211,7 +11211,7 @@
         <v>37</v>
       </c>
       <c r="F281">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G281" t="s">
         <v>38</v>
@@ -11237,7 +11237,7 @@
         <v>37</v>
       </c>
       <c r="F282">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G282" t="s">
         <v>38</v>
@@ -11263,7 +11263,7 @@
         <v>37</v>
       </c>
       <c r="F283">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="G283" t="s">
         <v>38</v>
@@ -11289,7 +11289,7 @@
         <v>37</v>
       </c>
       <c r="F284">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G284" t="s">
         <v>38</v>
@@ -11315,7 +11315,7 @@
         <v>37</v>
       </c>
       <c r="F285">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G285" t="s">
         <v>38</v>
@@ -11341,7 +11341,7 @@
         <v>37</v>
       </c>
       <c r="F286">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G286" t="s">
         <v>38</v>
@@ -11367,7 +11367,7 @@
         <v>37</v>
       </c>
       <c r="F287">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G287" t="s">
         <v>38</v>
@@ -11393,7 +11393,7 @@
         <v>37</v>
       </c>
       <c r="F288">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G288" t="s">
         <v>38</v>
@@ -11419,7 +11419,7 @@
         <v>37</v>
       </c>
       <c r="F289">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G289" t="s">
         <v>38</v>
@@ -11445,7 +11445,7 @@
         <v>37</v>
       </c>
       <c r="F290">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G290" t="s">
         <v>38</v>
@@ -11471,7 +11471,7 @@
         <v>37</v>
       </c>
       <c r="F291">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G291" t="s">
         <v>38</v>
@@ -11497,7 +11497,7 @@
         <v>37</v>
       </c>
       <c r="F292">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G292" t="s">
         <v>38</v>
@@ -11523,7 +11523,7 @@
         <v>37</v>
       </c>
       <c r="F293">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G293" t="s">
         <v>38</v>
@@ -11549,7 +11549,7 @@
         <v>37</v>
       </c>
       <c r="F294">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G294" t="s">
         <v>38</v>
@@ -11601,7 +11601,7 @@
         <v>37</v>
       </c>
       <c r="F296">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G296" t="s">
         <v>38</v>
@@ -11627,7 +11627,7 @@
         <v>37</v>
       </c>
       <c r="F297">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G297" t="s">
         <v>38</v>
@@ -11653,7 +11653,7 @@
         <v>37</v>
       </c>
       <c r="F298">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="G298" t="s">
         <v>38</v>
@@ -11705,7 +11705,7 @@
         <v>37</v>
       </c>
       <c r="F300">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G300" t="s">
         <v>38</v>
@@ -11731,7 +11731,7 @@
         <v>37</v>
       </c>
       <c r="F301">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G301" t="s">
         <v>38</v>
@@ -11757,7 +11757,7 @@
         <v>37</v>
       </c>
       <c r="F302">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G302" t="s">
         <v>38</v>
@@ -11783,7 +11783,7 @@
         <v>37</v>
       </c>
       <c r="F303">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G303" t="s">
         <v>38</v>
@@ -11809,7 +11809,7 @@
         <v>37</v>
       </c>
       <c r="F304">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G304" t="s">
         <v>38</v>
@@ -11835,7 +11835,7 @@
         <v>37</v>
       </c>
       <c r="F305">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G305" t="s">
         <v>38</v>
@@ -11861,7 +11861,7 @@
         <v>37</v>
       </c>
       <c r="F306">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="G306" t="s">
         <v>38</v>
@@ -11887,7 +11887,7 @@
         <v>37</v>
       </c>
       <c r="F307">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G307" t="s">
         <v>38</v>
@@ -11913,7 +11913,7 @@
         <v>37</v>
       </c>
       <c r="F308">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G308" t="s">
         <v>38</v>
@@ -11991,7 +11991,7 @@
         <v>37</v>
       </c>
       <c r="F311">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G311" t="s">
         <v>38</v>
@@ -12017,7 +12017,7 @@
         <v>37</v>
       </c>
       <c r="F312">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G312" t="s">
         <v>38</v>
@@ -12043,7 +12043,7 @@
         <v>37</v>
       </c>
       <c r="F313">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G313" t="s">
         <v>38</v>
@@ -12069,7 +12069,7 @@
         <v>37</v>
       </c>
       <c r="F314">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G314" t="s">
         <v>38</v>
@@ -12095,7 +12095,7 @@
         <v>37</v>
       </c>
       <c r="F315">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="G315" t="s">
         <v>38</v>
@@ -12121,7 +12121,7 @@
         <v>37</v>
       </c>
       <c r="F316">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G316" t="s">
         <v>38</v>
@@ -12147,7 +12147,7 @@
         <v>37</v>
       </c>
       <c r="F317">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G317" t="s">
         <v>38</v>
@@ -12173,7 +12173,7 @@
         <v>37</v>
       </c>
       <c r="F318">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="G318" t="s">
         <v>38</v>
@@ -12199,7 +12199,7 @@
         <v>37</v>
       </c>
       <c r="F319">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G319" t="s">
         <v>38</v>
@@ -12225,7 +12225,7 @@
         <v>37</v>
       </c>
       <c r="F320">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G320" t="s">
         <v>38</v>
@@ -12251,7 +12251,7 @@
         <v>37</v>
       </c>
       <c r="F321">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G321" t="s">
         <v>38</v>
@@ -12277,7 +12277,7 @@
         <v>37</v>
       </c>
       <c r="F322">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G322" t="s">
         <v>38</v>
@@ -12303,7 +12303,7 @@
         <v>37</v>
       </c>
       <c r="F323">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G323" t="s">
         <v>38</v>
@@ -12329,7 +12329,7 @@
         <v>37</v>
       </c>
       <c r="F324">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G324" t="s">
         <v>38</v>
@@ -12355,7 +12355,7 @@
         <v>37</v>
       </c>
       <c r="F325">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="G325" t="s">
         <v>38</v>
@@ -12381,7 +12381,7 @@
         <v>37</v>
       </c>
       <c r="F326">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G326" t="s">
         <v>38</v>
@@ -12407,7 +12407,7 @@
         <v>37</v>
       </c>
       <c r="F327">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G327" t="s">
         <v>38</v>
@@ -12433,7 +12433,7 @@
         <v>37</v>
       </c>
       <c r="F328">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G328" t="s">
         <v>38</v>
@@ -12459,7 +12459,7 @@
         <v>37</v>
       </c>
       <c r="F329">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G329" t="s">
         <v>38</v>
@@ -12485,7 +12485,7 @@
         <v>37</v>
       </c>
       <c r="F330">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G330" t="s">
         <v>38</v>
@@ -12511,7 +12511,7 @@
         <v>37</v>
       </c>
       <c r="F331">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="G331" t="s">
         <v>38</v>
@@ -12537,7 +12537,7 @@
         <v>37</v>
       </c>
       <c r="F332">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G332" t="s">
         <v>38</v>
@@ -12563,7 +12563,7 @@
         <v>37</v>
       </c>
       <c r="F333">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G333" t="s">
         <v>38</v>
@@ -12589,7 +12589,7 @@
         <v>37</v>
       </c>
       <c r="F334">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G334" t="s">
         <v>38</v>
@@ -12615,7 +12615,7 @@
         <v>37</v>
       </c>
       <c r="F335">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="G335" t="s">
         <v>38</v>
@@ -12641,7 +12641,7 @@
         <v>37</v>
       </c>
       <c r="F336">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G336" t="s">
         <v>38</v>
@@ -12667,7 +12667,7 @@
         <v>37</v>
       </c>
       <c r="F337">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="G337" t="s">
         <v>38</v>
@@ -12693,7 +12693,7 @@
         <v>37</v>
       </c>
       <c r="F338">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="G338" t="s">
         <v>38</v>
@@ -12719,7 +12719,7 @@
         <v>37</v>
       </c>
       <c r="F339">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G339" t="s">
         <v>38</v>
@@ -12745,7 +12745,7 @@
         <v>37</v>
       </c>
       <c r="F340">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G340" t="s">
         <v>38</v>
@@ -12771,7 +12771,7 @@
         <v>37</v>
       </c>
       <c r="F341">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G341" t="s">
         <v>38</v>
@@ -12797,7 +12797,7 @@
         <v>37</v>
       </c>
       <c r="F342">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G342" t="s">
         <v>38</v>
@@ -12823,7 +12823,7 @@
         <v>37</v>
       </c>
       <c r="F343">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G343" t="s">
         <v>38</v>
@@ -12849,7 +12849,7 @@
         <v>37</v>
       </c>
       <c r="F344">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G344" t="s">
         <v>38</v>
@@ -12875,7 +12875,7 @@
         <v>37</v>
       </c>
       <c r="F345">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G345" t="s">
         <v>38</v>
@@ -12901,7 +12901,7 @@
         <v>37</v>
       </c>
       <c r="F346">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G346" t="s">
         <v>38</v>
@@ -12927,7 +12927,7 @@
         <v>37</v>
       </c>
       <c r="F347">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G347" t="s">
         <v>38</v>
@@ -12953,7 +12953,7 @@
         <v>37</v>
       </c>
       <c r="F348">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G348" t="s">
         <v>38</v>
@@ -12979,7 +12979,7 @@
         <v>37</v>
       </c>
       <c r="F349">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G349" t="s">
         <v>38</v>
@@ -13005,7 +13005,7 @@
         <v>37</v>
       </c>
       <c r="F350">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G350" t="s">
         <v>38</v>
@@ -13031,7 +13031,7 @@
         <v>37</v>
       </c>
       <c r="F351">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G351" t="s">
         <v>38</v>
@@ -13057,7 +13057,7 @@
         <v>37</v>
       </c>
       <c r="F352">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G352" t="s">
         <v>38</v>
@@ -13083,7 +13083,7 @@
         <v>37</v>
       </c>
       <c r="F353">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G353" t="s">
         <v>38</v>
@@ -13109,7 +13109,7 @@
         <v>37</v>
       </c>
       <c r="F354">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G354" t="s">
         <v>38</v>
@@ -13135,7 +13135,7 @@
         <v>37</v>
       </c>
       <c r="F355">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G355" t="s">
         <v>38</v>
@@ -13161,7 +13161,7 @@
         <v>37</v>
       </c>
       <c r="F356">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G356" t="s">
         <v>38</v>
@@ -13187,7 +13187,7 @@
         <v>37</v>
       </c>
       <c r="F357">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G357" t="s">
         <v>38</v>
@@ -13213,7 +13213,7 @@
         <v>37</v>
       </c>
       <c r="F358">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G358" t="s">
         <v>38</v>
@@ -13239,7 +13239,7 @@
         <v>37</v>
       </c>
       <c r="F359">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="G359" t="s">
         <v>38</v>
@@ -13265,7 +13265,7 @@
         <v>37</v>
       </c>
       <c r="F360">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G360" t="s">
         <v>38</v>
@@ -13291,7 +13291,7 @@
         <v>37</v>
       </c>
       <c r="F361">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G361" t="s">
         <v>38</v>
@@ -13317,7 +13317,7 @@
         <v>37</v>
       </c>
       <c r="F362">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G362" t="s">
         <v>38</v>
@@ -13343,7 +13343,7 @@
         <v>37</v>
       </c>
       <c r="F363">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="G363" t="s">
         <v>38</v>
@@ -13369,7 +13369,7 @@
         <v>37</v>
       </c>
       <c r="F364">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G364" t="s">
         <v>38</v>
@@ -13395,7 +13395,7 @@
         <v>37</v>
       </c>
       <c r="F365">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G365" t="s">
         <v>38</v>
@@ -13421,7 +13421,7 @@
         <v>37</v>
       </c>
       <c r="F366">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G366" t="s">
         <v>38</v>
@@ -13447,7 +13447,7 @@
         <v>37</v>
       </c>
       <c r="F367">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G367" t="s">
         <v>38</v>
@@ -13473,7 +13473,7 @@
         <v>37</v>
       </c>
       <c r="F368">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G368" t="s">
         <v>38</v>
@@ -13499,7 +13499,7 @@
         <v>37</v>
       </c>
       <c r="F369">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G369" t="s">
         <v>38</v>
@@ -13525,7 +13525,7 @@
         <v>37</v>
       </c>
       <c r="F370">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G370" t="s">
         <v>38</v>
@@ -13551,7 +13551,7 @@
         <v>37</v>
       </c>
       <c r="F371">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G371" t="s">
         <v>38</v>
@@ -13577,7 +13577,7 @@
         <v>37</v>
       </c>
       <c r="F372">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G372" t="s">
         <v>38</v>
@@ -13603,7 +13603,7 @@
         <v>37</v>
       </c>
       <c r="F373">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G373" t="s">
         <v>38</v>
@@ -13629,7 +13629,7 @@
         <v>37</v>
       </c>
       <c r="F374">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G374" t="s">
         <v>38</v>
@@ -13655,7 +13655,7 @@
         <v>37</v>
       </c>
       <c r="F375">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G375" t="s">
         <v>38</v>
@@ -13681,7 +13681,7 @@
         <v>37</v>
       </c>
       <c r="F376">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="G376" t="s">
         <v>38</v>
@@ -13707,7 +13707,7 @@
         <v>37</v>
       </c>
       <c r="F377">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G377" t="s">
         <v>38</v>
@@ -13733,7 +13733,7 @@
         <v>37</v>
       </c>
       <c r="F378">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G378" t="s">
         <v>38</v>
@@ -13759,7 +13759,7 @@
         <v>37</v>
       </c>
       <c r="F379">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G379" t="s">
         <v>38</v>
@@ -13811,7 +13811,7 @@
         <v>37</v>
       </c>
       <c r="F381">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="G381" t="s">
         <v>38</v>
@@ -13837,7 +13837,7 @@
         <v>37</v>
       </c>
       <c r="F382">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G382" t="s">
         <v>38</v>
@@ -13863,7 +13863,7 @@
         <v>37</v>
       </c>
       <c r="F383">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G383" t="s">
         <v>38</v>
@@ -13889,7 +13889,7 @@
         <v>37</v>
       </c>
       <c r="F384">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="G384" t="s">
         <v>38</v>
@@ -13915,7 +13915,7 @@
         <v>37</v>
       </c>
       <c r="F385">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="G385" t="s">
         <v>38</v>
@@ -13941,7 +13941,7 @@
         <v>37</v>
       </c>
       <c r="F386">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G386" t="s">
         <v>38</v>
@@ -13967,7 +13967,7 @@
         <v>37</v>
       </c>
       <c r="F387">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G387" t="s">
         <v>38</v>
@@ -13993,7 +13993,7 @@
         <v>37</v>
       </c>
       <c r="F388">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G388" t="s">
         <v>38</v>
@@ -14019,7 +14019,7 @@
         <v>37</v>
       </c>
       <c r="F389">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G389" t="s">
         <v>38</v>
@@ -14045,7 +14045,7 @@
         <v>37</v>
       </c>
       <c r="F390">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G390" t="s">
         <v>38</v>
@@ -14071,7 +14071,7 @@
         <v>37</v>
       </c>
       <c r="F391">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="G391" t="s">
         <v>38</v>
@@ -14097,7 +14097,7 @@
         <v>37</v>
       </c>
       <c r="F392">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G392" t="s">
         <v>38</v>
@@ -14123,7 +14123,7 @@
         <v>37</v>
       </c>
       <c r="F393">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G393" t="s">
         <v>38</v>
@@ -14149,7 +14149,7 @@
         <v>37</v>
       </c>
       <c r="F394">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="G394" t="s">
         <v>38</v>
@@ -14175,7 +14175,7 @@
         <v>37</v>
       </c>
       <c r="F395">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G395" t="s">
         <v>38</v>
@@ -14201,7 +14201,7 @@
         <v>37</v>
       </c>
       <c r="F396">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G396" t="s">
         <v>38</v>
@@ -14227,7 +14227,7 @@
         <v>37</v>
       </c>
       <c r="F397">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G397" t="s">
         <v>38</v>
@@ -14253,7 +14253,7 @@
         <v>37</v>
       </c>
       <c r="F398">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G398" t="s">
         <v>38</v>
@@ -14279,7 +14279,7 @@
         <v>37</v>
       </c>
       <c r="F399">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G399" t="s">
         <v>38</v>
@@ -14305,7 +14305,7 @@
         <v>37</v>
       </c>
       <c r="F400">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G400" t="s">
         <v>38</v>
@@ -14331,7 +14331,7 @@
         <v>37</v>
       </c>
       <c r="F401">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G401" t="s">
         <v>38</v>
@@ -14357,7 +14357,7 @@
         <v>37</v>
       </c>
       <c r="F402">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G402" t="s">
         <v>38</v>
@@ -14383,7 +14383,7 @@
         <v>37</v>
       </c>
       <c r="F403">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G403" t="s">
         <v>38</v>
@@ -14409,7 +14409,7 @@
         <v>37</v>
       </c>
       <c r="F404">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G404" t="s">
         <v>38</v>
@@ -14435,7 +14435,7 @@
         <v>37</v>
       </c>
       <c r="F405">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G405" t="s">
         <v>38</v>
@@ -14461,7 +14461,7 @@
         <v>37</v>
       </c>
       <c r="F406">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G406" t="s">
         <v>38</v>
@@ -14487,7 +14487,7 @@
         <v>37</v>
       </c>
       <c r="F407">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G407" t="s">
         <v>38</v>
@@ -14513,7 +14513,7 @@
         <v>37</v>
       </c>
       <c r="F408">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G408" t="s">
         <v>38</v>
@@ -14539,7 +14539,7 @@
         <v>37</v>
       </c>
       <c r="F409">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="G409" t="s">
         <v>38</v>
@@ -14565,7 +14565,7 @@
         <v>37</v>
       </c>
       <c r="F410">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="G410" t="s">
         <v>38</v>
@@ -14591,7 +14591,7 @@
         <v>37</v>
       </c>
       <c r="F411">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G411" t="s">
         <v>38</v>
@@ -14617,7 +14617,7 @@
         <v>37</v>
       </c>
       <c r="F412">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G412" t="s">
         <v>38</v>
@@ -14643,7 +14643,7 @@
         <v>37</v>
       </c>
       <c r="F413">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G413" t="s">
         <v>38</v>
@@ -14669,7 +14669,7 @@
         <v>37</v>
       </c>
       <c r="F414">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G414" t="s">
         <v>38</v>
@@ -14695,7 +14695,7 @@
         <v>37</v>
       </c>
       <c r="F415">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G415" t="s">
         <v>38</v>
@@ -14721,7 +14721,7 @@
         <v>37</v>
       </c>
       <c r="F416">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G416" t="s">
         <v>38</v>
@@ -14747,7 +14747,7 @@
         <v>37</v>
       </c>
       <c r="F417">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G417" t="s">
         <v>38</v>
@@ -14773,7 +14773,7 @@
         <v>37</v>
       </c>
       <c r="F418">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G418" t="s">
         <v>38</v>
@@ -14799,7 +14799,7 @@
         <v>37</v>
       </c>
       <c r="F419">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G419" t="s">
         <v>38</v>
@@ -14825,7 +14825,7 @@
         <v>37</v>
       </c>
       <c r="F420">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G420" t="s">
         <v>38</v>
@@ -14851,7 +14851,7 @@
         <v>37</v>
       </c>
       <c r="F421">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G421" t="s">
         <v>38</v>
@@ -14877,7 +14877,7 @@
         <v>37</v>
       </c>
       <c r="F422">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G422" t="s">
         <v>38</v>
@@ -14903,7 +14903,7 @@
         <v>37</v>
       </c>
       <c r="F423">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G423" t="s">
         <v>38</v>
@@ -14929,7 +14929,7 @@
         <v>37</v>
       </c>
       <c r="F424">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G424" t="s">
         <v>38</v>
@@ -14955,7 +14955,7 @@
         <v>37</v>
       </c>
       <c r="F425">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G425" t="s">
         <v>38</v>
@@ -14981,7 +14981,7 @@
         <v>37</v>
       </c>
       <c r="F426">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="G426" t="s">
         <v>38</v>
@@ -15007,7 +15007,7 @@
         <v>37</v>
       </c>
       <c r="F427">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G427" t="s">
         <v>38</v>
@@ -15033,7 +15033,7 @@
         <v>37</v>
       </c>
       <c r="F428">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G428" t="s">
         <v>38</v>
@@ -15059,7 +15059,7 @@
         <v>37</v>
       </c>
       <c r="F429">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G429" t="s">
         <v>38</v>
@@ -15085,7 +15085,7 @@
         <v>37</v>
       </c>
       <c r="F430">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G430" t="s">
         <v>38</v>
@@ -15111,7 +15111,7 @@
         <v>37</v>
       </c>
       <c r="F431">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G431" t="s">
         <v>38</v>
@@ -15137,7 +15137,7 @@
         <v>37</v>
       </c>
       <c r="F432">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G432" t="s">
         <v>38</v>
@@ -15163,7 +15163,7 @@
         <v>37</v>
       </c>
       <c r="F433">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G433" t="s">
         <v>38</v>
@@ -15189,7 +15189,7 @@
         <v>37</v>
       </c>
       <c r="F434">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="G434" t="s">
         <v>38</v>
@@ -15215,7 +15215,7 @@
         <v>37</v>
       </c>
       <c r="F435">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G435" t="s">
         <v>38</v>
@@ -15241,7 +15241,7 @@
         <v>37</v>
       </c>
       <c r="F436">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="G436" t="s">
         <v>38</v>
@@ -15267,7 +15267,7 @@
         <v>37</v>
       </c>
       <c r="F437">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G437" t="s">
         <v>38</v>
@@ -15293,7 +15293,7 @@
         <v>37</v>
       </c>
       <c r="F438">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G438" t="s">
         <v>38</v>
@@ -15319,7 +15319,7 @@
         <v>37</v>
       </c>
       <c r="F439">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G439" t="s">
         <v>38</v>
@@ -15345,7 +15345,7 @@
         <v>37</v>
       </c>
       <c r="F440">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G440" t="s">
         <v>38</v>
@@ -15371,7 +15371,7 @@
         <v>37</v>
       </c>
       <c r="F441">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G441" t="s">
         <v>38</v>
@@ -15397,7 +15397,7 @@
         <v>37</v>
       </c>
       <c r="F442">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G442" t="s">
         <v>38</v>
@@ -15423,7 +15423,7 @@
         <v>37</v>
       </c>
       <c r="F443">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G443" t="s">
         <v>38</v>
@@ -15449,7 +15449,7 @@
         <v>37</v>
       </c>
       <c r="F444">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G444" t="s">
         <v>38</v>
@@ -15475,7 +15475,7 @@
         <v>37</v>
       </c>
       <c r="F445">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G445" t="s">
         <v>38</v>
@@ -15501,7 +15501,7 @@
         <v>37</v>
       </c>
       <c r="F446">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G446" t="s">
         <v>38</v>
@@ -15527,7 +15527,7 @@
         <v>37</v>
       </c>
       <c r="F447">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G447" t="s">
         <v>38</v>
@@ -15553,7 +15553,7 @@
         <v>37</v>
       </c>
       <c r="F448">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G448" t="s">
         <v>38</v>
@@ -15579,7 +15579,7 @@
         <v>37</v>
       </c>
       <c r="F449">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G449" t="s">
         <v>38</v>
@@ -15605,7 +15605,7 @@
         <v>37</v>
       </c>
       <c r="F450">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G450" t="s">
         <v>38</v>
@@ -15631,7 +15631,7 @@
         <v>37</v>
       </c>
       <c r="F451">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G451" t="s">
         <v>38</v>
@@ -15657,7 +15657,7 @@
         <v>37</v>
       </c>
       <c r="F452">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="G452" t="s">
         <v>38</v>
@@ -15683,7 +15683,7 @@
         <v>37</v>
       </c>
       <c r="F453">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G453" t="s">
         <v>38</v>
@@ -15709,7 +15709,7 @@
         <v>37</v>
       </c>
       <c r="F454">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G454" t="s">
         <v>38</v>
@@ -15735,7 +15735,7 @@
         <v>37</v>
       </c>
       <c r="F455">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="G455" t="s">
         <v>38</v>
@@ -15761,7 +15761,7 @@
         <v>37</v>
       </c>
       <c r="F456">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G456" t="s">
         <v>38</v>
@@ -15787,7 +15787,7 @@
         <v>37</v>
       </c>
       <c r="F457">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G457" t="s">
         <v>38</v>
@@ -15813,7 +15813,7 @@
         <v>37</v>
       </c>
       <c r="F458">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G458" t="s">
         <v>38</v>
@@ -15839,7 +15839,7 @@
         <v>37</v>
       </c>
       <c r="F459">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G459" t="s">
         <v>38</v>
@@ -15865,7 +15865,7 @@
         <v>37</v>
       </c>
       <c r="F460">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G460" t="s">
         <v>38</v>
@@ -15891,7 +15891,7 @@
         <v>37</v>
       </c>
       <c r="F461">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G461" t="s">
         <v>38</v>
@@ -15917,7 +15917,7 @@
         <v>37</v>
       </c>
       <c r="F462">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G462" t="s">
         <v>38</v>
@@ -15943,7 +15943,7 @@
         <v>37</v>
       </c>
       <c r="F463">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G463" t="s">
         <v>38</v>
@@ -15969,7 +15969,7 @@
         <v>37</v>
       </c>
       <c r="F464">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G464" t="s">
         <v>38</v>
@@ -15995,7 +15995,7 @@
         <v>37</v>
       </c>
       <c r="F465">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G465" t="s">
         <v>38</v>
@@ -16021,7 +16021,7 @@
         <v>37</v>
       </c>
       <c r="F466">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G466" t="s">
         <v>38</v>
@@ -16047,7 +16047,7 @@
         <v>37</v>
       </c>
       <c r="F467">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G467" t="s">
         <v>38</v>
@@ -16073,7 +16073,7 @@
         <v>37</v>
       </c>
       <c r="F468">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G468" t="s">
         <v>38</v>
@@ -16099,7 +16099,7 @@
         <v>37</v>
       </c>
       <c r="F469">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G469" t="s">
         <v>38</v>
@@ -16125,7 +16125,7 @@
         <v>37</v>
       </c>
       <c r="F470">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G470" t="s">
         <v>38</v>
@@ -16151,7 +16151,7 @@
         <v>37</v>
       </c>
       <c r="F471">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G471" t="s">
         <v>38</v>
@@ -16177,7 +16177,7 @@
         <v>37</v>
       </c>
       <c r="F472">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="G472" t="s">
         <v>38</v>
@@ -16203,7 +16203,7 @@
         <v>37</v>
       </c>
       <c r="F473">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G473" t="s">
         <v>38</v>
@@ -16229,7 +16229,7 @@
         <v>37</v>
       </c>
       <c r="F474">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G474" t="s">
         <v>38</v>
@@ -16255,7 +16255,7 @@
         <v>37</v>
       </c>
       <c r="F475">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G475" t="s">
         <v>38</v>
@@ -16281,7 +16281,7 @@
         <v>37</v>
       </c>
       <c r="F476">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G476" t="s">
         <v>38</v>
@@ -16307,7 +16307,7 @@
         <v>37</v>
       </c>
       <c r="F477">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="G477" t="s">
         <v>38</v>
@@ -16333,7 +16333,7 @@
         <v>37</v>
       </c>
       <c r="F478">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G478" t="s">
         <v>38</v>
@@ -16359,7 +16359,7 @@
         <v>37</v>
       </c>
       <c r="F479">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G479" t="s">
         <v>38</v>
@@ -16385,7 +16385,7 @@
         <v>37</v>
       </c>
       <c r="F480">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G480" t="s">
         <v>38</v>
@@ -16411,7 +16411,7 @@
         <v>37</v>
       </c>
       <c r="F481">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G481" t="s">
         <v>38</v>
@@ -16437,7 +16437,7 @@
         <v>37</v>
       </c>
       <c r="F482">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G482" t="s">
         <v>38</v>
@@ -16463,7 +16463,7 @@
         <v>37</v>
       </c>
       <c r="F483">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G483" t="s">
         <v>38</v>
@@ -16489,7 +16489,7 @@
         <v>37</v>
       </c>
       <c r="F484">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G484" t="s">
         <v>38</v>
@@ -16541,7 +16541,7 @@
         <v>37</v>
       </c>
       <c r="F486">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G486" t="s">
         <v>38</v>
@@ -16567,7 +16567,7 @@
         <v>37</v>
       </c>
       <c r="F487">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G487" t="s">
         <v>38</v>
@@ -16593,7 +16593,7 @@
         <v>37</v>
       </c>
       <c r="F488">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G488" t="s">
         <v>38</v>
@@ -16619,7 +16619,7 @@
         <v>37</v>
       </c>
       <c r="F489">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="G489" t="s">
         <v>38</v>
@@ -16645,7 +16645,7 @@
         <v>37</v>
       </c>
       <c r="F490">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G490" t="s">
         <v>38</v>
@@ -16671,7 +16671,7 @@
         <v>37</v>
       </c>
       <c r="F491">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G491" t="s">
         <v>38</v>
@@ -16697,7 +16697,7 @@
         <v>37</v>
       </c>
       <c r="F492">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G492" t="s">
         <v>38</v>
@@ -16723,7 +16723,7 @@
         <v>37</v>
       </c>
       <c r="F493">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G493" t="s">
         <v>38</v>
@@ -16749,7 +16749,7 @@
         <v>37</v>
       </c>
       <c r="F494">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G494" t="s">
         <v>38</v>
@@ -16775,7 +16775,7 @@
         <v>37</v>
       </c>
       <c r="F495">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G495" t="s">
         <v>38</v>
@@ -16801,7 +16801,7 @@
         <v>37</v>
       </c>
       <c r="F496">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="G496" t="s">
         <v>38</v>
@@ -16827,7 +16827,7 @@
         <v>37</v>
       </c>
       <c r="F497">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G497" t="s">
         <v>38</v>
@@ -16853,7 +16853,7 @@
         <v>37</v>
       </c>
       <c r="F498">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G498" t="s">
         <v>38</v>
@@ -16879,7 +16879,7 @@
         <v>37</v>
       </c>
       <c r="F499">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G499" t="s">
         <v>38</v>
@@ -16905,7 +16905,7 @@
         <v>37</v>
       </c>
       <c r="F500">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="G500" t="s">
         <v>38</v>
@@ -16931,7 +16931,7 @@
         <v>37</v>
       </c>
       <c r="F501">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G501" t="s">
         <v>38</v>
